--- a/tour-finance/output/TOUR_all_linked.xlsx
+++ b/tour-finance/output/TOUR_all_linked.xlsx
@@ -12722,38 +12722,70 @@
           <t>รายได้รวม</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
+      <c r="B3" t="n">
+        <v>161.421</v>
+      </c>
+      <c r="C3" t="n">
+        <v>143.655</v>
+      </c>
+      <c r="D3" t="n">
+        <v>146.768</v>
+      </c>
       <c r="E3" s="9">
         <f>F3-B3-C3-D3</f>
         <v/>
       </c>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
+      <c r="F3" t="n">
+        <v>599.845</v>
+      </c>
+      <c r="G3" t="n">
+        <v>173.164</v>
+      </c>
+      <c r="H3" t="n">
+        <v>210.576</v>
+      </c>
+      <c r="I3" t="n">
+        <v>255.119</v>
+      </c>
       <c r="J3" s="9">
         <f>K3-G3-H3-I3</f>
         <v/>
       </c>
-      <c r="K3" s="5" t="n"/>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
+      <c r="K3" t="n">
+        <v>924.299</v>
+      </c>
+      <c r="L3" t="n">
+        <v>299.966</v>
+      </c>
+      <c r="M3" t="n">
+        <v>289.335</v>
+      </c>
+      <c r="N3" t="n">
+        <v>307.831</v>
+      </c>
       <c r="O3" s="9">
         <f>P3-L3-M3-N3</f>
         <v/>
       </c>
-      <c r="P3" s="5" t="n"/>
-      <c r="Q3" s="5" t="n"/>
-      <c r="R3" s="5" t="n"/>
-      <c r="S3" s="5" t="n"/>
+      <c r="P3" t="n">
+        <v>1188.482</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>316.06</v>
+      </c>
+      <c r="R3" t="n">
+        <v>306.951</v>
+      </c>
+      <c r="S3" t="n">
+        <v>326.359</v>
+      </c>
       <c r="T3" s="9">
         <f>U3-Q3-R3-S3</f>
         <v/>
       </c>
-      <c r="U3" s="5" t="n"/>
+      <c r="U3" t="n">
+        <v>1275.109</v>
+      </c>
       <c r="V3" t="n">
         <v>342.684</v>
       </c>
@@ -12777,38 +12809,70 @@
           <t>รายได้อื่น</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="B4" t="n">
+        <v>12.568</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13.539</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8.788</v>
+      </c>
       <c r="E4" s="9">
         <f>F4-B4-C4-D4</f>
         <v/>
       </c>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
+      <c r="F4" t="n">
+        <v>48.375</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10.123</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11.369</v>
+      </c>
+      <c r="I4" t="n">
+        <v>12.28</v>
+      </c>
       <c r="J4" s="9">
         <f>K4-G4-H4-I4</f>
         <v/>
       </c>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
+      <c r="K4" t="n">
+        <v>45.181</v>
+      </c>
+      <c r="L4" t="n">
+        <v>15.717</v>
+      </c>
+      <c r="M4" t="n">
+        <v>16.357</v>
+      </c>
+      <c r="N4" t="n">
+        <v>22.347</v>
+      </c>
       <c r="O4" s="9">
         <f>P4-L4-M4-N4</f>
         <v/>
       </c>
-      <c r="P4" s="5" t="n"/>
-      <c r="Q4" s="5" t="n"/>
-      <c r="R4" s="5" t="n"/>
-      <c r="S4" s="5" t="n"/>
+      <c r="P4" t="n">
+        <v>72.435</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15.012</v>
+      </c>
+      <c r="R4" t="n">
+        <v>19.732</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15.012</v>
+      </c>
       <c r="T4" s="9">
         <f>U4-Q4-R4-S4</f>
         <v/>
       </c>
-      <c r="U4" s="5" t="n"/>
+      <c r="U4" t="n">
+        <v>77.119</v>
+      </c>
       <c r="V4" t="n">
         <v>19.762</v>
       </c>
@@ -12832,38 +12896,70 @@
           <t>ต้นทุนขาย (จริง)</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="B5" t="n">
+        <v>155.453</v>
+      </c>
+      <c r="C5" t="n">
+        <v>150.548</v>
+      </c>
+      <c r="D5" t="n">
+        <v>137.157</v>
+      </c>
       <c r="E5" s="9">
         <f>F5-B5-C5-D5</f>
         <v/>
       </c>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
+      <c r="F5" t="n">
+        <v>603.606</v>
+      </c>
+      <c r="G5" t="n">
+        <v>161.775</v>
+      </c>
+      <c r="H5" t="n">
+        <v>179.281</v>
+      </c>
+      <c r="I5" t="n">
+        <v>201.105</v>
+      </c>
       <c r="J5" s="9">
         <f>K5-G5-H5-I5</f>
         <v/>
       </c>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
+      <c r="K5" t="n">
+        <v>747.973</v>
+      </c>
+      <c r="L5" t="n">
+        <v>219.817</v>
+      </c>
+      <c r="M5" t="n">
+        <v>220.397</v>
+      </c>
+      <c r="N5" t="n">
+        <v>223.495</v>
+      </c>
       <c r="O5" s="9">
         <f>P5-L5-M5-N5</f>
         <v/>
       </c>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
+      <c r="P5" t="n">
+        <v>876.527</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>220.309</v>
+      </c>
+      <c r="R5" t="n">
+        <v>222.275</v>
+      </c>
+      <c r="S5" t="n">
+        <v>241.647</v>
+      </c>
       <c r="T5" s="9">
         <f>U5-Q5-R5-S5</f>
         <v/>
       </c>
-      <c r="U5" s="5" t="n"/>
+      <c r="U5" t="n">
+        <v>921.247</v>
+      </c>
       <c r="V5" t="n">
         <v>233.19</v>
       </c>
@@ -12887,38 +12983,70 @@
           <t>กำไรสุทธิ (รวม)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
+      <c r="B6" t="n">
+        <v>-48.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-58.89</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-37.553</v>
+      </c>
       <c r="E6" s="9">
         <f>F6-B6-C6-D6</f>
         <v/>
       </c>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
+      <c r="F6" t="n">
+        <v>-210.623</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-49.978</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-35.144</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-25.28</v>
+      </c>
       <c r="J6" s="9">
         <f>K6-G6-H6-I6</f>
         <v/>
       </c>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
+      <c r="K6" t="n">
+        <v>-112.271</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-13.24</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-5.875</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5.997</v>
+      </c>
       <c r="O6" s="9">
         <f>P6-L6-M6-N6</f>
         <v/>
       </c>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
+      <c r="P6" t="n">
+        <v>-60.57</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-4.117</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-4.096</v>
+      </c>
       <c r="T6" s="9">
         <f>U6-Q6-R6-S6</f>
         <v/>
       </c>
-      <c r="U6" s="5" t="n"/>
+      <c r="U6" t="n">
+        <v>-5.596</v>
+      </c>
       <c r="V6" t="n">
         <v>14.423</v>
       </c>
@@ -12943,32 +13071,48 @@
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
+      <c r="C7" t="n">
+        <v>-58.854</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-36.74</v>
+      </c>
       <c r="E7" s="9">
         <f>F7-B7-C7-D7</f>
         <v/>
       </c>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
+      <c r="H7" t="n">
+        <v>-35.074</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-24.879</v>
+      </c>
       <c r="J7" s="9">
         <f>K7-G7-H7-I7</f>
         <v/>
       </c>
       <c r="K7" s="5" t="n"/>
       <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
+      <c r="M7" t="n">
+        <v>-5.349</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6.344</v>
+      </c>
       <c r="O7" s="9">
         <f>P7-L7-M7-N7</f>
         <v/>
       </c>
       <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
+      <c r="R7" t="n">
+        <v>-3.459</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-3.001</v>
+      </c>
       <c r="T7" s="9">
         <f>U7-Q7-R7-S7</f>
         <v/>
@@ -15911,22 +16055,54 @@
           <t>ลูกหนี้การค้า</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="n"/>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-      <c r="P3" s="5" t="n"/>
-      <c r="Q3" s="5" t="n"/>
+      <c r="B3" t="n">
+        <v>136.25</v>
+      </c>
+      <c r="C3" t="n">
+        <v>145.444</v>
+      </c>
+      <c r="D3" t="n">
+        <v>139.641</v>
+      </c>
+      <c r="E3" t="n">
+        <v>198.409</v>
+      </c>
+      <c r="F3" t="n">
+        <v>134.447</v>
+      </c>
+      <c r="G3" t="n">
+        <v>140.663</v>
+      </c>
+      <c r="H3" t="n">
+        <v>142.238</v>
+      </c>
+      <c r="I3" t="n">
+        <v>127.504</v>
+      </c>
+      <c r="J3" t="n">
+        <v>137.68</v>
+      </c>
+      <c r="K3" t="n">
+        <v>150.621</v>
+      </c>
+      <c r="L3" t="n">
+        <v>143.885</v>
+      </c>
+      <c r="M3" t="n">
+        <v>149.662</v>
+      </c>
+      <c r="N3" t="n">
+        <v>122.044</v>
+      </c>
+      <c r="O3" t="n">
+        <v>125.417</v>
+      </c>
+      <c r="P3" t="n">
+        <v>115.971</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>105.384</v>
+      </c>
       <c r="R3" t="n">
         <v>87.279</v>
       </c>
@@ -15949,22 +16125,54 @@
           <t>สินค้าคงเหลือ</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-      <c r="P4" s="5" t="n"/>
-      <c r="Q4" s="5" t="n"/>
+      <c r="B4" t="n">
+        <v>40.331</v>
+      </c>
+      <c r="C4" t="n">
+        <v>39.374</v>
+      </c>
+      <c r="D4" t="n">
+        <v>39.459</v>
+      </c>
+      <c r="E4" t="n">
+        <v>39.702</v>
+      </c>
+      <c r="F4" t="n">
+        <v>39.693</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.429</v>
+      </c>
+      <c r="H4" t="n">
+        <v>39.954</v>
+      </c>
+      <c r="I4" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="J4" t="n">
+        <v>40.001</v>
+      </c>
+      <c r="K4" t="n">
+        <v>40.924</v>
+      </c>
+      <c r="L4" t="n">
+        <v>41.095</v>
+      </c>
+      <c r="M4" t="n">
+        <v>42.135</v>
+      </c>
+      <c r="N4" t="n">
+        <v>43.539</v>
+      </c>
+      <c r="O4" t="n">
+        <v>43.141</v>
+      </c>
+      <c r="P4" t="n">
+        <v>43.78</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>44.865</v>
+      </c>
       <c r="R4" t="n">
         <v>46.247</v>
       </c>
@@ -15987,22 +16195,54 @@
           <t>เจ้าหนี้การค้า</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
+      <c r="B5" t="n">
+        <v>21.655</v>
+      </c>
+      <c r="C5" t="n">
+        <v>17.226</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13.107</v>
+      </c>
+      <c r="E5" t="n">
+        <v>18.514</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14.131</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16.515</v>
+      </c>
+      <c r="H5" t="n">
+        <v>21.681</v>
+      </c>
+      <c r="I5" t="n">
+        <v>24.026</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24.926</v>
+      </c>
+      <c r="K5" t="n">
+        <v>27.178</v>
+      </c>
+      <c r="L5" t="n">
+        <v>24.927</v>
+      </c>
+      <c r="M5" t="n">
+        <v>27.801</v>
+      </c>
+      <c r="N5" t="n">
+        <v>27.136</v>
+      </c>
+      <c r="O5" t="n">
+        <v>29.724</v>
+      </c>
+      <c r="P5" t="n">
+        <v>28.136</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>34.269</v>
+      </c>
       <c r="R5" t="n">
         <v>33.155</v>
       </c>
@@ -16025,22 +16265,54 @@
           <t>สินทรัพย์รวม</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
+      <c r="B6" t="n">
+        <v>9569.273999999999</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9453.575999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9433.053</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9416.727000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10500.936</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10401.72</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10389.057</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10415.012</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10456.552</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10324.99</v>
+      </c>
+      <c r="L6" t="n">
+        <v>10277.756</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10250.041</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10212.295</v>
+      </c>
+      <c r="O6" t="n">
+        <v>10195.015</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10337.145</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>10147.093</v>
+      </c>
       <c r="R6" t="n">
         <v>10140.751</v>
       </c>
@@ -16063,22 +16335,54 @@
           <t>ส่วนของเจ้าของรวม</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
+      <c r="B7" t="n">
+        <v>5340.39</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5272.208</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5225.804</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5220.527</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6070.568</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6056.51</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6057.951</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6077.899</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6092.038</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6072.954</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6068.102</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6085.32</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6049.842</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6075.806</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6073.584</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5982.58</v>
+      </c>
       <c r="R7" t="n">
         <v>6008.757</v>
       </c>
@@ -16101,22 +16405,54 @@
           <t>หนี้สินรวม</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
+      <c r="B8" t="n">
+        <v>4228.883</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4181.369</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4207.248</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4196.199</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4430.368</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4345.21</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4331.106</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4337.113</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4364.514</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4252.036</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4209.654</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4164.722</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4162.454</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4119.209</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4263.561</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4164.514</v>
+      </c>
       <c r="R8" t="n">
         <v>4131.994</v>
       </c>
@@ -18619,7 +18955,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=4, CENTEL=4, DUSIT=4, ERW=4, MANRIN=4, MINT=6, OHTL=4, SHANG=4, SHR=4, VRANDA=4</t>
+          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=4, DUSIT=4, ERW=4, MANRIN=4, MINT=6, OHTL=4, SHANG=4, SHR=4, VRANDA=4</t>
         </is>
       </c>
     </row>

--- a/tour-finance/output/TOUR_all_linked.xlsx
+++ b/tour-finance/output/TOUR_all_linked.xlsx
@@ -13169,38 +13169,70 @@
           <t>รายได้รวม</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="B9" t="n">
+        <v>2754.569</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2661.964</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2396.598</v>
+      </c>
       <c r="E9" s="9">
         <f>F9-B9-C9-D9</f>
         <v/>
       </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
+      <c r="F9" t="n">
+        <v>11528.506</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3851.608</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4296.949</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4527.85</v>
+      </c>
       <c r="J9" s="9">
         <f>K9-G9-H9-I9</f>
         <v/>
       </c>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
+      <c r="K9" t="n">
+        <v>18036.317</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5804.619</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5171.518</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5351.553</v>
+      </c>
       <c r="O9" s="9">
         <f>P9-L9-M9-N9</f>
         <v/>
       </c>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
+      <c r="P9" t="n">
+        <v>22261.37</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6321.691</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5763.953</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5539.57</v>
+      </c>
       <c r="T9" s="9">
         <f>U9-Q9-R9-S9</f>
         <v/>
       </c>
-      <c r="U9" s="5" t="n"/>
+      <c r="U9" t="n">
+        <v>23949.529</v>
+      </c>
       <c r="V9" t="n">
         <v>6695.756</v>
       </c>
@@ -13224,38 +13256,70 @@
           <t>รายได้อื่น</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
+      <c r="B10" t="n">
+        <v>72.532</v>
+      </c>
+      <c r="C10" t="n">
+        <v>264.614</v>
+      </c>
+      <c r="D10" t="n">
+        <v>341.183</v>
+      </c>
       <c r="E10" s="9">
         <f>F10-B10-C10-D10</f>
         <v/>
       </c>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
+      <c r="F10" t="n">
+        <v>317.256</v>
+      </c>
+      <c r="G10" t="n">
+        <v>170.493</v>
+      </c>
+      <c r="H10" t="n">
+        <v>379.093</v>
+      </c>
+      <c r="I10" t="n">
+        <v>384.698</v>
+      </c>
       <c r="J10" s="9">
         <f>K10-G10-H10-I10</f>
         <v/>
       </c>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
+      <c r="K10" t="n">
+        <v>534.308</v>
+      </c>
+      <c r="L10" t="n">
+        <v>274.671</v>
+      </c>
+      <c r="M10" t="n">
+        <v>495.957</v>
+      </c>
+      <c r="N10" t="n">
+        <v>664.926</v>
+      </c>
       <c r="O10" s="9">
         <f>P10-L10-M10-N10</f>
         <v/>
       </c>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n"/>
+      <c r="P10" t="n">
+        <v>703.732</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>217.796</v>
+      </c>
+      <c r="R10" t="n">
+        <v>674.042</v>
+      </c>
+      <c r="S10" t="n">
+        <v>721.003</v>
+      </c>
       <c r="T10" s="9">
         <f>U10-Q10-R10-S10</f>
         <v/>
       </c>
-      <c r="U10" s="5" t="n"/>
+      <c r="U10" t="n">
+        <v>900.6609999999999</v>
+      </c>
       <c r="V10" t="n">
         <v>273.087</v>
       </c>
@@ -13279,38 +13343,70 @@
           <t>ต้นทุนขาย (จริง)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
+      <c r="B11" t="n">
+        <v>1813.043</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1848.835</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1757.659</v>
+      </c>
       <c r="E11" s="9">
         <f>F11-B11-C11-D11</f>
         <v/>
       </c>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
+      <c r="F11" t="n">
+        <v>7613.439</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2285.245</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2518.558</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2669.11</v>
+      </c>
       <c r="J11" s="9">
         <f>K11-G11-H11-I11</f>
         <v/>
       </c>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
+      <c r="K11" t="n">
+        <v>10493.716</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3049.21</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3044.968</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3120.644</v>
+      </c>
       <c r="O11" s="9">
         <f>P11-L11-M11-N11</f>
         <v/>
       </c>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="5" t="n"/>
+      <c r="P11" t="n">
+        <v>12710.76</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3335.369</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3275.665</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3257.927</v>
+      </c>
       <c r="T11" s="9">
         <f>U11-Q11-R11-S11</f>
         <v/>
       </c>
-      <c r="U11" s="5" t="n"/>
+      <c r="U11" t="n">
+        <v>13424.442</v>
+      </c>
       <c r="V11" t="n">
         <v>3390.386</v>
       </c>
@@ -13334,38 +13430,70 @@
           <t>กำไรสุทธิ (รวม)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
+      <c r="B12" t="n">
+        <v>-480.758</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-634.245</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-832.299</v>
+      </c>
       <c r="E12" s="9">
         <f>F12-B12-C12-D12</f>
         <v/>
       </c>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
+      <c r="F12" t="n">
+        <v>-1757.4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-23.161</v>
+      </c>
+      <c r="H12" t="n">
+        <v>18.661</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-90.175</v>
+      </c>
       <c r="J12" s="9">
         <f>K12-G12-H12-I12</f>
         <v/>
       </c>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
+      <c r="K12" t="n">
+        <v>414.432</v>
+      </c>
+      <c r="L12" t="n">
+        <v>680.9349999999999</v>
+      </c>
+      <c r="M12" t="n">
+        <v>99.086</v>
+      </c>
+      <c r="N12" t="n">
+        <v>53.971</v>
+      </c>
       <c r="O12" s="9">
         <f>P12-L12-M12-N12</f>
         <v/>
       </c>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n"/>
+      <c r="P12" t="n">
+        <v>1256.213</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>785.318</v>
+      </c>
+      <c r="R12" t="n">
+        <v>124.139</v>
+      </c>
+      <c r="S12" t="n">
+        <v>150.556</v>
+      </c>
       <c r="T12" s="9">
         <f>U12-Q12-R12-S12</f>
         <v/>
       </c>
-      <c r="U12" s="5" t="n"/>
+      <c r="U12" t="n">
+        <v>1696.274</v>
+      </c>
       <c r="V12" t="n">
         <v>761.578</v>
       </c>
@@ -13389,38 +13517,70 @@
           <t>กำไรสุทธิ (ส่วนแม่)</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
+      <c r="B13" t="n">
+        <v>-475.727</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-606.4930000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-803.319</v>
+      </c>
       <c r="E13" s="9">
         <f>F13-B13-C13-D13</f>
         <v/>
       </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
+      <c r="F13" t="n">
+        <v>-1733.207</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-43.692</v>
+      </c>
+      <c r="H13" t="n">
+        <v>22.063</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-78.062</v>
+      </c>
       <c r="J13" s="9">
         <f>K13-G13-H13-I13</f>
         <v/>
       </c>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
+      <c r="K13" t="n">
+        <v>398.082</v>
+      </c>
+      <c r="L13" t="n">
+        <v>629.08</v>
+      </c>
+      <c r="M13" t="n">
+        <v>120.632</v>
+      </c>
+      <c r="N13" t="n">
+        <v>73.77200000000001</v>
+      </c>
       <c r="O13" s="9">
         <f>P13-L13-M13-N13</f>
         <v/>
       </c>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="5" t="n"/>
+      <c r="P13" t="n">
+        <v>1248.096</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>755.314</v>
+      </c>
+      <c r="R13" t="n">
+        <v>167.522</v>
+      </c>
+      <c r="S13" t="n">
+        <v>163.096</v>
+      </c>
       <c r="T13" s="9">
         <f>U13-Q13-R13-S13</f>
         <v/>
       </c>
-      <c r="U13" s="5" t="n"/>
+      <c r="U13" t="n">
+        <v>1752.985</v>
+      </c>
       <c r="V13" t="n">
         <v>747.845</v>
       </c>
@@ -16503,22 +16663,54 @@
           <t>ลูกหนี้การค้า</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="n"/>
+      <c r="B10" t="n">
+        <v>514.365</v>
+      </c>
+      <c r="C10" t="n">
+        <v>547.528</v>
+      </c>
+      <c r="D10" t="n">
+        <v>617.865</v>
+      </c>
+      <c r="E10" t="n">
+        <v>636.505</v>
+      </c>
+      <c r="F10" t="n">
+        <v>801.362</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000.029</v>
+      </c>
+      <c r="H10" t="n">
+        <v>942.428</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1016.611</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1227.403</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1302.916</v>
+      </c>
+      <c r="L10" t="n">
+        <v>758.174</v>
+      </c>
+      <c r="M10" t="n">
+        <v>829.4299999999999</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1518.978</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1316.054</v>
+      </c>
+      <c r="P10" t="n">
+        <v>935.457</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>861.2910000000001</v>
+      </c>
       <c r="R10" t="n">
         <v>1207.737</v>
       </c>
@@ -16541,22 +16733,54 @@
           <t>สินค้าคงเหลือ</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
+      <c r="B11" t="n">
+        <v>781.75</v>
+      </c>
+      <c r="C11" t="n">
+        <v>724.063</v>
+      </c>
+      <c r="D11" t="n">
+        <v>709.102</v>
+      </c>
+      <c r="E11" t="n">
+        <v>692.58</v>
+      </c>
+      <c r="F11" t="n">
+        <v>747.784</v>
+      </c>
+      <c r="G11" t="n">
+        <v>708.707</v>
+      </c>
+      <c r="H11" t="n">
+        <v>761.576</v>
+      </c>
+      <c r="I11" t="n">
+        <v>810.562</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1023.892</v>
+      </c>
+      <c r="K11" t="n">
+        <v>921.8440000000001</v>
+      </c>
+      <c r="L11" t="n">
+        <v>947.188</v>
+      </c>
+      <c r="M11" t="n">
+        <v>994.67</v>
+      </c>
+      <c r="N11" t="n">
+        <v>982.422</v>
+      </c>
+      <c r="O11" t="n">
+        <v>833.05</v>
+      </c>
+      <c r="P11" t="n">
+        <v>781.03</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>850.04</v>
+      </c>
       <c r="R11" t="n">
         <v>904.759</v>
       </c>
@@ -16579,22 +16803,54 @@
           <t>เจ้าหนี้การค้า</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="5" t="n"/>
+      <c r="B12" t="n">
+        <v>1872.976</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1709.627</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2025.123</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2231.583</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2669.31</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2499.627</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2692.844</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2944.464</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3459.77</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3104.468</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2603.264</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2676.562</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3445.335</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2946.41</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3422.567</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3499.966</v>
+      </c>
       <c r="R12" t="n">
         <v>4423.239</v>
       </c>
@@ -16617,22 +16873,54 @@
           <t>สินทรัพย์รวม</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="5" t="n"/>
+      <c r="B13" t="n">
+        <v>35350.143</v>
+      </c>
+      <c r="C13" t="n">
+        <v>35606.005</v>
+      </c>
+      <c r="D13" t="n">
+        <v>47682.473</v>
+      </c>
+      <c r="E13" t="n">
+        <v>47879.915</v>
+      </c>
+      <c r="F13" t="n">
+        <v>48592.543</v>
+      </c>
+      <c r="G13" t="n">
+        <v>48299.979</v>
+      </c>
+      <c r="H13" t="n">
+        <v>48024.246</v>
+      </c>
+      <c r="I13" t="n">
+        <v>48487.277</v>
+      </c>
+      <c r="J13" t="n">
+        <v>48165.592</v>
+      </c>
+      <c r="K13" t="n">
+        <v>53217.562</v>
+      </c>
+      <c r="L13" t="n">
+        <v>55207.933</v>
+      </c>
+      <c r="M13" t="n">
+        <v>53693.546</v>
+      </c>
+      <c r="N13" t="n">
+        <v>54203.613</v>
+      </c>
+      <c r="O13" t="n">
+        <v>54465.345</v>
+      </c>
+      <c r="P13" t="n">
+        <v>56258.126</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>56536.705</v>
+      </c>
       <c r="R13" t="n">
         <v>60760.633</v>
       </c>
@@ -16655,24 +16943,56 @@
           <t>ส่วนของเจ้าของรวม</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="5" t="n"/>
+      <c r="B14" t="n">
+        <v>10215.557</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9870.319</v>
+      </c>
+      <c r="D14" t="n">
+        <v>18980.132</v>
+      </c>
+      <c r="E14" t="n">
+        <v>18303.915</v>
+      </c>
+      <c r="F14" t="n">
+        <v>18431.688</v>
+      </c>
+      <c r="G14" t="n">
+        <v>18406.311</v>
+      </c>
+      <c r="H14" t="n">
+        <v>18618.833</v>
+      </c>
+      <c r="I14" t="n">
+        <v>18831.117</v>
+      </c>
+      <c r="J14" t="n">
+        <v>18890.728</v>
+      </c>
+      <c r="K14" t="n">
+        <v>19545.804</v>
+      </c>
+      <c r="L14" t="n">
+        <v>19812.619</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20005.735</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20017.983</v>
+      </c>
+      <c r="O14" t="n">
+        <v>21173.536</v>
+      </c>
+      <c r="P14" t="n">
+        <v>20811.002</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>19919.18</v>
+      </c>
       <c r="R14" t="n">
-        <v>20949.738</v>
+        <v>20949.737</v>
       </c>
       <c r="S14" t="n">
         <v>21712.54</v>
@@ -16693,22 +17013,54 @@
           <t>หนี้สินรวม</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="5" t="n"/>
+      <c r="B15" t="n">
+        <v>25134.586</v>
+      </c>
+      <c r="C15" t="n">
+        <v>25735.686</v>
+      </c>
+      <c r="D15" t="n">
+        <v>28702.341</v>
+      </c>
+      <c r="E15" t="n">
+        <v>29576</v>
+      </c>
+      <c r="F15" t="n">
+        <v>30160.854</v>
+      </c>
+      <c r="G15" t="n">
+        <v>29893.668</v>
+      </c>
+      <c r="H15" t="n">
+        <v>29405.413</v>
+      </c>
+      <c r="I15" t="n">
+        <v>29656.16</v>
+      </c>
+      <c r="J15" t="n">
+        <v>29274.864</v>
+      </c>
+      <c r="K15" t="n">
+        <v>33671.758</v>
+      </c>
+      <c r="L15" t="n">
+        <v>35395.314</v>
+      </c>
+      <c r="M15" t="n">
+        <v>33687.811</v>
+      </c>
+      <c r="N15" t="n">
+        <v>34185.63</v>
+      </c>
+      <c r="O15" t="n">
+        <v>33291.809</v>
+      </c>
+      <c r="P15" t="n">
+        <v>35447.124</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>36617.525</v>
+      </c>
       <c r="R15" t="n">
         <v>39810.895</v>
       </c>
@@ -18955,7 +19307,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=4, DUSIT=4, ERW=4, MANRIN=4, MINT=6, OHTL=4, SHANG=4, SHR=4, VRANDA=4</t>
+          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=4, ERW=4, MANRIN=4, MINT=6, OHTL=4, SHANG=4, SHR=4, VRANDA=4</t>
         </is>
       </c>
     </row>

--- a/tour-finance/output/TOUR_all_linked.xlsx
+++ b/tour-finance/output/TOUR_all_linked.xlsx
@@ -13636,38 +13636,70 @@
           <t>รายได้รวม</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
+      <c r="B15" t="n">
+        <v>666.595</v>
+      </c>
+      <c r="C15" t="n">
+        <v>632.841</v>
+      </c>
+      <c r="D15" t="n">
+        <v>830.933</v>
+      </c>
       <c r="E15" s="9">
         <f>F15-B15-C15-D15</f>
         <v/>
       </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
+      <c r="F15" t="n">
+        <v>3427.418</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1112.198</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1033.032</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1257.963</v>
+      </c>
       <c r="J15" s="9">
         <f>K15-G15-H15-I15</f>
         <v/>
       </c>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
+      <c r="K15" t="n">
+        <v>5104.079</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1688.672</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1348.349</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1415.732</v>
+      </c>
       <c r="O15" s="9">
         <f>P15-L15-M15-N15</f>
         <v/>
       </c>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="5" t="n"/>
+      <c r="P15" t="n">
+        <v>6361.84</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2105.334</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1561.562</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1441.319</v>
+      </c>
       <c r="T15" s="9">
         <f>U15-Q15-R15-S15</f>
         <v/>
       </c>
-      <c r="U15" s="5" t="n"/>
+      <c r="U15" t="n">
+        <v>11080.275</v>
+      </c>
       <c r="V15" t="n">
         <v>2344.842</v>
       </c>
@@ -13691,38 +13723,70 @@
           <t>รายได้อื่น</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
+      <c r="B16" t="n">
+        <v>111.981</v>
+      </c>
+      <c r="C16" t="n">
+        <v>95.873</v>
+      </c>
+      <c r="D16" t="n">
+        <v>83.685</v>
+      </c>
       <c r="E16" s="9">
         <f>F16-B16-C16-D16</f>
         <v/>
       </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
+      <c r="F16" t="n">
+        <v>415.078</v>
+      </c>
+      <c r="G16" t="n">
+        <v>78.605</v>
+      </c>
+      <c r="H16" t="n">
+        <v>143.172</v>
+      </c>
+      <c r="I16" t="n">
+        <v>244.914</v>
+      </c>
       <c r="J16" s="9">
         <f>K16-G16-H16-I16</f>
         <v/>
       </c>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
+      <c r="K16" t="n">
+        <v>613.544</v>
+      </c>
+      <c r="L16" t="n">
+        <v>204.263</v>
+      </c>
+      <c r="M16" t="n">
+        <v>212.948</v>
+      </c>
+      <c r="N16" t="n">
+        <v>221.776</v>
+      </c>
       <c r="O16" s="9">
         <f>P16-L16-M16-N16</f>
         <v/>
       </c>
-      <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="5" t="n"/>
+      <c r="P16" t="n">
+        <v>881.649</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>279.83</v>
+      </c>
+      <c r="R16" t="n">
+        <v>170.769</v>
+      </c>
+      <c r="S16" t="n">
+        <v>168.247</v>
+      </c>
       <c r="T16" s="9">
         <f>U16-Q16-R16-S16</f>
         <v/>
       </c>
-      <c r="U16" s="5" t="n"/>
+      <c r="U16" t="n">
+        <v>905.859</v>
+      </c>
       <c r="V16" t="n">
         <v>218.828</v>
       </c>
@@ -13746,38 +13810,70 @@
           <t>ต้นทุนขาย (จริง)</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
+      <c r="B17" t="n">
+        <v>508.519</v>
+      </c>
+      <c r="C17" t="n">
+        <v>402.241</v>
+      </c>
+      <c r="D17" t="n">
+        <v>541.069</v>
+      </c>
       <c r="E17" s="9">
         <f>F17-B17-C17-D17</f>
         <v/>
       </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
+      <c r="F17" t="n">
+        <v>2043.818</v>
+      </c>
+      <c r="G17" t="n">
+        <v>618.443</v>
+      </c>
+      <c r="H17" t="n">
+        <v>646.479</v>
+      </c>
+      <c r="I17" t="n">
+        <v>721.753</v>
+      </c>
       <c r="J17" s="9">
         <f>K17-G17-H17-I17</f>
         <v/>
       </c>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
+      <c r="K17" t="n">
+        <v>2851.015</v>
+      </c>
+      <c r="L17" t="n">
+        <v>897.178</v>
+      </c>
+      <c r="M17" t="n">
+        <v>772.196</v>
+      </c>
+      <c r="N17" t="n">
+        <v>843.255</v>
+      </c>
       <c r="O17" s="9">
         <f>P17-L17-M17-N17</f>
         <v/>
       </c>
-      <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="5" t="n"/>
+      <c r="P17" t="n">
+        <v>3612.823</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1105.459</v>
+      </c>
+      <c r="R17" t="n">
+        <v>917.9349999999999</v>
+      </c>
+      <c r="S17" t="n">
+        <v>888.6900000000001</v>
+      </c>
       <c r="T17" s="9">
         <f>U17-Q17-R17-S17</f>
         <v/>
       </c>
-      <c r="U17" s="5" t="n"/>
+      <c r="U17" t="n">
+        <v>7228.101</v>
+      </c>
       <c r="V17" t="n">
         <v>1355.983</v>
       </c>
@@ -13801,38 +13897,70 @@
           <t>กำไรสุทธิ (รวม)</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
+      <c r="B18" t="n">
+        <v>55.029</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-407.99</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-304.231</v>
+      </c>
       <c r="E18" s="9">
         <f>F18-B18-C18-D18</f>
         <v/>
       </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
+      <c r="F18" t="n">
+        <v>-1023.973</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-145.62</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-275.736</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-183.952</v>
+      </c>
       <c r="J18" s="9">
         <f>K18-G18-H18-I18</f>
         <v/>
       </c>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
+      <c r="K18" t="n">
+        <v>-547.147</v>
+      </c>
+      <c r="L18" t="n">
+        <v>11.324</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-193.65</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-253.504</v>
+      </c>
       <c r="O18" s="9">
         <f>P18-L18-M18-N18</f>
         <v/>
       </c>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="5" t="n"/>
+      <c r="P18" t="n">
+        <v>-584.066</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>126.005</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-136.814</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-571.999</v>
+      </c>
       <c r="T18" s="9">
         <f>U18-Q18-R18-S18</f>
         <v/>
       </c>
-      <c r="U18" s="5" t="n"/>
+      <c r="U18" t="n">
+        <v>-151.367</v>
+      </c>
       <c r="V18" t="n">
         <v>36.15</v>
       </c>
@@ -13856,38 +13984,70 @@
           <t>กำไรสุทธิ (ส่วนแม่)</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
+      <c r="B19" t="n">
+        <v>73.786</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-375.562</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-301.809</v>
+      </c>
       <c r="E19" s="9">
         <f>F19-B19-C19-D19</f>
         <v/>
       </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
+      <c r="F19" t="n">
+        <v>-944.997</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-128.665</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-257.749</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-161.23</v>
+      </c>
       <c r="J19" s="9">
         <f>K19-G19-H19-I19</f>
         <v/>
       </c>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
+      <c r="K19" t="n">
+        <v>-501.462</v>
+      </c>
+      <c r="L19" t="n">
+        <v>8.628</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-185.949</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-246.966</v>
+      </c>
       <c r="O19" s="9">
         <f>P19-L19-M19-N19</f>
         <v/>
       </c>
-      <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="5" t="n"/>
+      <c r="P19" t="n">
+        <v>-569.8200000000001</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>122.117</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-130.848</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-538.078</v>
+      </c>
       <c r="T19" s="9">
         <f>U19-Q19-R19-S19</f>
         <v/>
       </c>
-      <c r="U19" s="5" t="n"/>
+      <c r="U19" t="n">
+        <v>-236.765</v>
+      </c>
       <c r="V19" t="n">
         <v>47.856</v>
       </c>
@@ -17111,22 +17271,54 @@
           <t>ลูกหนี้การค้า</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="5" t="n"/>
+      <c r="B17" t="n">
+        <v>653.419</v>
+      </c>
+      <c r="C17" t="n">
+        <v>690.047</v>
+      </c>
+      <c r="D17" t="n">
+        <v>356.836</v>
+      </c>
+      <c r="E17" t="n">
+        <v>391.843</v>
+      </c>
+      <c r="F17" t="n">
+        <v>437.811</v>
+      </c>
+      <c r="G17" t="n">
+        <v>474.284</v>
+      </c>
+      <c r="H17" t="n">
+        <v>468.063</v>
+      </c>
+      <c r="I17" t="n">
+        <v>479.575</v>
+      </c>
+      <c r="J17" t="n">
+        <v>533.587</v>
+      </c>
+      <c r="K17" t="n">
+        <v>608.309</v>
+      </c>
+      <c r="L17" t="n">
+        <v>551.16</v>
+      </c>
+      <c r="M17" t="n">
+        <v>541.537</v>
+      </c>
+      <c r="N17" t="n">
+        <v>588.034</v>
+      </c>
+      <c r="O17" t="n">
+        <v>696.4109999999999</v>
+      </c>
+      <c r="P17" t="n">
+        <v>633.355</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>605.2089999999999</v>
+      </c>
       <c r="R17" t="n">
         <v>1145.08</v>
       </c>
@@ -17149,22 +17341,54 @@
           <t>สินค้าคงเหลือ</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="5" t="n"/>
+      <c r="B18" t="n">
+        <v>60.804</v>
+      </c>
+      <c r="C18" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>61.041</v>
+      </c>
+      <c r="E18" t="n">
+        <v>60.491</v>
+      </c>
+      <c r="F18" t="n">
+        <v>64.645</v>
+      </c>
+      <c r="G18" t="n">
+        <v>62.979</v>
+      </c>
+      <c r="H18" t="n">
+        <v>97.569</v>
+      </c>
+      <c r="I18" t="n">
+        <v>96.346</v>
+      </c>
+      <c r="J18" t="n">
+        <v>108.936</v>
+      </c>
+      <c r="K18" t="n">
+        <v>101.163</v>
+      </c>
+      <c r="L18" t="n">
+        <v>96.155</v>
+      </c>
+      <c r="M18" t="n">
+        <v>104.491</v>
+      </c>
+      <c r="N18" t="n">
+        <v>111.339</v>
+      </c>
+      <c r="O18" t="n">
+        <v>110.28</v>
+      </c>
+      <c r="P18" t="n">
+        <v>103.673</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>113.651</v>
+      </c>
       <c r="R18" t="n">
         <v>130.736</v>
       </c>
@@ -17187,22 +17411,54 @@
           <t>เจ้าหนี้การค้า</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="5" t="n"/>
+      <c r="B19" t="n">
+        <v>1387.644</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1320.651</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1288.561</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1079.508</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1120.696</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1183.463</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1340.928</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1499.649</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1924.155</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1590.817</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1583.687</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1535.035</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1963.555</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1958.66</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1985.955</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1551.973</v>
+      </c>
       <c r="R19" t="n">
         <v>1909.206</v>
       </c>
@@ -17225,22 +17481,54 @@
           <t>สินทรัพย์รวม</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="5" t="n"/>
+      <c r="B20" t="n">
+        <v>22837.787</v>
+      </c>
+      <c r="C20" t="n">
+        <v>22906.168</v>
+      </c>
+      <c r="D20" t="n">
+        <v>23480.262</v>
+      </c>
+      <c r="E20" t="n">
+        <v>23205.748</v>
+      </c>
+      <c r="F20" t="n">
+        <v>23784.095</v>
+      </c>
+      <c r="G20" t="n">
+        <v>23633.973</v>
+      </c>
+      <c r="H20" t="n">
+        <v>24406.326</v>
+      </c>
+      <c r="I20" t="n">
+        <v>25174.767</v>
+      </c>
+      <c r="J20" t="n">
+        <v>26229.168</v>
+      </c>
+      <c r="K20" t="n">
+        <v>26120.156</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26372.37</v>
+      </c>
+      <c r="M20" t="n">
+        <v>26866.736</v>
+      </c>
+      <c r="N20" t="n">
+        <v>27921.871</v>
+      </c>
+      <c r="O20" t="n">
+        <v>29137.063</v>
+      </c>
+      <c r="P20" t="n">
+        <v>36091.311</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>36535.809</v>
+      </c>
       <c r="R20" t="n">
         <v>38270.77</v>
       </c>
@@ -17263,22 +17551,54 @@
           <t>ส่วนของเจ้าของรวม</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
+      <c r="B21" t="n">
+        <v>4941.623</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5018.146</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4598.673</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4270.658</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3894.707</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3745.462</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3382.117</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4939.511</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5044.523</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4996.057</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4779.847</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4459.141</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4313.116</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4358.869</v>
+      </c>
+      <c r="P21" t="n">
+        <v>9148.35</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>8405.571</v>
+      </c>
       <c r="R21" t="n">
         <v>8788.434999999999</v>
       </c>
@@ -17301,22 +17621,54 @@
           <t>หนี้สินรวม</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
+      <c r="B22" t="n">
+        <v>17896.164</v>
+      </c>
+      <c r="C22" t="n">
+        <v>17888.022</v>
+      </c>
+      <c r="D22" t="n">
+        <v>18881.589</v>
+      </c>
+      <c r="E22" t="n">
+        <v>18935.09</v>
+      </c>
+      <c r="F22" t="n">
+        <v>19889.388</v>
+      </c>
+      <c r="G22" t="n">
+        <v>19888.511</v>
+      </c>
+      <c r="H22" t="n">
+        <v>21024.209</v>
+      </c>
+      <c r="I22" t="n">
+        <v>20235.256</v>
+      </c>
+      <c r="J22" t="n">
+        <v>21184.645</v>
+      </c>
+      <c r="K22" t="n">
+        <v>21124.099</v>
+      </c>
+      <c r="L22" t="n">
+        <v>21592.523</v>
+      </c>
+      <c r="M22" t="n">
+        <v>22407.595</v>
+      </c>
+      <c r="N22" t="n">
+        <v>23608.755</v>
+      </c>
+      <c r="O22" t="n">
+        <v>24778.194</v>
+      </c>
+      <c r="P22" t="n">
+        <v>26942.961</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>28130.238</v>
+      </c>
       <c r="R22" t="n">
         <v>29482.335</v>
       </c>
@@ -19307,7 +19659,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=4, ERW=4, MANRIN=4, MINT=6, OHTL=4, SHANG=4, SHR=4, VRANDA=4</t>
+          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=4, MANRIN=4, MINT=6, OHTL=4, SHANG=4, SHR=4, VRANDA=4</t>
         </is>
       </c>
     </row>

--- a/tour-finance/output/TOUR_all_linked.xlsx
+++ b/tour-finance/output/TOUR_all_linked.xlsx
@@ -14103,38 +14103,70 @@
           <t>รายได้รวม</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
+      <c r="B21" t="n">
+        <v>390.059</v>
+      </c>
+      <c r="C21" t="n">
+        <v>269.132</v>
+      </c>
+      <c r="D21" t="n">
+        <v>253.762</v>
+      </c>
       <c r="E21" s="9">
         <f>F21-B21-C21-D21</f>
         <v/>
       </c>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
+      <c r="F21" t="n">
+        <v>1641.258</v>
+      </c>
+      <c r="G21" t="n">
+        <v>646.0940000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1006.085</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1289.39</v>
+      </c>
       <c r="J21" s="9">
         <f>K21-G21-H21-I21</f>
         <v/>
       </c>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
+      <c r="K21" t="n">
+        <v>4717.288</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1774.625</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1641.935</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1742.8</v>
+      </c>
       <c r="O21" s="9">
         <f>P21-L21-M21-N21</f>
         <v/>
       </c>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="5" t="n"/>
+      <c r="P21" t="n">
+        <v>7046.29</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2119.357</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1843.268</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1856.024</v>
+      </c>
       <c r="T21" s="9">
         <f>U21-Q21-R21-S21</f>
         <v/>
       </c>
-      <c r="U21" s="5" t="n"/>
+      <c r="U21" t="n">
+        <v>8053.926</v>
+      </c>
       <c r="V21" t="n">
         <v>2135.663</v>
       </c>
@@ -14158,38 +14190,70 @@
           <t>รายได้อื่น</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
+      <c r="B22" t="n">
+        <v>11.432</v>
+      </c>
+      <c r="C22" t="n">
+        <v>23.294</v>
+      </c>
+      <c r="D22" t="n">
+        <v>70.71899999999999</v>
+      </c>
       <c r="E22" s="9">
         <f>F22-B22-C22-D22</f>
         <v/>
       </c>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
+      <c r="F22" t="n">
+        <v>77.11799999999999</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7.275</v>
+      </c>
+      <c r="H22" t="n">
+        <v>69.651</v>
+      </c>
+      <c r="I22" t="n">
+        <v>49.647</v>
+      </c>
       <c r="J22" s="9">
         <f>K22-G22-H22-I22</f>
         <v/>
       </c>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
+      <c r="K22" t="n">
+        <v>86.023</v>
+      </c>
+      <c r="L22" t="n">
+        <v>20.232</v>
+      </c>
+      <c r="M22" t="n">
+        <v>52.552</v>
+      </c>
+      <c r="N22" t="n">
+        <v>48.472</v>
+      </c>
       <c r="O22" s="9">
         <f>P22-L22-M22-N22</f>
         <v/>
       </c>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n"/>
+      <c r="P22" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>14.968</v>
+      </c>
+      <c r="R22" t="n">
+        <v>28.872</v>
+      </c>
+      <c r="S22" t="n">
+        <v>33.976</v>
+      </c>
       <c r="T22" s="9">
         <f>U22-Q22-R22-S22</f>
         <v/>
       </c>
-      <c r="U22" s="5" t="n"/>
+      <c r="U22" t="n">
+        <v>45.19</v>
+      </c>
       <c r="V22" t="n">
         <v>6.865</v>
       </c>
@@ -14213,38 +14277,70 @@
           <t>ต้นทุนขาย (จริง)</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
+      <c r="B23" t="n">
+        <v>315.026</v>
+      </c>
+      <c r="C23" t="n">
+        <v>284.888</v>
+      </c>
+      <c r="D23" t="n">
+        <v>286.682</v>
+      </c>
       <c r="E23" s="9">
         <f>F23-B23-C23-D23</f>
         <v/>
       </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
+      <c r="F23" t="n">
+        <v>1284.16</v>
+      </c>
+      <c r="G23" t="n">
+        <v>404.82</v>
+      </c>
+      <c r="H23" t="n">
+        <v>519.9880000000001</v>
+      </c>
+      <c r="I23" t="n">
+        <v>607.211</v>
+      </c>
       <c r="J23" s="9">
         <f>K23-G23-H23-I23</f>
         <v/>
       </c>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
+      <c r="K23" t="n">
+        <v>2282.152</v>
+      </c>
+      <c r="L23" t="n">
+        <v>775.229</v>
+      </c>
+      <c r="M23" t="n">
+        <v>726.693</v>
+      </c>
+      <c r="N23" t="n">
+        <v>757.077</v>
+      </c>
       <c r="O23" s="9">
         <f>P23-L23-M23-N23</f>
         <v/>
       </c>
-      <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="5" t="n"/>
-      <c r="R23" s="5" t="n"/>
-      <c r="S23" s="5" t="n"/>
+      <c r="P23" t="n">
+        <v>3034.518</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>793.662</v>
+      </c>
+      <c r="R23" t="n">
+        <v>809.742</v>
+      </c>
+      <c r="S23" t="n">
+        <v>812.235</v>
+      </c>
       <c r="T23" s="9">
         <f>U23-Q23-R23-S23</f>
         <v/>
       </c>
-      <c r="U23" s="5" t="n"/>
+      <c r="U23" t="n">
+        <v>3275.985</v>
+      </c>
       <c r="V23" t="n">
         <v>836.5890000000001</v>
       </c>
@@ -14268,38 +14364,70 @@
           <t>กำไรสุทธิ (รวม)</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
+      <c r="B24" t="n">
+        <v>-512.877</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-716.788</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-667.617</v>
+      </c>
       <c r="E24" s="9">
         <f>F24-B24-C24-D24</f>
         <v/>
       </c>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
+      <c r="F24" t="n">
+        <v>-2155.372</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-324.862</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-143.041</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-5.353</v>
+      </c>
       <c r="J24" s="9">
         <f>K24-G24-H24-I24</f>
         <v/>
       </c>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
+      <c r="K24" t="n">
+        <v>-213.062</v>
+      </c>
+      <c r="L24" t="n">
+        <v>237.391</v>
+      </c>
+      <c r="M24" t="n">
+        <v>143.879</v>
+      </c>
+      <c r="N24" t="n">
+        <v>155.228</v>
+      </c>
       <c r="O24" s="9">
         <f>P24-L24-M24-N24</f>
         <v/>
       </c>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="5" t="n"/>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="5" t="n"/>
+      <c r="P24" t="n">
+        <v>759.877</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>428.404</v>
+      </c>
+      <c r="R24" t="n">
+        <v>365.506</v>
+      </c>
+      <c r="S24" t="n">
+        <v>124.49</v>
+      </c>
       <c r="T24" s="9">
         <f>U24-Q24-R24-S24</f>
         <v/>
       </c>
-      <c r="U24" s="5" t="n"/>
+      <c r="U24" t="n">
+        <v>1312.506</v>
+      </c>
       <c r="V24" t="n">
         <v>362.736</v>
       </c>
@@ -14324,32 +14452,48 @@
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
+      <c r="C25" t="n">
+        <v>-689.778</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-622.789</v>
+      </c>
       <c r="E25" s="9">
         <f>F25-B25-C25-D25</f>
         <v/>
       </c>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
+      <c r="H25" t="n">
+        <v>-139.108</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-11.52</v>
+      </c>
       <c r="J25" s="9">
         <f>K25-G25-H25-I25</f>
         <v/>
       </c>
       <c r="K25" s="5" t="n"/>
       <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
+      <c r="M25" t="n">
+        <v>141.969</v>
+      </c>
+      <c r="N25" t="n">
+        <v>148.293</v>
+      </c>
       <c r="O25" s="9">
         <f>P25-L25-M25-N25</f>
         <v/>
       </c>
       <c r="P25" s="5" t="n"/>
       <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="5" t="n"/>
-      <c r="S25" s="5" t="n"/>
+      <c r="R25" t="n">
+        <v>361.434</v>
+      </c>
+      <c r="S25" t="n">
+        <v>124.53</v>
+      </c>
       <c r="T25" s="9">
         <f>U25-Q25-R25-S25</f>
         <v/>
@@ -17719,22 +17863,54 @@
           <t>ลูกหนี้การค้า</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="5" t="n"/>
+      <c r="B24" t="n">
+        <v>76.587</v>
+      </c>
+      <c r="C24" t="n">
+        <v>66.958</v>
+      </c>
+      <c r="D24" t="n">
+        <v>47.166</v>
+      </c>
+      <c r="E24" t="n">
+        <v>53.535</v>
+      </c>
+      <c r="F24" t="n">
+        <v>99.854</v>
+      </c>
+      <c r="G24" t="n">
+        <v>116.99</v>
+      </c>
+      <c r="H24" t="n">
+        <v>115.151</v>
+      </c>
+      <c r="I24" t="n">
+        <v>145.022</v>
+      </c>
+      <c r="J24" t="n">
+        <v>159.805</v>
+      </c>
+      <c r="K24" t="n">
+        <v>155.536</v>
+      </c>
+      <c r="L24" t="n">
+        <v>129.797</v>
+      </c>
+      <c r="M24" t="n">
+        <v>127.605</v>
+      </c>
+      <c r="N24" t="n">
+        <v>169.827</v>
+      </c>
+      <c r="O24" t="n">
+        <v>150.106</v>
+      </c>
+      <c r="P24" t="n">
+        <v>143.792</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>139.711</v>
+      </c>
       <c r="R24" t="n">
         <v>222.438</v>
       </c>
@@ -17757,22 +17933,54 @@
           <t>สินค้าคงเหลือ</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="5" t="n"/>
+      <c r="B25" t="n">
+        <v>46.207</v>
+      </c>
+      <c r="C25" t="n">
+        <v>40.275</v>
+      </c>
+      <c r="D25" t="n">
+        <v>38.527</v>
+      </c>
+      <c r="E25" t="n">
+        <v>37.071</v>
+      </c>
+      <c r="F25" t="n">
+        <v>39.306</v>
+      </c>
+      <c r="G25" t="n">
+        <v>35.258</v>
+      </c>
+      <c r="H25" t="n">
+        <v>37.341</v>
+      </c>
+      <c r="I25" t="n">
+        <v>38.492</v>
+      </c>
+      <c r="J25" t="n">
+        <v>43.467</v>
+      </c>
+      <c r="K25" t="n">
+        <v>37.421</v>
+      </c>
+      <c r="L25" t="n">
+        <v>37.818</v>
+      </c>
+      <c r="M25" t="n">
+        <v>41.197</v>
+      </c>
+      <c r="N25" t="n">
+        <v>48.963</v>
+      </c>
+      <c r="O25" t="n">
+        <v>42.976</v>
+      </c>
+      <c r="P25" t="n">
+        <v>40.795</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>41.77</v>
+      </c>
       <c r="R25" t="n">
         <v>42.817</v>
       </c>
@@ -17795,22 +18003,54 @@
           <t>เจ้าหนี้การค้า</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="5" t="n"/>
+      <c r="B26" t="n">
+        <v>144.666</v>
+      </c>
+      <c r="C26" t="n">
+        <v>103.802</v>
+      </c>
+      <c r="D26" t="n">
+        <v>70.72799999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>70.03</v>
+      </c>
+      <c r="F26" t="n">
+        <v>142.676</v>
+      </c>
+      <c r="G26" t="n">
+        <v>106.87</v>
+      </c>
+      <c r="H26" t="n">
+        <v>126.184</v>
+      </c>
+      <c r="I26" t="n">
+        <v>142.653</v>
+      </c>
+      <c r="J26" t="n">
+        <v>234.513</v>
+      </c>
+      <c r="K26" t="n">
+        <v>173.704</v>
+      </c>
+      <c r="L26" t="n">
+        <v>150.803</v>
+      </c>
+      <c r="M26" t="n">
+        <v>180.31</v>
+      </c>
+      <c r="N26" t="n">
+        <v>226.853</v>
+      </c>
+      <c r="O26" t="n">
+        <v>209.768</v>
+      </c>
+      <c r="P26" t="n">
+        <v>192.776</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>169.55</v>
+      </c>
       <c r="R26" t="n">
         <v>266.009</v>
       </c>
@@ -17833,22 +18073,54 @@
           <t>สินทรัพย์รวม</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="5" t="n"/>
+      <c r="B27" t="n">
+        <v>21214.717</v>
+      </c>
+      <c r="C27" t="n">
+        <v>21048.98</v>
+      </c>
+      <c r="D27" t="n">
+        <v>23603.712</v>
+      </c>
+      <c r="E27" t="n">
+        <v>23296.713</v>
+      </c>
+      <c r="F27" t="n">
+        <v>22450.213</v>
+      </c>
+      <c r="G27" t="n">
+        <v>22388.076</v>
+      </c>
+      <c r="H27" t="n">
+        <v>21250.682</v>
+      </c>
+      <c r="I27" t="n">
+        <v>21433.702</v>
+      </c>
+      <c r="J27" t="n">
+        <v>21711.812</v>
+      </c>
+      <c r="K27" t="n">
+        <v>21482.14</v>
+      </c>
+      <c r="L27" t="n">
+        <v>21552.764</v>
+      </c>
+      <c r="M27" t="n">
+        <v>23814.068</v>
+      </c>
+      <c r="N27" t="n">
+        <v>23674.931</v>
+      </c>
+      <c r="O27" t="n">
+        <v>23907.039</v>
+      </c>
+      <c r="P27" t="n">
+        <v>25567.646</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>24928.592</v>
+      </c>
       <c r="R27" t="n">
         <v>26246.078</v>
       </c>
@@ -17871,22 +18143,54 @@
           <t>ส่วนของเจ้าของรวม</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-      <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="5" t="n"/>
+      <c r="B28" t="n">
+        <v>3928.559</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3439.943</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6959.668</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6309.161</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6022.719</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5657.401</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5551.743</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5566.029</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5721.626</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5980.403</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6166.695</v>
+      </c>
+      <c r="M28" t="n">
+        <v>6277.706</v>
+      </c>
+      <c r="N28" t="n">
+        <v>6369.945</v>
+      </c>
+      <c r="O28" t="n">
+        <v>6831.886</v>
+      </c>
+      <c r="P28" t="n">
+        <v>7860.623</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>7834.106</v>
+      </c>
       <c r="R28" t="n">
         <v>9491.813</v>
       </c>
@@ -17909,22 +18213,54 @@
           <t>หนี้สินรวม</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-      <c r="P29" s="5" t="n"/>
-      <c r="Q29" s="5" t="n"/>
+      <c r="B29" t="n">
+        <v>17286.158</v>
+      </c>
+      <c r="C29" t="n">
+        <v>17609.037</v>
+      </c>
+      <c r="D29" t="n">
+        <v>16644.044</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16987.552</v>
+      </c>
+      <c r="F29" t="n">
+        <v>16427.494</v>
+      </c>
+      <c r="G29" t="n">
+        <v>16730.675</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15698.939</v>
+      </c>
+      <c r="I29" t="n">
+        <v>15867.673</v>
+      </c>
+      <c r="J29" t="n">
+        <v>15990.185</v>
+      </c>
+      <c r="K29" t="n">
+        <v>15501.737</v>
+      </c>
+      <c r="L29" t="n">
+        <v>15386.069</v>
+      </c>
+      <c r="M29" t="n">
+        <v>17536.362</v>
+      </c>
+      <c r="N29" t="n">
+        <v>17304.986</v>
+      </c>
+      <c r="O29" t="n">
+        <v>17075.153</v>
+      </c>
+      <c r="P29" t="n">
+        <v>17707.023</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>17094.486</v>
+      </c>
       <c r="R29" t="n">
         <v>16754.265</v>
       </c>
@@ -19659,7 +19995,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=4, MANRIN=4, MINT=6, OHTL=4, SHANG=4, SHR=4, VRANDA=4</t>
+          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=20, MANRIN=4, MINT=6, OHTL=4, SHANG=4, SHR=4, VRANDA=4</t>
         </is>
       </c>
     </row>

--- a/tour-finance/output/TOUR_all_linked.xlsx
+++ b/tour-finance/output/TOUR_all_linked.xlsx
@@ -13081,7 +13081,10 @@
         <f>F7-B7-C7-D7</f>
         <v/>
       </c>
-      <c r="F7" s="5" t="n"/>
+      <c r="F7" s="9">
+        <f>B7+C7+D7+E7</f>
+        <v/>
+      </c>
       <c r="G7" s="5" t="n"/>
       <c r="H7" t="n">
         <v>-35.074</v>
@@ -13093,7 +13096,10 @@
         <f>K7-G7-H7-I7</f>
         <v/>
       </c>
-      <c r="K7" s="5" t="n"/>
+      <c r="K7" s="9">
+        <f>G7+H7+I7+J7</f>
+        <v/>
+      </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" t="n">
         <v>-5.349</v>
@@ -13105,7 +13111,10 @@
         <f>P7-L7-M7-N7</f>
         <v/>
       </c>
-      <c r="P7" s="5" t="n"/>
+      <c r="P7" s="9">
+        <f>L7+M7+N7+O7</f>
+        <v/>
+      </c>
       <c r="Q7" s="5" t="n"/>
       <c r="R7" t="n">
         <v>-3.459</v>
@@ -13117,7 +13126,10 @@
         <f>U7-Q7-R7-S7</f>
         <v/>
       </c>
-      <c r="U7" s="5" t="n"/>
+      <c r="U7" s="9">
+        <f>Q7+R7+S7+T7</f>
+        <v/>
+      </c>
       <c r="V7" s="5" t="n"/>
       <c r="W7" t="n">
         <v>-14.469</v>
@@ -13129,7 +13141,10 @@
         <f>Z7-V7-W7-X7</f>
         <v/>
       </c>
-      <c r="Z7" s="5" t="n"/>
+      <c r="Z7" s="9">
+        <f>V7+W7+X7+Y7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -14462,7 +14477,10 @@
         <f>F25-B25-C25-D25</f>
         <v/>
       </c>
-      <c r="F25" s="5" t="n"/>
+      <c r="F25" s="9">
+        <f>B25+C25+D25+E25</f>
+        <v/>
+      </c>
       <c r="G25" s="5" t="n"/>
       <c r="H25" t="n">
         <v>-139.108</v>
@@ -14474,7 +14492,10 @@
         <f>K25-G25-H25-I25</f>
         <v/>
       </c>
-      <c r="K25" s="5" t="n"/>
+      <c r="K25" s="9">
+        <f>G25+H25+I25+J25</f>
+        <v/>
+      </c>
       <c r="L25" s="5" t="n"/>
       <c r="M25" t="n">
         <v>141.969</v>
@@ -14486,7 +14507,10 @@
         <f>P25-L25-M25-N25</f>
         <v/>
       </c>
-      <c r="P25" s="5" t="n"/>
+      <c r="P25" s="9">
+        <f>L25+M25+N25+O25</f>
+        <v/>
+      </c>
       <c r="Q25" s="5" t="n"/>
       <c r="R25" t="n">
         <v>361.434</v>
@@ -14498,7 +14522,10 @@
         <f>U25-Q25-R25-S25</f>
         <v/>
       </c>
-      <c r="U25" s="5" t="n"/>
+      <c r="U25" s="9">
+        <f>Q25+R25+S25+T25</f>
+        <v/>
+      </c>
       <c r="V25" s="5" t="n"/>
       <c r="W25" s="5" t="n"/>
       <c r="X25" t="n">
@@ -14508,7 +14535,10 @@
         <f>Z25-V25-W25-X25</f>
         <v/>
       </c>
-      <c r="Z25" s="5" t="n"/>
+      <c r="Z25" s="9">
+        <f>V25+W25+X25+Y25</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -14548,38 +14578,70 @@
           <t>รายได้รวม</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="9">
-        <f>F27-B27-C27-D27</f>
-        <v/>
-      </c>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="9">
-        <f>K27-G27-H27-I27</f>
-        <v/>
-      </c>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="9">
-        <f>P27-L27-M27-N27</f>
-        <v/>
-      </c>
-      <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="5" t="n"/>
-      <c r="R27" s="5" t="n"/>
-      <c r="S27" s="5" t="n"/>
+      <c r="B27" t="n">
+        <v>9.414</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4.916</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E27" t="n">
+        <v>9.366</v>
+      </c>
+      <c r="F27" s="9">
+        <f>B27+C27+D27+E27</f>
+        <v/>
+      </c>
+      <c r="G27" t="n">
+        <v>13.143</v>
+      </c>
+      <c r="H27" t="n">
+        <v>32.014</v>
+      </c>
+      <c r="I27" t="n">
+        <v>51.026</v>
+      </c>
+      <c r="J27" t="n">
+        <v>71.111</v>
+      </c>
+      <c r="K27" s="9">
+        <f>G27+H27+I27+J27</f>
+        <v/>
+      </c>
+      <c r="L27" t="n">
+        <v>76.04000000000001</v>
+      </c>
+      <c r="M27" t="n">
+        <v>68.61499999999999</v>
+      </c>
+      <c r="N27" t="n">
+        <v>90.678</v>
+      </c>
+      <c r="O27" t="n">
+        <v>89.961</v>
+      </c>
+      <c r="P27" s="9">
+        <f>L27+M27+N27+O27</f>
+        <v/>
+      </c>
+      <c r="Q27" t="n">
+        <v>93.40300000000001</v>
+      </c>
+      <c r="R27" t="n">
+        <v>80.831</v>
+      </c>
+      <c r="S27" t="n">
+        <v>99.85599999999999</v>
+      </c>
       <c r="T27" s="9">
         <f>U27-Q27-R27-S27</f>
         <v/>
       </c>
-      <c r="U27" s="5" t="n"/>
+      <c r="U27" t="n">
+        <v>376.742</v>
+      </c>
       <c r="V27" t="n">
         <v>97.881</v>
       </c>
@@ -14603,38 +14665,70 @@
           <t>รายได้อื่น</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="9">
-        <f>F28-B28-C28-D28</f>
-        <v/>
-      </c>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="9">
-        <f>K28-G28-H28-I28</f>
-        <v/>
-      </c>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="9">
-        <f>P28-L28-M28-N28</f>
-        <v/>
-      </c>
-      <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="5" t="n"/>
-      <c r="R28" s="5" t="n"/>
-      <c r="S28" s="5" t="n"/>
+      <c r="B28" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="F28" s="9">
+        <f>B28+C28+D28+E28</f>
+        <v/>
+      </c>
+      <c r="G28" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K28" s="9">
+        <f>G28+H28+I28+J28</f>
+        <v/>
+      </c>
+      <c r="L28" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="P28" s="9">
+        <f>L28+M28+N28+O28</f>
+        <v/>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.239</v>
+      </c>
       <c r="T28" s="9">
         <f>U28-Q28-R28-S28</f>
         <v/>
       </c>
-      <c r="U28" s="5" t="n"/>
+      <c r="U28" t="n">
+        <v>1.161</v>
+      </c>
       <c r="V28" t="n">
         <v>0.176</v>
       </c>
@@ -14658,38 +14752,70 @@
           <t>ต้นทุนขาย (จริง)</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="9">
-        <f>F29-B29-C29-D29</f>
-        <v/>
-      </c>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="9">
-        <f>K29-G29-H29-I29</f>
-        <v/>
-      </c>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="9">
-        <f>P29-L29-M29-N29</f>
-        <v/>
-      </c>
-      <c r="P29" s="5" t="n"/>
-      <c r="Q29" s="5" t="n"/>
-      <c r="R29" s="5" t="n"/>
-      <c r="S29" s="5" t="n"/>
+      <c r="B29" t="n">
+        <v>24.135</v>
+      </c>
+      <c r="C29" t="n">
+        <v>22.547</v>
+      </c>
+      <c r="D29" t="n">
+        <v>20.772</v>
+      </c>
+      <c r="E29" t="n">
+        <v>24.077</v>
+      </c>
+      <c r="F29" s="9">
+        <f>B29+C29+D29+E29</f>
+        <v/>
+      </c>
+      <c r="G29" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="H29" t="n">
+        <v>34.428</v>
+      </c>
+      <c r="I29" t="n">
+        <v>42.762</v>
+      </c>
+      <c r="J29" t="n">
+        <v>48.739</v>
+      </c>
+      <c r="K29" s="9">
+        <f>G29+H29+I29+J29</f>
+        <v/>
+      </c>
+      <c r="L29" t="n">
+        <v>51.265</v>
+      </c>
+      <c r="M29" t="n">
+        <v>46.198</v>
+      </c>
+      <c r="N29" t="n">
+        <v>55.052</v>
+      </c>
+      <c r="O29" t="n">
+        <v>52.535</v>
+      </c>
+      <c r="P29" s="9">
+        <f>L29+M29+N29+O29</f>
+        <v/>
+      </c>
+      <c r="Q29" t="n">
+        <v>50.823</v>
+      </c>
+      <c r="R29" t="n">
+        <v>46.844</v>
+      </c>
+      <c r="S29" t="n">
+        <v>55.598</v>
+      </c>
       <c r="T29" s="9">
         <f>U29-Q29-R29-S29</f>
         <v/>
       </c>
-      <c r="U29" s="5" t="n"/>
+      <c r="U29" t="n">
+        <v>210.68</v>
+      </c>
       <c r="V29" t="n">
         <v>53.115</v>
       </c>
@@ -14713,38 +14839,70 @@
           <t>กำไรสุทธิ (รวม)</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="9">
-        <f>F30-B30-C30-D30</f>
-        <v/>
-      </c>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="9">
-        <f>K30-G30-H30-I30</f>
-        <v/>
-      </c>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="9">
-        <f>P30-L30-M30-N30</f>
-        <v/>
-      </c>
-      <c r="P30" s="5" t="n"/>
-      <c r="Q30" s="5" t="n"/>
-      <c r="R30" s="5" t="n"/>
-      <c r="S30" s="5" t="n"/>
+      <c r="B30" t="n">
+        <v>-16.489</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-22.583</v>
+      </c>
+      <c r="D30" t="n">
+        <v>12.558</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-22.328</v>
+      </c>
+      <c r="F30" s="9">
+        <f>B30+C30+D30+E30</f>
+        <v/>
+      </c>
+      <c r="G30" t="n">
+        <v>-30.293</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-12.05</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-4.503</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6.961</v>
+      </c>
+      <c r="K30" s="9">
+        <f>G30+H30+I30+J30</f>
+        <v/>
+      </c>
+      <c r="L30" t="n">
+        <v>6.844</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="N30" t="n">
+        <v>15.371</v>
+      </c>
+      <c r="O30" t="n">
+        <v>11.273</v>
+      </c>
+      <c r="P30" s="9">
+        <f>L30+M30+N30+O30</f>
+        <v/>
+      </c>
+      <c r="Q30" t="n">
+        <v>13.794</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6.882</v>
+      </c>
+      <c r="S30" t="n">
+        <v>18.194</v>
+      </c>
       <c r="T30" s="9">
         <f>U30-Q30-R30-S30</f>
         <v/>
       </c>
-      <c r="U30" s="5" t="n"/>
+      <c r="U30" t="n">
+        <v>50.821</v>
+      </c>
       <c r="V30" t="n">
         <v>14.114</v>
       </c>
@@ -14771,27 +14929,27 @@
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="5" t="n"/>
       <c r="D31" s="5" t="n"/>
-      <c r="E31" s="9">
-        <f>F31-B31-C31-D31</f>
-        <v/>
-      </c>
-      <c r="F31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="9">
+        <f>B31+C31+D31+E31</f>
+        <v/>
+      </c>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="n"/>
-      <c r="J31" s="9">
-        <f>K31-G31-H31-I31</f>
-        <v/>
-      </c>
-      <c r="K31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="9">
+        <f>G31+H31+I31+J31</f>
+        <v/>
+      </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="5" t="n"/>
       <c r="N31" s="5" t="n"/>
-      <c r="O31" s="9">
-        <f>P31-L31-M31-N31</f>
-        <v/>
-      </c>
-      <c r="P31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="9">
+        <f>L31+M31+N31+O31</f>
+        <v/>
+      </c>
       <c r="Q31" s="5" t="n"/>
       <c r="R31" s="5" t="n"/>
       <c r="S31" s="5" t="n"/>
@@ -14799,7 +14957,10 @@
         <f>U31-Q31-R31-S31</f>
         <v/>
       </c>
-      <c r="U31" s="5" t="n"/>
+      <c r="U31" s="9">
+        <f>Q31+R31+S31+T31</f>
+        <v/>
+      </c>
       <c r="V31" s="5" t="n"/>
       <c r="W31" s="5" t="n"/>
       <c r="X31" s="5" t="n"/>
@@ -14807,7 +14968,10 @@
         <f>Z31-V31-W31-X31</f>
         <v/>
       </c>
-      <c r="Z31" s="5" t="n"/>
+      <c r="Z31" s="9">
+        <f>V31+W31+X31+Y31</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -14850,19 +15014,19 @@
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="5" t="n"/>
       <c r="D33" s="5" t="n"/>
-      <c r="E33" s="9">
-        <f>F33-B33-C33-D33</f>
-        <v/>
-      </c>
-      <c r="F33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="9">
+        <f>B33+C33+D33+E33</f>
+        <v/>
+      </c>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="n"/>
-      <c r="J33" s="9">
-        <f>K33-G33-H33-I33</f>
-        <v/>
-      </c>
-      <c r="K33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="9">
+        <f>G33+H33+I33+J33</f>
+        <v/>
+      </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="5" t="n"/>
       <c r="N33" s="5" t="n"/>
@@ -14909,19 +15073,19 @@
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n"/>
       <c r="D34" s="5" t="n"/>
-      <c r="E34" s="9">
-        <f>F34-B34-C34-D34</f>
-        <v/>
-      </c>
-      <c r="F34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="9">
+        <f>B34+C34+D34+E34</f>
+        <v/>
+      </c>
       <c r="G34" s="5" t="n"/>
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="n"/>
-      <c r="J34" s="9">
-        <f>K34-G34-H34-I34</f>
-        <v/>
-      </c>
-      <c r="K34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="9">
+        <f>G34+H34+I34+J34</f>
+        <v/>
+      </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="5" t="n"/>
       <c r="N34" s="5" t="n"/>
@@ -14968,19 +15132,19 @@
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="5" t="n"/>
-      <c r="E35" s="9">
-        <f>F35-B35-C35-D35</f>
-        <v/>
-      </c>
-      <c r="F35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="9">
+        <f>B35+C35+D35+E35</f>
+        <v/>
+      </c>
       <c r="G35" s="5" t="n"/>
       <c r="H35" s="5" t="n"/>
       <c r="I35" s="5" t="n"/>
-      <c r="J35" s="9">
-        <f>K35-G35-H35-I35</f>
-        <v/>
-      </c>
-      <c r="K35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="9">
+        <f>G35+H35+I35+J35</f>
+        <v/>
+      </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="5" t="n"/>
       <c r="N35" s="5" t="n"/>
@@ -15027,19 +15191,19 @@
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="5" t="n"/>
       <c r="D36" s="5" t="n"/>
-      <c r="E36" s="9">
-        <f>F36-B36-C36-D36</f>
-        <v/>
-      </c>
-      <c r="F36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="9">
+        <f>B36+C36+D36+E36</f>
+        <v/>
+      </c>
       <c r="G36" s="5" t="n"/>
       <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="n"/>
-      <c r="J36" s="9">
-        <f>K36-G36-H36-I36</f>
-        <v/>
-      </c>
-      <c r="K36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="9">
+        <f>G36+H36+I36+J36</f>
+        <v/>
+      </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="5" t="n"/>
       <c r="N36" s="5" t="n"/>
@@ -15086,19 +15250,19 @@
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="n"/>
       <c r="D37" s="5" t="n"/>
-      <c r="E37" s="9">
-        <f>F37-B37-C37-D37</f>
-        <v/>
-      </c>
-      <c r="F37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="9">
+        <f>B37+C37+D37+E37</f>
+        <v/>
+      </c>
       <c r="G37" s="5" t="n"/>
       <c r="H37" s="5" t="n"/>
       <c r="I37" s="5" t="n"/>
-      <c r="J37" s="9">
-        <f>K37-G37-H37-I37</f>
-        <v/>
-      </c>
-      <c r="K37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="9">
+        <f>G37+H37+I37+J37</f>
+        <v/>
+      </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="5" t="n"/>
       <c r="N37" s="5" t="n"/>
@@ -15177,35 +15341,35 @@
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="5" t="n"/>
       <c r="D39" s="5" t="n"/>
-      <c r="E39" s="9">
-        <f>F39-B39-C39-D39</f>
-        <v/>
-      </c>
-      <c r="F39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="9">
+        <f>B39+C39+D39+E39</f>
+        <v/>
+      </c>
       <c r="G39" s="5" t="n"/>
       <c r="H39" s="5" t="n"/>
       <c r="I39" s="5" t="n"/>
-      <c r="J39" s="9">
-        <f>K39-G39-H39-I39</f>
-        <v/>
-      </c>
-      <c r="K39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="9">
+        <f>G39+H39+I39+J39</f>
+        <v/>
+      </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="5" t="n"/>
       <c r="N39" s="5" t="n"/>
-      <c r="O39" s="9">
-        <f>P39-L39-M39-N39</f>
-        <v/>
-      </c>
-      <c r="P39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="9">
+        <f>L39+M39+N39+O39</f>
+        <v/>
+      </c>
       <c r="Q39" s="5" t="n"/>
       <c r="R39" s="5" t="n"/>
       <c r="S39" s="5" t="n"/>
-      <c r="T39" s="9">
-        <f>U39-Q39-R39-S39</f>
-        <v/>
-      </c>
-      <c r="U39" s="5" t="n"/>
+      <c r="T39" s="5" t="n"/>
+      <c r="U39" s="9">
+        <f>Q39+R39+S39+T39</f>
+        <v/>
+      </c>
       <c r="V39" t="n">
         <v>789.301</v>
       </c>
@@ -15232,35 +15396,35 @@
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="5" t="n"/>
       <c r="D40" s="5" t="n"/>
-      <c r="E40" s="9">
-        <f>F40-B40-C40-D40</f>
-        <v/>
-      </c>
-      <c r="F40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="9">
+        <f>B40+C40+D40+E40</f>
+        <v/>
+      </c>
       <c r="G40" s="5" t="n"/>
       <c r="H40" s="5" t="n"/>
       <c r="I40" s="5" t="n"/>
-      <c r="J40" s="9">
-        <f>K40-G40-H40-I40</f>
-        <v/>
-      </c>
-      <c r="K40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="9">
+        <f>G40+H40+I40+J40</f>
+        <v/>
+      </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="5" t="n"/>
       <c r="N40" s="5" t="n"/>
-      <c r="O40" s="9">
-        <f>P40-L40-M40-N40</f>
-        <v/>
-      </c>
-      <c r="P40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="9">
+        <f>L40+M40+N40+O40</f>
+        <v/>
+      </c>
       <c r="Q40" s="5" t="n"/>
       <c r="R40" s="5" t="n"/>
       <c r="S40" s="5" t="n"/>
-      <c r="T40" s="9">
-        <f>U40-Q40-R40-S40</f>
-        <v/>
-      </c>
-      <c r="U40" s="5" t="n"/>
+      <c r="T40" s="5" t="n"/>
+      <c r="U40" s="9">
+        <f>Q40+R40+S40+T40</f>
+        <v/>
+      </c>
       <c r="V40" t="n">
         <v>0.857</v>
       </c>
@@ -15287,35 +15451,35 @@
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="n"/>
       <c r="D41" s="5" t="n"/>
-      <c r="E41" s="9">
-        <f>F41-B41-C41-D41</f>
-        <v/>
-      </c>
-      <c r="F41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="9">
+        <f>B41+C41+D41+E41</f>
+        <v/>
+      </c>
       <c r="G41" s="5" t="n"/>
       <c r="H41" s="5" t="n"/>
       <c r="I41" s="5" t="n"/>
-      <c r="J41" s="9">
-        <f>K41-G41-H41-I41</f>
-        <v/>
-      </c>
-      <c r="K41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="9">
+        <f>G41+H41+I41+J41</f>
+        <v/>
+      </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="5" t="n"/>
       <c r="N41" s="5" t="n"/>
-      <c r="O41" s="9">
-        <f>P41-L41-M41-N41</f>
-        <v/>
-      </c>
-      <c r="P41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="9">
+        <f>L41+M41+N41+O41</f>
+        <v/>
+      </c>
       <c r="Q41" s="5" t="n"/>
       <c r="R41" s="5" t="n"/>
       <c r="S41" s="5" t="n"/>
-      <c r="T41" s="9">
-        <f>U41-Q41-R41-S41</f>
-        <v/>
-      </c>
-      <c r="U41" s="5" t="n"/>
+      <c r="T41" s="5" t="n"/>
+      <c r="U41" s="9">
+        <f>Q41+R41+S41+T41</f>
+        <v/>
+      </c>
       <c r="V41" t="n">
         <v>332.62</v>
       </c>
@@ -15342,35 +15506,35 @@
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="5" t="n"/>
       <c r="D42" s="5" t="n"/>
-      <c r="E42" s="9">
-        <f>F42-B42-C42-D42</f>
-        <v/>
-      </c>
-      <c r="F42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="9">
+        <f>B42+C42+D42+E42</f>
+        <v/>
+      </c>
       <c r="G42" s="5" t="n"/>
       <c r="H42" s="5" t="n"/>
       <c r="I42" s="5" t="n"/>
-      <c r="J42" s="9">
-        <f>K42-G42-H42-I42</f>
-        <v/>
-      </c>
-      <c r="K42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="9">
+        <f>G42+H42+I42+J42</f>
+        <v/>
+      </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="5" t="n"/>
       <c r="N42" s="5" t="n"/>
-      <c r="O42" s="9">
-        <f>P42-L42-M42-N42</f>
-        <v/>
-      </c>
-      <c r="P42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="9">
+        <f>L42+M42+N42+O42</f>
+        <v/>
+      </c>
       <c r="Q42" s="5" t="n"/>
       <c r="R42" s="5" t="n"/>
       <c r="S42" s="5" t="n"/>
-      <c r="T42" s="9">
-        <f>U42-Q42-R42-S42</f>
-        <v/>
-      </c>
-      <c r="U42" s="5" t="n"/>
+      <c r="T42" s="5" t="n"/>
+      <c r="U42" s="9">
+        <f>Q42+R42+S42+T42</f>
+        <v/>
+      </c>
       <c r="V42" t="n">
         <v>193.859</v>
       </c>
@@ -15397,35 +15561,35 @@
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="5" t="n"/>
       <c r="D43" s="5" t="n"/>
-      <c r="E43" s="9">
-        <f>F43-B43-C43-D43</f>
-        <v/>
-      </c>
-      <c r="F43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="9">
+        <f>B43+C43+D43+E43</f>
+        <v/>
+      </c>
       <c r="G43" s="5" t="n"/>
       <c r="H43" s="5" t="n"/>
       <c r="I43" s="5" t="n"/>
-      <c r="J43" s="9">
-        <f>K43-G43-H43-I43</f>
-        <v/>
-      </c>
-      <c r="K43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="9">
+        <f>G43+H43+I43+J43</f>
+        <v/>
+      </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="5" t="n"/>
       <c r="N43" s="5" t="n"/>
-      <c r="O43" s="9">
-        <f>P43-L43-M43-N43</f>
-        <v/>
-      </c>
-      <c r="P43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="9">
+        <f>L43+M43+N43+O43</f>
+        <v/>
+      </c>
       <c r="Q43" s="5" t="n"/>
       <c r="R43" s="5" t="n"/>
       <c r="S43" s="5" t="n"/>
-      <c r="T43" s="9">
-        <f>U43-Q43-R43-S43</f>
-        <v/>
-      </c>
-      <c r="U43" s="5" t="n"/>
+      <c r="T43" s="5" t="n"/>
+      <c r="U43" s="9">
+        <f>Q43+R43+S43+T43</f>
+        <v/>
+      </c>
       <c r="V43" t="n">
         <v>193.859</v>
       </c>
@@ -15484,35 +15648,35 @@
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="5" t="n"/>
       <c r="D45" s="5" t="n"/>
-      <c r="E45" s="9">
-        <f>F45-B45-C45-D45</f>
-        <v/>
-      </c>
-      <c r="F45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="9">
+        <f>B45+C45+D45+E45</f>
+        <v/>
+      </c>
       <c r="G45" s="5" t="n"/>
       <c r="H45" s="5" t="n"/>
       <c r="I45" s="5" t="n"/>
-      <c r="J45" s="9">
-        <f>K45-G45-H45-I45</f>
-        <v/>
-      </c>
-      <c r="K45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="9">
+        <f>G45+H45+I45+J45</f>
+        <v/>
+      </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="5" t="n"/>
       <c r="N45" s="5" t="n"/>
-      <c r="O45" s="9">
-        <f>P45-L45-M45-N45</f>
-        <v/>
-      </c>
-      <c r="P45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="9">
+        <f>L45+M45+N45+O45</f>
+        <v/>
+      </c>
       <c r="Q45" s="5" t="n"/>
       <c r="R45" s="5" t="n"/>
       <c r="S45" s="5" t="n"/>
-      <c r="T45" s="9">
-        <f>U45-Q45-R45-S45</f>
-        <v/>
-      </c>
-      <c r="U45" s="5" t="n"/>
+      <c r="T45" s="5" t="n"/>
+      <c r="U45" s="9">
+        <f>Q45+R45+S45+T45</f>
+        <v/>
+      </c>
       <c r="V45" t="n">
         <v>659.954</v>
       </c>
@@ -15539,35 +15703,35 @@
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="5" t="n"/>
       <c r="D46" s="5" t="n"/>
-      <c r="E46" s="9">
-        <f>F46-B46-C46-D46</f>
-        <v/>
-      </c>
-      <c r="F46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="9">
+        <f>B46+C46+D46+E46</f>
+        <v/>
+      </c>
       <c r="G46" s="5" t="n"/>
       <c r="H46" s="5" t="n"/>
       <c r="I46" s="5" t="n"/>
-      <c r="J46" s="9">
-        <f>K46-G46-H46-I46</f>
-        <v/>
-      </c>
-      <c r="K46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="9">
+        <f>G46+H46+I46+J46</f>
+        <v/>
+      </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="5" t="n"/>
       <c r="N46" s="5" t="n"/>
-      <c r="O46" s="9">
-        <f>P46-L46-M46-N46</f>
-        <v/>
-      </c>
-      <c r="P46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="9">
+        <f>L46+M46+N46+O46</f>
+        <v/>
+      </c>
       <c r="Q46" s="5" t="n"/>
       <c r="R46" s="5" t="n"/>
       <c r="S46" s="5" t="n"/>
-      <c r="T46" s="9">
-        <f>U46-Q46-R46-S46</f>
-        <v/>
-      </c>
-      <c r="U46" s="5" t="n"/>
+      <c r="T46" s="5" t="n"/>
+      <c r="U46" s="9">
+        <f>Q46+R46+S46+T46</f>
+        <v/>
+      </c>
       <c r="V46" t="n">
         <v>4.999</v>
       </c>
@@ -15594,35 +15758,35 @@
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="5" t="n"/>
       <c r="D47" s="5" t="n"/>
-      <c r="E47" s="9">
-        <f>F47-B47-C47-D47</f>
-        <v/>
-      </c>
-      <c r="F47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="9">
+        <f>B47+C47+D47+E47</f>
+        <v/>
+      </c>
       <c r="G47" s="5" t="n"/>
       <c r="H47" s="5" t="n"/>
       <c r="I47" s="5" t="n"/>
-      <c r="J47" s="9">
-        <f>K47-G47-H47-I47</f>
-        <v/>
-      </c>
-      <c r="K47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="9">
+        <f>G47+H47+I47+J47</f>
+        <v/>
+      </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="5" t="n"/>
       <c r="N47" s="5" t="n"/>
-      <c r="O47" s="9">
-        <f>P47-L47-M47-N47</f>
-        <v/>
-      </c>
-      <c r="P47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="9">
+        <f>L47+M47+N47+O47</f>
+        <v/>
+      </c>
       <c r="Q47" s="5" t="n"/>
       <c r="R47" s="5" t="n"/>
       <c r="S47" s="5" t="n"/>
-      <c r="T47" s="9">
-        <f>U47-Q47-R47-S47</f>
-        <v/>
-      </c>
-      <c r="U47" s="5" t="n"/>
+      <c r="T47" s="5" t="n"/>
+      <c r="U47" s="9">
+        <f>Q47+R47+S47+T47</f>
+        <v/>
+      </c>
       <c r="V47" t="n">
         <v>188.579</v>
       </c>
@@ -15649,35 +15813,35 @@
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="5" t="n"/>
       <c r="D48" s="5" t="n"/>
-      <c r="E48" s="9">
-        <f>F48-B48-C48-D48</f>
-        <v/>
-      </c>
-      <c r="F48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="9">
+        <f>B48+C48+D48+E48</f>
+        <v/>
+      </c>
       <c r="G48" s="5" t="n"/>
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="5" t="n"/>
-      <c r="J48" s="9">
-        <f>K48-G48-H48-I48</f>
-        <v/>
-      </c>
-      <c r="K48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="9">
+        <f>G48+H48+I48+J48</f>
+        <v/>
+      </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="5" t="n"/>
       <c r="N48" s="5" t="n"/>
-      <c r="O48" s="9">
-        <f>P48-L48-M48-N48</f>
-        <v/>
-      </c>
-      <c r="P48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="9">
+        <f>L48+M48+N48+O48</f>
+        <v/>
+      </c>
       <c r="Q48" s="5" t="n"/>
       <c r="R48" s="5" t="n"/>
       <c r="S48" s="5" t="n"/>
-      <c r="T48" s="9">
-        <f>U48-Q48-R48-S48</f>
-        <v/>
-      </c>
-      <c r="U48" s="5" t="n"/>
+      <c r="T48" s="5" t="n"/>
+      <c r="U48" s="9">
+        <f>Q48+R48+S48+T48</f>
+        <v/>
+      </c>
       <c r="V48" t="n">
         <v>159.821</v>
       </c>
@@ -15704,35 +15868,35 @@
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="5" t="n"/>
       <c r="D49" s="5" t="n"/>
-      <c r="E49" s="9">
-        <f>F49-B49-C49-D49</f>
-        <v/>
-      </c>
-      <c r="F49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="9">
+        <f>B49+C49+D49+E49</f>
+        <v/>
+      </c>
       <c r="G49" s="5" t="n"/>
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="n"/>
-      <c r="J49" s="9">
-        <f>K49-G49-H49-I49</f>
-        <v/>
-      </c>
-      <c r="K49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="9">
+        <f>G49+H49+I49+J49</f>
+        <v/>
+      </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="5" t="n"/>
       <c r="N49" s="5" t="n"/>
-      <c r="O49" s="9">
-        <f>P49-L49-M49-N49</f>
-        <v/>
-      </c>
-      <c r="P49" s="5" t="n"/>
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="9">
+        <f>L49+M49+N49+O49</f>
+        <v/>
+      </c>
       <c r="Q49" s="5" t="n"/>
       <c r="R49" s="5" t="n"/>
       <c r="S49" s="5" t="n"/>
-      <c r="T49" s="9">
-        <f>U49-Q49-R49-S49</f>
-        <v/>
-      </c>
-      <c r="U49" s="5" t="n"/>
+      <c r="T49" s="5" t="n"/>
+      <c r="U49" s="9">
+        <f>Q49+R49+S49+T49</f>
+        <v/>
+      </c>
       <c r="V49" t="n">
         <v>159.817</v>
       </c>
@@ -15791,35 +15955,35 @@
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="5" t="n"/>
       <c r="D51" s="5" t="n"/>
-      <c r="E51" s="9">
-        <f>F51-B51-C51-D51</f>
-        <v/>
-      </c>
-      <c r="F51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="9">
+        <f>B51+C51+D51+E51</f>
+        <v/>
+      </c>
       <c r="G51" s="5" t="n"/>
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="n"/>
-      <c r="J51" s="9">
-        <f>K51-G51-H51-I51</f>
-        <v/>
-      </c>
-      <c r="K51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="9">
+        <f>G51+H51+I51+J51</f>
+        <v/>
+      </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="5" t="n"/>
       <c r="N51" s="5" t="n"/>
-      <c r="O51" s="9">
-        <f>P51-L51-M51-N51</f>
-        <v/>
-      </c>
-      <c r="P51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="9">
+        <f>L51+M51+N51+O51</f>
+        <v/>
+      </c>
       <c r="Q51" s="5" t="n"/>
       <c r="R51" s="5" t="n"/>
       <c r="S51" s="5" t="n"/>
-      <c r="T51" s="9">
-        <f>U51-Q51-R51-S51</f>
-        <v/>
-      </c>
-      <c r="U51" s="5" t="n"/>
+      <c r="T51" s="5" t="n"/>
+      <c r="U51" s="9">
+        <f>Q51+R51+S51+T51</f>
+        <v/>
+      </c>
       <c r="V51" t="n">
         <v>2649.224</v>
       </c>
@@ -15846,35 +16010,35 @@
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="5" t="n"/>
       <c r="D52" s="5" t="n"/>
-      <c r="E52" s="9">
-        <f>F52-B52-C52-D52</f>
-        <v/>
-      </c>
-      <c r="F52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="9">
+        <f>B52+C52+D52+E52</f>
+        <v/>
+      </c>
       <c r="G52" s="5" t="n"/>
       <c r="H52" s="5" t="n"/>
       <c r="I52" s="5" t="n"/>
-      <c r="J52" s="9">
-        <f>K52-G52-H52-I52</f>
-        <v/>
-      </c>
-      <c r="K52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="9">
+        <f>G52+H52+I52+J52</f>
+        <v/>
+      </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="5" t="n"/>
       <c r="N52" s="5" t="n"/>
-      <c r="O52" s="9">
-        <f>P52-L52-M52-N52</f>
-        <v/>
-      </c>
-      <c r="P52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="9">
+        <f>L52+M52+N52+O52</f>
+        <v/>
+      </c>
       <c r="Q52" s="5" t="n"/>
       <c r="R52" s="5" t="n"/>
       <c r="S52" s="5" t="n"/>
-      <c r="T52" s="9">
-        <f>U52-Q52-R52-S52</f>
-        <v/>
-      </c>
-      <c r="U52" s="5" t="n"/>
+      <c r="T52" s="5" t="n"/>
+      <c r="U52" s="9">
+        <f>Q52+R52+S52+T52</f>
+        <v/>
+      </c>
       <c r="V52" t="n">
         <v>27.131</v>
       </c>
@@ -15901,35 +16065,35 @@
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="5" t="n"/>
       <c r="D53" s="5" t="n"/>
-      <c r="E53" s="9">
-        <f>F53-B53-C53-D53</f>
-        <v/>
-      </c>
-      <c r="F53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="9">
+        <f>B53+C53+D53+E53</f>
+        <v/>
+      </c>
       <c r="G53" s="5" t="n"/>
       <c r="H53" s="5" t="n"/>
       <c r="I53" s="5" t="n"/>
-      <c r="J53" s="9">
-        <f>K53-G53-H53-I53</f>
-        <v/>
-      </c>
-      <c r="K53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="9">
+        <f>G53+H53+I53+J53</f>
+        <v/>
+      </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="5" t="n"/>
       <c r="N53" s="5" t="n"/>
-      <c r="O53" s="9">
-        <f>P53-L53-M53-N53</f>
-        <v/>
-      </c>
-      <c r="P53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="9">
+        <f>L53+M53+N53+O53</f>
+        <v/>
+      </c>
       <c r="Q53" s="5" t="n"/>
       <c r="R53" s="5" t="n"/>
       <c r="S53" s="5" t="n"/>
-      <c r="T53" s="9">
-        <f>U53-Q53-R53-S53</f>
-        <v/>
-      </c>
-      <c r="U53" s="5" t="n"/>
+      <c r="T53" s="5" t="n"/>
+      <c r="U53" s="9">
+        <f>Q53+R53+S53+T53</f>
+        <v/>
+      </c>
       <c r="V53" t="n">
         <v>1582.956</v>
       </c>
@@ -15956,35 +16120,35 @@
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="5" t="n"/>
       <c r="D54" s="5" t="n"/>
-      <c r="E54" s="9">
-        <f>F54-B54-C54-D54</f>
-        <v/>
-      </c>
-      <c r="F54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="9">
+        <f>B54+C54+D54+E54</f>
+        <v/>
+      </c>
       <c r="G54" s="5" t="n"/>
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="n"/>
-      <c r="J54" s="9">
-        <f>K54-G54-H54-I54</f>
-        <v/>
-      </c>
-      <c r="K54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="9">
+        <f>G54+H54+I54+J54</f>
+        <v/>
+      </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="5" t="n"/>
       <c r="N54" s="5" t="n"/>
-      <c r="O54" s="9">
-        <f>P54-L54-M54-N54</f>
-        <v/>
-      </c>
-      <c r="P54" s="5" t="n"/>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="9">
+        <f>L54+M54+N54+O54</f>
+        <v/>
+      </c>
       <c r="Q54" s="5" t="n"/>
       <c r="R54" s="5" t="n"/>
       <c r="S54" s="5" t="n"/>
-      <c r="T54" s="9">
-        <f>U54-Q54-R54-S54</f>
-        <v/>
-      </c>
-      <c r="U54" s="5" t="n"/>
+      <c r="T54" s="5" t="n"/>
+      <c r="U54" s="9">
+        <f>Q54+R54+S54+T54</f>
+        <v/>
+      </c>
       <c r="V54" t="n">
         <v>175.544</v>
       </c>
@@ -16011,35 +16175,35 @@
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="5" t="n"/>
       <c r="D55" s="5" t="n"/>
-      <c r="E55" s="9">
-        <f>F55-B55-C55-D55</f>
-        <v/>
-      </c>
-      <c r="F55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="9">
+        <f>B55+C55+D55+E55</f>
+        <v/>
+      </c>
       <c r="G55" s="5" t="n"/>
       <c r="H55" s="5" t="n"/>
       <c r="I55" s="5" t="n"/>
-      <c r="J55" s="9">
-        <f>K55-G55-H55-I55</f>
-        <v/>
-      </c>
-      <c r="K55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="9">
+        <f>G55+H55+I55+J55</f>
+        <v/>
+      </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="5" t="n"/>
       <c r="N55" s="5" t="n"/>
-      <c r="O55" s="9">
-        <f>P55-L55-M55-N55</f>
-        <v/>
-      </c>
-      <c r="P55" s="5" t="n"/>
+      <c r="O55" s="5" t="n"/>
+      <c r="P55" s="9">
+        <f>L55+M55+N55+O55</f>
+        <v/>
+      </c>
       <c r="Q55" s="5" t="n"/>
       <c r="R55" s="5" t="n"/>
       <c r="S55" s="5" t="n"/>
-      <c r="T55" s="9">
-        <f>U55-Q55-R55-S55</f>
-        <v/>
-      </c>
-      <c r="U55" s="5" t="n"/>
+      <c r="T55" s="5" t="n"/>
+      <c r="U55" s="9">
+        <f>Q55+R55+S55+T55</f>
+        <v/>
+      </c>
       <c r="V55" s="5" t="n"/>
       <c r="W55" s="5" t="n"/>
       <c r="X55" s="5" t="n"/>
@@ -16047,7 +16211,10 @@
         <f>Z55-V55-W55-X55</f>
         <v/>
       </c>
-      <c r="Z55" s="5" t="n"/>
+      <c r="Z55" s="9">
+        <f>V55+W55+X55+Y55</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -16090,35 +16257,35 @@
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="5" t="n"/>
       <c r="D57" s="5" t="n"/>
-      <c r="E57" s="9">
-        <f>F57-B57-C57-D57</f>
-        <v/>
-      </c>
-      <c r="F57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="9">
+        <f>B57+C57+D57+E57</f>
+        <v/>
+      </c>
       <c r="G57" s="5" t="n"/>
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="n"/>
-      <c r="J57" s="9">
-        <f>K57-G57-H57-I57</f>
-        <v/>
-      </c>
-      <c r="K57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="9">
+        <f>G57+H57+I57+J57</f>
+        <v/>
+      </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="5" t="n"/>
       <c r="N57" s="5" t="n"/>
-      <c r="O57" s="9">
-        <f>P57-L57-M57-N57</f>
-        <v/>
-      </c>
-      <c r="P57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="9">
+        <f>L57+M57+N57+O57</f>
+        <v/>
+      </c>
       <c r="Q57" s="5" t="n"/>
       <c r="R57" s="5" t="n"/>
       <c r="S57" s="5" t="n"/>
-      <c r="T57" s="9">
-        <f>U57-Q57-R57-S57</f>
-        <v/>
-      </c>
-      <c r="U57" s="5" t="n"/>
+      <c r="T57" s="5" t="n"/>
+      <c r="U57" s="9">
+        <f>Q57+R57+S57+T57</f>
+        <v/>
+      </c>
       <c r="V57" t="n">
         <v>427.929</v>
       </c>
@@ -16145,35 +16312,35 @@
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="5" t="n"/>
       <c r="D58" s="5" t="n"/>
-      <c r="E58" s="9">
-        <f>F58-B58-C58-D58</f>
-        <v/>
-      </c>
-      <c r="F58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="9">
+        <f>B58+C58+D58+E58</f>
+        <v/>
+      </c>
       <c r="G58" s="5" t="n"/>
       <c r="H58" s="5" t="n"/>
       <c r="I58" s="5" t="n"/>
-      <c r="J58" s="9">
-        <f>K58-G58-H58-I58</f>
-        <v/>
-      </c>
-      <c r="K58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="9">
+        <f>G58+H58+I58+J58</f>
+        <v/>
+      </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="5" t="n"/>
       <c r="N58" s="5" t="n"/>
-      <c r="O58" s="9">
-        <f>P58-L58-M58-N58</f>
-        <v/>
-      </c>
-      <c r="P58" s="5" t="n"/>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="9">
+        <f>L58+M58+N58+O58</f>
+        <v/>
+      </c>
       <c r="Q58" s="5" t="n"/>
       <c r="R58" s="5" t="n"/>
       <c r="S58" s="5" t="n"/>
-      <c r="T58" s="9">
-        <f>U58-Q58-R58-S58</f>
-        <v/>
-      </c>
-      <c r="U58" s="5" t="n"/>
+      <c r="T58" s="5" t="n"/>
+      <c r="U58" s="9">
+        <f>Q58+R58+S58+T58</f>
+        <v/>
+      </c>
       <c r="V58" t="n">
         <v>15.045</v>
       </c>
@@ -16200,35 +16367,35 @@
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="5" t="n"/>
       <c r="D59" s="5" t="n"/>
-      <c r="E59" s="9">
-        <f>F59-B59-C59-D59</f>
-        <v/>
-      </c>
-      <c r="F59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="9">
+        <f>B59+C59+D59+E59</f>
+        <v/>
+      </c>
       <c r="G59" s="5" t="n"/>
       <c r="H59" s="5" t="n"/>
       <c r="I59" s="5" t="n"/>
-      <c r="J59" s="9">
-        <f>K59-G59-H59-I59</f>
-        <v/>
-      </c>
-      <c r="K59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="9">
+        <f>G59+H59+I59+J59</f>
+        <v/>
+      </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="5" t="n"/>
       <c r="N59" s="5" t="n"/>
-      <c r="O59" s="9">
-        <f>P59-L59-M59-N59</f>
-        <v/>
-      </c>
-      <c r="P59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="9">
+        <f>L59+M59+N59+O59</f>
+        <v/>
+      </c>
       <c r="Q59" s="5" t="n"/>
       <c r="R59" s="5" t="n"/>
       <c r="S59" s="5" t="n"/>
-      <c r="T59" s="9">
-        <f>U59-Q59-R59-S59</f>
-        <v/>
-      </c>
-      <c r="U59" s="5" t="n"/>
+      <c r="T59" s="5" t="n"/>
+      <c r="U59" s="9">
+        <f>Q59+R59+S59+T59</f>
+        <v/>
+      </c>
       <c r="V59" t="n">
         <v>218.02</v>
       </c>
@@ -16255,35 +16422,35 @@
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="5" t="n"/>
       <c r="D60" s="5" t="n"/>
-      <c r="E60" s="9">
-        <f>F60-B60-C60-D60</f>
-        <v/>
-      </c>
-      <c r="F60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="9">
+        <f>B60+C60+D60+E60</f>
+        <v/>
+      </c>
       <c r="G60" s="5" t="n"/>
       <c r="H60" s="5" t="n"/>
       <c r="I60" s="5" t="n"/>
-      <c r="J60" s="9">
-        <f>K60-G60-H60-I60</f>
-        <v/>
-      </c>
-      <c r="K60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="9">
+        <f>G60+H60+I60+J60</f>
+        <v/>
+      </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="5" t="n"/>
       <c r="N60" s="5" t="n"/>
-      <c r="O60" s="9">
-        <f>P60-L60-M60-N60</f>
-        <v/>
-      </c>
-      <c r="P60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="9">
+        <f>L60+M60+N60+O60</f>
+        <v/>
+      </c>
       <c r="Q60" s="5" t="n"/>
       <c r="R60" s="5" t="n"/>
       <c r="S60" s="5" t="n"/>
-      <c r="T60" s="9">
-        <f>U60-Q60-R60-S60</f>
-        <v/>
-      </c>
-      <c r="U60" s="5" t="n"/>
+      <c r="T60" s="5" t="n"/>
+      <c r="U60" s="9">
+        <f>Q60+R60+S60+T60</f>
+        <v/>
+      </c>
       <c r="V60" t="n">
         <v>42.867</v>
       </c>
@@ -16310,35 +16477,35 @@
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="5" t="n"/>
       <c r="D61" s="5" t="n"/>
-      <c r="E61" s="9">
-        <f>F61-B61-C61-D61</f>
-        <v/>
-      </c>
-      <c r="F61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="9">
+        <f>B61+C61+D61+E61</f>
+        <v/>
+      </c>
       <c r="G61" s="5" t="n"/>
       <c r="H61" s="5" t="n"/>
       <c r="I61" s="5" t="n"/>
-      <c r="J61" s="9">
-        <f>K61-G61-H61-I61</f>
-        <v/>
-      </c>
-      <c r="K61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="9">
+        <f>G61+H61+I61+J61</f>
+        <v/>
+      </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="5" t="n"/>
       <c r="N61" s="5" t="n"/>
-      <c r="O61" s="9">
-        <f>P61-L61-M61-N61</f>
-        <v/>
-      </c>
-      <c r="P61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="9">
+        <f>L61+M61+N61+O61</f>
+        <v/>
+      </c>
       <c r="Q61" s="5" t="n"/>
       <c r="R61" s="5" t="n"/>
       <c r="S61" s="5" t="n"/>
-      <c r="T61" s="9">
-        <f>U61-Q61-R61-S61</f>
-        <v/>
-      </c>
-      <c r="U61" s="5" t="n"/>
+      <c r="T61" s="5" t="n"/>
+      <c r="U61" s="9">
+        <f>Q61+R61+S61+T61</f>
+        <v/>
+      </c>
       <c r="V61" t="n">
         <v>42.867</v>
       </c>
@@ -18311,22 +18478,54 @@
           <t>ลูกหนี้การค้า</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-      <c r="P31" s="5" t="n"/>
-      <c r="Q31" s="5" t="n"/>
+      <c r="B31" t="n">
+        <v>3.025</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4.021</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4.634</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5.573</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5.767</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6.469</v>
+      </c>
+      <c r="H31" t="n">
+        <v>9.369</v>
+      </c>
+      <c r="I31" t="n">
+        <v>12.364</v>
+      </c>
+      <c r="J31" t="n">
+        <v>10.382</v>
+      </c>
+      <c r="K31" t="n">
+        <v>11.744</v>
+      </c>
+      <c r="L31" t="n">
+        <v>11.053</v>
+      </c>
+      <c r="M31" t="n">
+        <v>12.165</v>
+      </c>
+      <c r="N31" t="n">
+        <v>12.261</v>
+      </c>
+      <c r="O31" t="n">
+        <v>18.823</v>
+      </c>
+      <c r="P31" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>15.883</v>
+      </c>
       <c r="R31" t="n">
         <v>13.217</v>
       </c>
@@ -18349,22 +18548,54 @@
           <t>สินค้าคงเหลือ</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-      <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="5" t="n"/>
+      <c r="B32" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.243</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.217</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.039</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.112</v>
+      </c>
       <c r="R32" t="n">
         <v>1.626</v>
       </c>
@@ -18387,22 +18618,54 @@
           <t>เจ้าหนี้การค้า</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-      <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="5" t="n"/>
+      <c r="B33" t="n">
+        <v>13.798</v>
+      </c>
+      <c r="C33" t="n">
+        <v>13.426</v>
+      </c>
+      <c r="D33" t="n">
+        <v>9.601000000000001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9.201000000000001</v>
+      </c>
+      <c r="F33" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="G33" t="n">
+        <v>16.715</v>
+      </c>
+      <c r="H33" t="n">
+        <v>22.378</v>
+      </c>
+      <c r="I33" t="n">
+        <v>32.985</v>
+      </c>
+      <c r="J33" t="n">
+        <v>32.359</v>
+      </c>
+      <c r="K33" t="n">
+        <v>26.155</v>
+      </c>
+      <c r="L33" t="n">
+        <v>26.195</v>
+      </c>
+      <c r="M33" t="n">
+        <v>26.106</v>
+      </c>
+      <c r="N33" t="n">
+        <v>27.752</v>
+      </c>
+      <c r="O33" t="n">
+        <v>31.306</v>
+      </c>
+      <c r="P33" t="n">
+        <v>36.151</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>34.527</v>
+      </c>
       <c r="R33" t="n">
         <v>40.06</v>
       </c>
@@ -18425,22 +18688,54 @@
           <t>สินทรัพย์รวม</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="5" t="n"/>
-      <c r="P34" s="5" t="n"/>
-      <c r="Q34" s="5" t="n"/>
+      <c r="B34" t="n">
+        <v>848.837</v>
+      </c>
+      <c r="C34" t="n">
+        <v>871.25</v>
+      </c>
+      <c r="D34" t="n">
+        <v>844.104</v>
+      </c>
+      <c r="E34" t="n">
+        <v>855.513</v>
+      </c>
+      <c r="F34" t="n">
+        <v>835.4450000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>808.893</v>
+      </c>
+      <c r="H34" t="n">
+        <v>801.741</v>
+      </c>
+      <c r="I34" t="n">
+        <v>807.069</v>
+      </c>
+      <c r="J34" t="n">
+        <v>811.325</v>
+      </c>
+      <c r="K34" t="n">
+        <v>804.05</v>
+      </c>
+      <c r="L34" t="n">
+        <v>747.3579999999999</v>
+      </c>
+      <c r="M34" t="n">
+        <v>754.702</v>
+      </c>
+      <c r="N34" t="n">
+        <v>759.002</v>
+      </c>
+      <c r="O34" t="n">
+        <v>722.818</v>
+      </c>
+      <c r="P34" t="n">
+        <v>698.999</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>699.754</v>
+      </c>
       <c r="R34" t="n">
         <v>691.668</v>
       </c>
@@ -18463,22 +18758,54 @@
           <t>ส่วนของเจ้าของรวม</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="n"/>
-      <c r="O35" s="5" t="n"/>
-      <c r="P35" s="5" t="n"/>
-      <c r="Q35" s="5" t="n"/>
+      <c r="B35" t="n">
+        <v>439.059</v>
+      </c>
+      <c r="C35" t="n">
+        <v>422.571</v>
+      </c>
+      <c r="D35" t="n">
+        <v>399.987</v>
+      </c>
+      <c r="E35" t="n">
+        <v>412.545</v>
+      </c>
+      <c r="F35" t="n">
+        <v>390.217</v>
+      </c>
+      <c r="G35" t="n">
+        <v>359.923</v>
+      </c>
+      <c r="H35" t="n">
+        <v>347.873</v>
+      </c>
+      <c r="I35" t="n">
+        <v>343.37</v>
+      </c>
+      <c r="J35" t="n">
+        <v>353.04</v>
+      </c>
+      <c r="K35" t="n">
+        <v>359.884</v>
+      </c>
+      <c r="L35" t="n">
+        <v>361.079</v>
+      </c>
+      <c r="M35" t="n">
+        <v>376.451</v>
+      </c>
+      <c r="N35" t="n">
+        <v>387.724</v>
+      </c>
+      <c r="O35" t="n">
+        <v>401.518</v>
+      </c>
+      <c r="P35" t="n">
+        <v>408.4</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>426.595</v>
+      </c>
       <c r="R35" t="n">
         <v>438.545</v>
       </c>
@@ -18501,22 +18828,54 @@
           <t>หนี้สินรวม</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="n"/>
-      <c r="O36" s="5" t="n"/>
-      <c r="P36" s="5" t="n"/>
-      <c r="Q36" s="5" t="n"/>
+      <c r="B36" t="n">
+        <v>409.778</v>
+      </c>
+      <c r="C36" t="n">
+        <v>448.679</v>
+      </c>
+      <c r="D36" t="n">
+        <v>444.117</v>
+      </c>
+      <c r="E36" t="n">
+        <v>442.968</v>
+      </c>
+      <c r="F36" t="n">
+        <v>445.228</v>
+      </c>
+      <c r="G36" t="n">
+        <v>448.969</v>
+      </c>
+      <c r="H36" t="n">
+        <v>453.868</v>
+      </c>
+      <c r="I36" t="n">
+        <v>463.699</v>
+      </c>
+      <c r="J36" t="n">
+        <v>458.286</v>
+      </c>
+      <c r="K36" t="n">
+        <v>444.166</v>
+      </c>
+      <c r="L36" t="n">
+        <v>386.279</v>
+      </c>
+      <c r="M36" t="n">
+        <v>378.251</v>
+      </c>
+      <c r="N36" t="n">
+        <v>371.278</v>
+      </c>
+      <c r="O36" t="n">
+        <v>321.299</v>
+      </c>
+      <c r="P36" t="n">
+        <v>290.599</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>273.159</v>
+      </c>
       <c r="R36" t="n">
         <v>253.123</v>
       </c>
@@ -19995,7 +20354,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=20, MANRIN=4, MINT=6, OHTL=4, SHANG=4, SHR=4, VRANDA=4</t>
+          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=20, MANRIN=17, MINT=6, OHTL=4, SHANG=4, SHR=4, VRANDA=4</t>
         </is>
       </c>
     </row>

--- a/tour-finance/output/TOUR_all_linked.xlsx
+++ b/tour-finance/output/TOUR_all_linked.xlsx
@@ -15011,25 +15011,47 @@
           <t>รายได้รวม</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="9">
-        <f>B33+C33+D33+E33</f>
-        <v/>
-      </c>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="9">
-        <f>G33+H33+I33+J33</f>
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
+      <c r="B33" t="n">
+        <v>12653.858</v>
+      </c>
+      <c r="C33" t="n">
+        <v>15840.486</v>
+      </c>
+      <c r="D33" t="n">
+        <v>20789.337</v>
+      </c>
+      <c r="E33" s="9">
+        <f>F33-B33-C33-D33</f>
+        <v/>
+      </c>
+      <c r="F33" t="n">
+        <v>76211.261</v>
+      </c>
+      <c r="G33" t="n">
+        <v>20672.252</v>
+      </c>
+      <c r="H33" t="n">
+        <v>32348.359</v>
+      </c>
+      <c r="I33" t="n">
+        <v>35153.927</v>
+      </c>
+      <c r="J33" s="9">
+        <f>K33-G33-H33-I33</f>
+        <v/>
+      </c>
+      <c r="K33" t="n">
+        <v>124205.848</v>
+      </c>
+      <c r="L33" t="n">
+        <v>32229.34</v>
+      </c>
+      <c r="M33" t="n">
+        <v>40588.347</v>
+      </c>
+      <c r="N33" t="n">
+        <v>39840.815</v>
+      </c>
       <c r="O33" s="9">
         <f>P33-L33-M33-N33</f>
         <v/>
@@ -15037,9 +15059,15 @@
       <c r="P33" t="n">
         <v>153049.242</v>
       </c>
-      <c r="Q33" s="5" t="n"/>
-      <c r="R33" s="5" t="n"/>
-      <c r="S33" s="5" t="n"/>
+      <c r="Q33" t="n">
+        <v>37818.351</v>
+      </c>
+      <c r="R33" t="n">
+        <v>44303.008</v>
+      </c>
+      <c r="S33" t="n">
+        <v>41612.614</v>
+      </c>
       <c r="T33" s="9">
         <f>U33-Q33-R33-S33</f>
         <v/>
@@ -15070,25 +15098,47 @@
           <t>รายได้อื่น</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="9">
-        <f>B34+C34+D34+E34</f>
-        <v/>
-      </c>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="9">
-        <f>G34+H34+I34+J34</f>
-        <v/>
-      </c>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="n"/>
+      <c r="B34" t="n">
+        <v>469.091</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1997.136</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1213.841</v>
+      </c>
+      <c r="E34" s="9">
+        <f>F34-B34-C34-D34</f>
+        <v/>
+      </c>
+      <c r="F34" t="n">
+        <v>6096.415</v>
+      </c>
+      <c r="G34" t="n">
+        <v>832.631</v>
+      </c>
+      <c r="H34" t="n">
+        <v>720.23</v>
+      </c>
+      <c r="I34" t="n">
+        <v>985.7</v>
+      </c>
+      <c r="J34" s="9">
+        <f>K34-G34-H34-I34</f>
+        <v/>
+      </c>
+      <c r="K34" t="n">
+        <v>3411.985</v>
+      </c>
+      <c r="L34" t="n">
+        <v>694.83</v>
+      </c>
+      <c r="M34" t="n">
+        <v>487.442</v>
+      </c>
+      <c r="N34" t="n">
+        <v>563.386</v>
+      </c>
       <c r="O34" s="9">
         <f>P34-L34-M34-N34</f>
         <v/>
@@ -15096,9 +15146,15 @@
       <c r="P34" t="n">
         <v>2344.767</v>
       </c>
-      <c r="Q34" s="5" t="n"/>
-      <c r="R34" s="5" t="n"/>
-      <c r="S34" s="5" t="n"/>
+      <c r="Q34" t="n">
+        <v>950.347</v>
+      </c>
+      <c r="R34" t="n">
+        <v>257.577</v>
+      </c>
+      <c r="S34" t="n">
+        <v>693.591</v>
+      </c>
       <c r="T34" s="9">
         <f>U34-Q34-R34-S34</f>
         <v/>
@@ -15129,25 +15185,47 @@
           <t>ต้นทุนขาย (จริง)</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="9">
-        <f>B35+C35+D35+E35</f>
-        <v/>
-      </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="9">
-        <f>G35+H35+I35+J35</f>
-        <v/>
-      </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="n"/>
+      <c r="B35" t="n">
+        <v>8670.877</v>
+      </c>
+      <c r="C35" t="n">
+        <v>9770.642</v>
+      </c>
+      <c r="D35" t="n">
+        <v>11835.953</v>
+      </c>
+      <c r="E35" s="9">
+        <f>F35-B35-C35-D35</f>
+        <v/>
+      </c>
+      <c r="F35" t="n">
+        <v>42471.697</v>
+      </c>
+      <c r="G35" t="n">
+        <v>13113.487</v>
+      </c>
+      <c r="H35" t="n">
+        <v>16080.254</v>
+      </c>
+      <c r="I35" t="n">
+        <v>17222.59</v>
+      </c>
+      <c r="J35" s="9">
+        <f>K35-G35-H35-I35</f>
+        <v/>
+      </c>
+      <c r="K35" t="n">
+        <v>63827.792</v>
+      </c>
+      <c r="L35" t="n">
+        <v>17326.308</v>
+      </c>
+      <c r="M35" t="n">
+        <v>19634.453</v>
+      </c>
+      <c r="N35" t="n">
+        <v>19633.64</v>
+      </c>
       <c r="O35" s="9">
         <f>P35-L35-M35-N35</f>
         <v/>
@@ -15155,9 +15233,15 @@
       <c r="P35" t="n">
         <v>78150.469</v>
       </c>
-      <c r="Q35" s="5" t="n"/>
-      <c r="R35" s="5" t="n"/>
-      <c r="S35" s="5" t="n"/>
+      <c r="Q35" t="n">
+        <v>20253.5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>22584.012</v>
+      </c>
+      <c r="S35" t="n">
+        <v>21452.758</v>
+      </c>
       <c r="T35" s="9">
         <f>U35-Q35-R35-S35</f>
         <v/>
@@ -15188,25 +15272,47 @@
           <t>กำไรสุทธิ (รวม)</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="9">
-        <f>B36+C36+D36+E36</f>
-        <v/>
-      </c>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="9">
-        <f>G36+H36+I36+J36</f>
-        <v/>
-      </c>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="n"/>
+      <c r="B36" t="n">
+        <v>-7798.673</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-4188.238</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-551.893</v>
+      </c>
+      <c r="E36" s="9">
+        <f>F36-B36-C36-D36</f>
+        <v/>
+      </c>
+      <c r="F36" t="n">
+        <v>-14175.37</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-4067.712</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1701.487</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4775.446</v>
+      </c>
+      <c r="J36" s="9">
+        <f>K36-G36-H36-I36</f>
+        <v/>
+      </c>
+      <c r="K36" t="n">
+        <v>4522.68</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-940.597</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3490.163</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2323.736</v>
+      </c>
       <c r="O36" s="9">
         <f>P36-L36-M36-N36</f>
         <v/>
@@ -15214,9 +15320,15 @@
       <c r="P36" t="n">
         <v>6087.974</v>
       </c>
-      <c r="Q36" s="5" t="n"/>
-      <c r="R36" s="5" t="n"/>
-      <c r="S36" s="5" t="n"/>
+      <c r="Q36" t="n">
+        <v>1288.472</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3031.497</v>
+      </c>
+      <c r="S36" t="n">
+        <v>361.424</v>
+      </c>
       <c r="T36" s="9">
         <f>U36-Q36-R36-S36</f>
         <v/>
@@ -15247,25 +15359,47 @@
           <t>กำไรสุทธิ (ส่วนแม่)</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="9">
-        <f>B37+C37+D37+E37</f>
-        <v/>
-      </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="9">
-        <f>G37+H37+I37+J37</f>
-        <v/>
-      </c>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="5" t="n"/>
+      <c r="B37" t="n">
+        <v>-7249.723</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-3923.912</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-435.558</v>
+      </c>
+      <c r="E37" s="9">
+        <f>F37-B37-C37-D37</f>
+        <v/>
+      </c>
+      <c r="F37" t="n">
+        <v>-13166.508</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-3793.733</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1561.499</v>
+      </c>
+      <c r="I37" t="n">
+        <v>4607.942</v>
+      </c>
+      <c r="J37" s="9">
+        <f>K37-G37-H37-I37</f>
+        <v/>
+      </c>
+      <c r="K37" t="n">
+        <v>4286.373</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-975.899</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3255.129</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2143.757</v>
+      </c>
       <c r="O37" s="9">
         <f>P37-L37-M37-N37</f>
         <v/>
@@ -15273,9 +15407,15 @@
       <c r="P37" t="n">
         <v>5407.055</v>
       </c>
-      <c r="Q37" s="5" t="n"/>
-      <c r="R37" s="5" t="n"/>
-      <c r="S37" s="5" t="n"/>
+      <c r="Q37" t="n">
+        <v>1146.079</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2823.217</v>
+      </c>
+      <c r="S37" t="n">
+        <v>149.396</v>
+      </c>
       <c r="T37" s="9">
         <f>U37-Q37-R37-S37</f>
         <v/>
@@ -18926,26 +19066,54 @@
           <t>ลูกหนี้การค้า</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
+      <c r="B38" t="n">
+        <v>12285.894</v>
+      </c>
+      <c r="C38" t="n">
+        <v>12560.738</v>
+      </c>
+      <c r="D38" t="n">
+        <v>12245.698</v>
+      </c>
+      <c r="E38" t="n">
+        <v>14057.042</v>
+      </c>
+      <c r="F38" t="n">
+        <v>14637.995</v>
+      </c>
+      <c r="G38" t="n">
+        <v>18889.532</v>
+      </c>
+      <c r="H38" t="n">
+        <v>17198.61</v>
+      </c>
+      <c r="I38" t="n">
+        <v>18590.806</v>
+      </c>
       <c r="J38" t="n">
         <v>17052.269</v>
       </c>
-      <c r="K38" s="5" t="n"/>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="5" t="n"/>
+      <c r="K38" t="n">
+        <v>17614.873</v>
+      </c>
+      <c r="L38" t="n">
+        <v>19429.147</v>
+      </c>
+      <c r="M38" t="n">
+        <v>19843.861</v>
+      </c>
       <c r="N38" t="n">
         <v>18487.349</v>
       </c>
-      <c r="O38" s="5" t="n"/>
-      <c r="P38" s="5" t="n"/>
-      <c r="Q38" s="5" t="n"/>
+      <c r="O38" t="n">
+        <v>19703.261</v>
+      </c>
+      <c r="P38" t="n">
+        <v>20247.792</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>18407.006</v>
+      </c>
       <c r="R38" t="n">
         <v>13970.341</v>
       </c>
@@ -18968,26 +19136,54 @@
           <t>สินค้าคงเหลือ</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
+      <c r="B39" t="n">
+        <v>3682.608</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3667.674</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3636.485</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3777.876</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3490.183</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3671.525</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3982.958</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3907.026</v>
+      </c>
       <c r="J39" t="n">
         <v>3909.198</v>
       </c>
-      <c r="K39" s="5" t="n"/>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
+      <c r="K39" t="n">
+        <v>3817.805</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3981.635</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3875.773</v>
+      </c>
       <c r="N39" t="n">
         <v>3820.416</v>
       </c>
-      <c r="O39" s="5" t="n"/>
-      <c r="P39" s="5" t="n"/>
-      <c r="Q39" s="5" t="n"/>
+      <c r="O39" t="n">
+        <v>3756.272</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3907.044</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3908.265</v>
+      </c>
       <c r="R39" t="n">
         <v>3917.636</v>
       </c>
@@ -19010,26 +19206,54 @@
           <t>เจ้าหนี้การค้า</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
+      <c r="B40" t="n">
+        <v>15310.438</v>
+      </c>
+      <c r="C40" t="n">
+        <v>15245.522</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15838.852</v>
+      </c>
+      <c r="E40" t="n">
+        <v>17618.801</v>
+      </c>
+      <c r="F40" t="n">
+        <v>18393.64</v>
+      </c>
+      <c r="G40" t="n">
+        <v>18781.601</v>
+      </c>
+      <c r="H40" t="n">
+        <v>19282.544</v>
+      </c>
+      <c r="I40" t="n">
+        <v>20414.772</v>
+      </c>
       <c r="J40" t="n">
         <v>21806.521</v>
       </c>
-      <c r="K40" s="5" t="n"/>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
+      <c r="K40" t="n">
+        <v>21635.269</v>
+      </c>
+      <c r="L40" t="n">
+        <v>24038.032</v>
+      </c>
+      <c r="M40" t="n">
+        <v>23542.235</v>
+      </c>
       <c r="N40" t="n">
         <v>24953.308</v>
       </c>
-      <c r="O40" s="5" t="n"/>
-      <c r="P40" s="5" t="n"/>
-      <c r="Q40" s="5" t="n"/>
+      <c r="O40" t="n">
+        <v>24726.24</v>
+      </c>
+      <c r="P40" t="n">
+        <v>23792.342</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>22804.063</v>
+      </c>
       <c r="R40" t="n">
         <v>24414.611</v>
       </c>
@@ -19052,26 +19276,54 @@
           <t>สินทรัพย์รวม</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
+      <c r="B41" t="n">
+        <v>362326.518</v>
+      </c>
+      <c r="C41" t="n">
+        <v>353002.88</v>
+      </c>
+      <c r="D41" t="n">
+        <v>362628.36</v>
+      </c>
+      <c r="E41" t="n">
+        <v>359719.892</v>
+      </c>
+      <c r="F41" t="n">
+        <v>369632.89</v>
+      </c>
+      <c r="G41" t="n">
+        <v>363430.987</v>
+      </c>
+      <c r="H41" t="n">
+        <v>364423.437</v>
+      </c>
+      <c r="I41" t="n">
+        <v>370265.417</v>
+      </c>
       <c r="J41" t="n">
         <v>358209.761</v>
       </c>
-      <c r="K41" s="5" t="n"/>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
+      <c r="K41" t="n">
+        <v>362049.415</v>
+      </c>
+      <c r="L41" t="n">
+        <v>371204.823</v>
+      </c>
+      <c r="M41" t="n">
+        <v>370070.456</v>
+      </c>
       <c r="N41" t="n">
         <v>359195.923</v>
       </c>
-      <c r="O41" s="5" t="n"/>
-      <c r="P41" s="5" t="n"/>
-      <c r="Q41" s="5" t="n"/>
+      <c r="O41" t="n">
+        <v>368813.476</v>
+      </c>
+      <c r="P41" t="n">
+        <v>372383.166</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>344558.581</v>
+      </c>
       <c r="R41" t="n">
         <v>346844.932</v>
       </c>
@@ -19094,26 +19346,54 @@
           <t>ส่วนของเจ้าของรวม</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
+      <c r="B42" t="n">
+        <v>76323.90300000001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>69419.738</v>
+      </c>
+      <c r="D42" t="n">
+        <v>65612.425</v>
+      </c>
+      <c r="E42" t="n">
+        <v>63481.21</v>
+      </c>
+      <c r="F42" t="n">
+        <v>79492.42999999999</v>
+      </c>
+      <c r="G42" t="n">
+        <v>75663.465</v>
+      </c>
+      <c r="H42" t="n">
+        <v>79308.323</v>
+      </c>
+      <c r="I42" t="n">
+        <v>84082.853</v>
+      </c>
       <c r="J42" t="n">
         <v>82608.97</v>
       </c>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
+      <c r="K42" t="n">
+        <v>92390.46000000001</v>
+      </c>
+      <c r="L42" t="n">
+        <v>85719.93700000001</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88073.20600000001</v>
+      </c>
       <c r="N42" t="n">
         <v>87294.557</v>
       </c>
-      <c r="O42" s="5" t="n"/>
-      <c r="P42" s="5" t="n"/>
-      <c r="Q42" s="5" t="n"/>
+      <c r="O42" t="n">
+        <v>91861.587</v>
+      </c>
+      <c r="P42" t="n">
+        <v>94773.579</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>89490.583</v>
+      </c>
       <c r="R42" t="n">
         <v>99136.83100000001</v>
       </c>
@@ -19136,26 +19416,54 @@
           <t>หนี้สินรวม</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
+      <c r="B43" t="n">
+        <v>286002.615</v>
+      </c>
+      <c r="C43" t="n">
+        <v>283583.142</v>
+      </c>
+      <c r="D43" t="n">
+        <v>297015.935</v>
+      </c>
+      <c r="E43" t="n">
+        <v>296238.682</v>
+      </c>
+      <c r="F43" t="n">
+        <v>290140.459</v>
+      </c>
+      <c r="G43" t="n">
+        <v>287767.522</v>
+      </c>
+      <c r="H43" t="n">
+        <v>285115.114</v>
+      </c>
+      <c r="I43" t="n">
+        <v>286182.564</v>
+      </c>
       <c r="J43" t="n">
         <v>275600.791</v>
       </c>
-      <c r="K43" s="5" t="n"/>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
+      <c r="K43" t="n">
+        <v>269658.955</v>
+      </c>
+      <c r="L43" t="n">
+        <v>285484.886</v>
+      </c>
+      <c r="M43" t="n">
+        <v>281997.25</v>
+      </c>
       <c r="N43" t="n">
         <v>271901.367</v>
       </c>
-      <c r="O43" s="5" t="n"/>
-      <c r="P43" s="5" t="n"/>
-      <c r="Q43" s="5" t="n"/>
+      <c r="O43" t="n">
+        <v>276951.889</v>
+      </c>
+      <c r="P43" t="n">
+        <v>277609.587</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>255067.998</v>
+      </c>
       <c r="R43" t="n">
         <v>247708.101</v>
       </c>
@@ -20354,7 +20662,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=20, MANRIN=17, MINT=6, OHTL=4, SHANG=4, SHR=4, VRANDA=4</t>
+          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=20, MANRIN=17, MINT=20, OHTL=4, SHANG=4, SHR=4, VRANDA=4</t>
         </is>
       </c>
     </row>

--- a/tour-finance/output/TOUR_all_linked.xlsx
+++ b/tour-finance/output/TOUR_all_linked.xlsx
@@ -15478,37 +15478,69 @@
           <t>รายได้รวม</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="9">
-        <f>B39+C39+D39+E39</f>
-        <v/>
-      </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="9">
-        <f>G39+H39+I39+J39</f>
-        <v/>
-      </c>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="n"/>
-      <c r="O39" s="5" t="n"/>
-      <c r="P39" s="9">
-        <f>L39+M39+N39+O39</f>
-        <v/>
-      </c>
-      <c r="Q39" s="5" t="n"/>
-      <c r="R39" s="5" t="n"/>
-      <c r="S39" s="5" t="n"/>
-      <c r="T39" s="5" t="n"/>
-      <c r="U39" s="9">
-        <f>Q39+R39+S39+T39</f>
-        <v/>
+      <c r="B39" t="n">
+        <v>150.921</v>
+      </c>
+      <c r="C39" t="n">
+        <v>84.16</v>
+      </c>
+      <c r="D39" t="n">
+        <v>106.611</v>
+      </c>
+      <c r="E39" s="9">
+        <f>F39-B39-C39-D39</f>
+        <v/>
+      </c>
+      <c r="F39" t="n">
+        <v>562.367</v>
+      </c>
+      <c r="G39" t="n">
+        <v>253.984</v>
+      </c>
+      <c r="H39" t="n">
+        <v>335.731</v>
+      </c>
+      <c r="I39" t="n">
+        <v>479.84</v>
+      </c>
+      <c r="J39" s="9">
+        <f>K39-G39-H39-I39</f>
+        <v/>
+      </c>
+      <c r="K39" t="n">
+        <v>1931.398</v>
+      </c>
+      <c r="L39" t="n">
+        <v>687.622</v>
+      </c>
+      <c r="M39" t="n">
+        <v>546.3819999999999</v>
+      </c>
+      <c r="N39" t="n">
+        <v>574.546</v>
+      </c>
+      <c r="O39" s="9">
+        <f>P39-L39-M39-N39</f>
+        <v/>
+      </c>
+      <c r="P39" t="n">
+        <v>2520.311</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>773.141</v>
+      </c>
+      <c r="R39" t="n">
+        <v>525.654</v>
+      </c>
+      <c r="S39" t="n">
+        <v>621.4640000000001</v>
+      </c>
+      <c r="T39" s="9">
+        <f>U39-Q39-R39-S39</f>
+        <v/>
+      </c>
+      <c r="U39" t="n">
+        <v>2705.661</v>
       </c>
       <c r="V39" t="n">
         <v>789.301</v>
@@ -15533,37 +15565,69 @@
           <t>รายได้อื่น</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="9">
-        <f>B40+C40+D40+E40</f>
-        <v/>
-      </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="9">
-        <f>G40+H40+I40+J40</f>
-        <v/>
-      </c>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="n"/>
-      <c r="O40" s="5" t="n"/>
-      <c r="P40" s="9">
-        <f>L40+M40+N40+O40</f>
-        <v/>
-      </c>
-      <c r="Q40" s="5" t="n"/>
-      <c r="R40" s="5" t="n"/>
-      <c r="S40" s="5" t="n"/>
-      <c r="T40" s="5" t="n"/>
-      <c r="U40" s="9">
-        <f>Q40+R40+S40+T40</f>
-        <v/>
+      <c r="B40" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="E40" s="9">
+        <f>F40-B40-C40-D40</f>
+        <v/>
+      </c>
+      <c r="F40" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.705</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="J40" s="9">
+        <f>K40-G40-H40-I40</f>
+        <v/>
+      </c>
+      <c r="K40" t="n">
+        <v>3.627</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.069</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="O40" s="9">
+        <f>P40-L40-M40-N40</f>
+        <v/>
+      </c>
+      <c r="P40" t="n">
+        <v>3.488</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="T40" s="9">
+        <f>U40-Q40-R40-S40</f>
+        <v/>
+      </c>
+      <c r="U40" t="n">
+        <v>3.875</v>
       </c>
       <c r="V40" t="n">
         <v>0.857</v>
@@ -15588,37 +15652,69 @@
           <t>ต้นทุนขาย (จริง)</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="9">
-        <f>B41+C41+D41+E41</f>
-        <v/>
-      </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="9">
-        <f>G41+H41+I41+J41</f>
-        <v/>
-      </c>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-      <c r="N41" s="5" t="n"/>
-      <c r="O41" s="5" t="n"/>
-      <c r="P41" s="9">
-        <f>L41+M41+N41+O41</f>
-        <v/>
-      </c>
-      <c r="Q41" s="5" t="n"/>
-      <c r="R41" s="5" t="n"/>
-      <c r="S41" s="5" t="n"/>
-      <c r="T41" s="5" t="n"/>
-      <c r="U41" s="9">
-        <f>Q41+R41+S41+T41</f>
-        <v/>
+      <c r="B41" t="n">
+        <v>217.638</v>
+      </c>
+      <c r="C41" t="n">
+        <v>183.835</v>
+      </c>
+      <c r="D41" t="n">
+        <v>176.104</v>
+      </c>
+      <c r="E41" s="9">
+        <f>F41-B41-C41-D41</f>
+        <v/>
+      </c>
+      <c r="F41" t="n">
+        <v>795.12</v>
+      </c>
+      <c r="G41" t="n">
+        <v>235.337</v>
+      </c>
+      <c r="H41" t="n">
+        <v>264.835</v>
+      </c>
+      <c r="I41" t="n">
+        <v>321.314</v>
+      </c>
+      <c r="J41" s="9">
+        <f>K41-G41-H41-I41</f>
+        <v/>
+      </c>
+      <c r="K41" t="n">
+        <v>1193.08</v>
+      </c>
+      <c r="L41" t="n">
+        <v>323.953</v>
+      </c>
+      <c r="M41" t="n">
+        <v>311.278</v>
+      </c>
+      <c r="N41" t="n">
+        <v>354.249</v>
+      </c>
+      <c r="O41" s="9">
+        <f>P41-L41-M41-N41</f>
+        <v/>
+      </c>
+      <c r="P41" t="n">
+        <v>1355.378</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>348.903</v>
+      </c>
+      <c r="R41" t="n">
+        <v>307.95</v>
+      </c>
+      <c r="S41" t="n">
+        <v>368.041</v>
+      </c>
+      <c r="T41" s="9">
+        <f>U41-Q41-R41-S41</f>
+        <v/>
+      </c>
+      <c r="U41" t="n">
+        <v>1393.389</v>
       </c>
       <c r="V41" t="n">
         <v>332.62</v>
@@ -15643,37 +15739,69 @@
           <t>กำไรสุทธิ (รวม)</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="9">
-        <f>B42+C42+D42+E42</f>
-        <v/>
-      </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="9">
-        <f>G42+H42+I42+J42</f>
-        <v/>
-      </c>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="n"/>
-      <c r="O42" s="5" t="n"/>
-      <c r="P42" s="9">
-        <f>L42+M42+N42+O42</f>
-        <v/>
-      </c>
-      <c r="Q42" s="5" t="n"/>
-      <c r="R42" s="5" t="n"/>
-      <c r="S42" s="5" t="n"/>
-      <c r="T42" s="5" t="n"/>
-      <c r="U42" s="9">
-        <f>Q42+R42+S42+T42</f>
-        <v/>
+      <c r="B42" t="n">
+        <v>-155.476</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-167.678</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-174.236</v>
+      </c>
+      <c r="E42" s="9">
+        <f>F42-B42-C42-D42</f>
+        <v/>
+      </c>
+      <c r="F42" t="n">
+        <v>-620.641</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-112.251</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-58.2</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-8.022</v>
+      </c>
+      <c r="J42" s="9">
+        <f>K42-G42-H42-I42</f>
+        <v/>
+      </c>
+      <c r="K42" t="n">
+        <v>88.208</v>
+      </c>
+      <c r="L42" t="n">
+        <v>127.765</v>
+      </c>
+      <c r="M42" t="n">
+        <v>34.223</v>
+      </c>
+      <c r="N42" t="n">
+        <v>16.205</v>
+      </c>
+      <c r="O42" s="9">
+        <f>P42-L42-M42-N42</f>
+        <v/>
+      </c>
+      <c r="P42" t="n">
+        <v>277.444</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>163.092</v>
+      </c>
+      <c r="R42" t="n">
+        <v>35.838</v>
+      </c>
+      <c r="S42" t="n">
+        <v>57.065</v>
+      </c>
+      <c r="T42" s="9">
+        <f>U42-Q42-R42-S42</f>
+        <v/>
+      </c>
+      <c r="U42" t="n">
+        <v>420.022</v>
       </c>
       <c r="V42" t="n">
         <v>193.859</v>
@@ -15698,37 +15826,69 @@
           <t>กำไรสุทธิ (ส่วนแม่)</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="9">
-        <f>B43+C43+D43+E43</f>
-        <v/>
-      </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="9">
-        <f>G43+H43+I43+J43</f>
-        <v/>
-      </c>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="n"/>
-      <c r="O43" s="5" t="n"/>
-      <c r="P43" s="9">
-        <f>L43+M43+N43+O43</f>
-        <v/>
-      </c>
-      <c r="Q43" s="5" t="n"/>
-      <c r="R43" s="5" t="n"/>
-      <c r="S43" s="5" t="n"/>
-      <c r="T43" s="5" t="n"/>
-      <c r="U43" s="9">
-        <f>Q43+R43+S43+T43</f>
-        <v/>
+      <c r="B43" t="n">
+        <v>-155.476</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-167.678</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-174.236</v>
+      </c>
+      <c r="E43" s="9">
+        <f>F43-B43-C43-D43</f>
+        <v/>
+      </c>
+      <c r="F43" t="n">
+        <v>-620.641</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-112.251</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-58.2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-8.022</v>
+      </c>
+      <c r="J43" s="9">
+        <f>K43-G43-H43-I43</f>
+        <v/>
+      </c>
+      <c r="K43" t="n">
+        <v>88.208</v>
+      </c>
+      <c r="L43" t="n">
+        <v>127.765</v>
+      </c>
+      <c r="M43" t="n">
+        <v>34.223</v>
+      </c>
+      <c r="N43" t="n">
+        <v>16.205</v>
+      </c>
+      <c r="O43" s="9">
+        <f>P43-L43-M43-N43</f>
+        <v/>
+      </c>
+      <c r="P43" t="n">
+        <v>277.444</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>163.092</v>
+      </c>
+      <c r="R43" t="n">
+        <v>35.838</v>
+      </c>
+      <c r="S43" t="n">
+        <v>57.065</v>
+      </c>
+      <c r="T43" s="9">
+        <f>U43-Q43-R43-S43</f>
+        <v/>
+      </c>
+      <c r="U43" t="n">
+        <v>420.022</v>
       </c>
       <c r="V43" t="n">
         <v>193.859</v>
@@ -19514,22 +19674,54 @@
           <t>ลูกหนี้การค้า</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="n"/>
-      <c r="O45" s="5" t="n"/>
-      <c r="P45" s="5" t="n"/>
-      <c r="Q45" s="5" t="n"/>
+      <c r="B45" t="n">
+        <v>46.356</v>
+      </c>
+      <c r="C45" t="n">
+        <v>30.211</v>
+      </c>
+      <c r="D45" t="n">
+        <v>29.348</v>
+      </c>
+      <c r="E45" t="n">
+        <v>45.735</v>
+      </c>
+      <c r="F45" t="n">
+        <v>67.10299999999999</v>
+      </c>
+      <c r="G45" t="n">
+        <v>48.531</v>
+      </c>
+      <c r="H45" t="n">
+        <v>61.559</v>
+      </c>
+      <c r="I45" t="n">
+        <v>68.98399999999999</v>
+      </c>
+      <c r="J45" t="n">
+        <v>120.81</v>
+      </c>
+      <c r="K45" t="n">
+        <v>87.801</v>
+      </c>
+      <c r="L45" t="n">
+        <v>94.71599999999999</v>
+      </c>
+      <c r="M45" t="n">
+        <v>95.655</v>
+      </c>
+      <c r="N45" t="n">
+        <v>102.683</v>
+      </c>
+      <c r="O45" t="n">
+        <v>80.002</v>
+      </c>
+      <c r="P45" t="n">
+        <v>86.32299999999999</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>98.321</v>
+      </c>
       <c r="R45" t="n">
         <v>84.202</v>
       </c>
@@ -19552,22 +19744,54 @@
           <t>สินค้าคงเหลือ</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="n"/>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="n"/>
-      <c r="O46" s="5" t="n"/>
-      <c r="P46" s="5" t="n"/>
-      <c r="Q46" s="5" t="n"/>
+      <c r="B46" t="n">
+        <v>18.225</v>
+      </c>
+      <c r="C46" t="n">
+        <v>18.218</v>
+      </c>
+      <c r="D46" t="n">
+        <v>20.254</v>
+      </c>
+      <c r="E46" t="n">
+        <v>19.472</v>
+      </c>
+      <c r="F46" t="n">
+        <v>20.546</v>
+      </c>
+      <c r="G46" t="n">
+        <v>20.229</v>
+      </c>
+      <c r="H46" t="n">
+        <v>20.987</v>
+      </c>
+      <c r="I46" t="n">
+        <v>20.889</v>
+      </c>
+      <c r="J46" t="n">
+        <v>26.577</v>
+      </c>
+      <c r="K46" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="L46" t="n">
+        <v>27.031</v>
+      </c>
+      <c r="M46" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="N46" t="n">
+        <v>32.461</v>
+      </c>
+      <c r="O46" t="n">
+        <v>24.372</v>
+      </c>
+      <c r="P46" t="n">
+        <v>24.019</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>22.476</v>
+      </c>
       <c r="R46" t="n">
         <v>28.86</v>
       </c>
@@ -19590,22 +19814,54 @@
           <t>เจ้าหนี้การค้า</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="n"/>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="n"/>
-      <c r="O47" s="5" t="n"/>
-      <c r="P47" s="5" t="n"/>
-      <c r="Q47" s="5" t="n"/>
+      <c r="B47" t="n">
+        <v>397.078</v>
+      </c>
+      <c r="C47" t="n">
+        <v>304.342</v>
+      </c>
+      <c r="D47" t="n">
+        <v>275.818</v>
+      </c>
+      <c r="E47" t="n">
+        <v>249.384</v>
+      </c>
+      <c r="F47" t="n">
+        <v>294.506</v>
+      </c>
+      <c r="G47" t="n">
+        <v>273.374</v>
+      </c>
+      <c r="H47" t="n">
+        <v>255.272</v>
+      </c>
+      <c r="I47" t="n">
+        <v>323.347</v>
+      </c>
+      <c r="J47" t="n">
+        <v>344.898</v>
+      </c>
+      <c r="K47" t="n">
+        <v>250.411</v>
+      </c>
+      <c r="L47" t="n">
+        <v>285.624</v>
+      </c>
+      <c r="M47" t="n">
+        <v>346.704</v>
+      </c>
+      <c r="N47" t="n">
+        <v>365.717</v>
+      </c>
+      <c r="O47" t="n">
+        <v>319.664</v>
+      </c>
+      <c r="P47" t="n">
+        <v>296.01</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>343.843</v>
+      </c>
       <c r="R47" t="n">
         <v>374.801</v>
       </c>
@@ -19628,22 +19884,54 @@
           <t>สินทรัพย์รวม</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="n"/>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="n"/>
-      <c r="O48" s="5" t="n"/>
-      <c r="P48" s="5" t="n"/>
-      <c r="Q48" s="5" t="n"/>
+      <c r="B48" t="n">
+        <v>6742.074</v>
+      </c>
+      <c r="C48" t="n">
+        <v>6566.336</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6436.177</v>
+      </c>
+      <c r="E48" t="n">
+        <v>6335.593</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6303.015</v>
+      </c>
+      <c r="G48" t="n">
+        <v>6169.437</v>
+      </c>
+      <c r="H48" t="n">
+        <v>6101.65</v>
+      </c>
+      <c r="I48" t="n">
+        <v>6099.483</v>
+      </c>
+      <c r="J48" t="n">
+        <v>6123.689</v>
+      </c>
+      <c r="K48" t="n">
+        <v>5998.52</v>
+      </c>
+      <c r="L48" t="n">
+        <v>5988.515</v>
+      </c>
+      <c r="M48" t="n">
+        <v>5964.746</v>
+      </c>
+      <c r="N48" t="n">
+        <v>5948.566</v>
+      </c>
+      <c r="O48" t="n">
+        <v>5904.48</v>
+      </c>
+      <c r="P48" t="n">
+        <v>5818.265</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>5820.068</v>
+      </c>
       <c r="R48" t="n">
         <v>5742.7</v>
       </c>
@@ -19666,22 +19954,54 @@
           <t>ส่วนของเจ้าของรวม</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="n"/>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="n"/>
-      <c r="O49" s="5" t="n"/>
-      <c r="P49" s="5" t="n"/>
-      <c r="Q49" s="5" t="n"/>
+      <c r="B49" t="n">
+        <v>2123.641</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1971.678</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1803.968</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1630.456</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1559.096</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1450.778</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1397.127</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1387.521</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1663.502</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1790.99</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1954.239</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1971.439</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2068.992</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2230.144</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2265.982</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2323.047</v>
+      </c>
       <c r="R49" t="n">
         <v>2483.822</v>
       </c>
@@ -19704,22 +20024,54 @@
           <t>หนี้สินรวม</t>
         </is>
       </c>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="5" t="n"/>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="n"/>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="n"/>
-      <c r="O50" s="5" t="n"/>
-      <c r="P50" s="5" t="n"/>
-      <c r="Q50" s="5" t="n"/>
+      <c r="B50" t="n">
+        <v>4618.433</v>
+      </c>
+      <c r="C50" t="n">
+        <v>4594.658</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4632.209</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4705.137</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4743.919</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4718.659</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4704.523</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4711.963</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4460.186</v>
+      </c>
+      <c r="K50" t="n">
+        <v>4207.531</v>
+      </c>
+      <c r="L50" t="n">
+        <v>4034.276</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3993.306</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3879.574</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3674.337</v>
+      </c>
+      <c r="P50" t="n">
+        <v>3552.284</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3497.021</v>
+      </c>
       <c r="R50" t="n">
         <v>3258.879</v>
       </c>
@@ -20662,7 +21014,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=20, MANRIN=17, MINT=20, OHTL=4, SHANG=4, SHR=4, VRANDA=4</t>
+          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=20, MANRIN=17, MINT=20, OHTL=20, SHANG=4, SHR=4, VRANDA=4</t>
         </is>
       </c>
     </row>

--- a/tour-finance/output/TOUR_all_linked.xlsx
+++ b/tour-finance/output/TOUR_all_linked.xlsx
@@ -15945,37 +15945,69 @@
           <t>รายได้รวม</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="9">
-        <f>B45+C45+D45+E45</f>
-        <v/>
-      </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="9">
-        <f>G45+H45+I45+J45</f>
-        <v/>
-      </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="n"/>
-      <c r="O45" s="5" t="n"/>
-      <c r="P45" s="9">
-        <f>L45+M45+N45+O45</f>
-        <v/>
-      </c>
-      <c r="Q45" s="5" t="n"/>
-      <c r="R45" s="5" t="n"/>
-      <c r="S45" s="5" t="n"/>
-      <c r="T45" s="5" t="n"/>
-      <c r="U45" s="9">
-        <f>Q45+R45+S45+T45</f>
-        <v/>
+      <c r="B45" t="n">
+        <v>77.03700000000001</v>
+      </c>
+      <c r="C45" t="n">
+        <v>65.75700000000001</v>
+      </c>
+      <c r="D45" t="n">
+        <v>72.79600000000001</v>
+      </c>
+      <c r="E45" s="9">
+        <f>F45-B45-C45-D45</f>
+        <v/>
+      </c>
+      <c r="F45" t="n">
+        <v>355.874</v>
+      </c>
+      <c r="G45" t="n">
+        <v>126.409</v>
+      </c>
+      <c r="H45" t="n">
+        <v>199.551</v>
+      </c>
+      <c r="I45" t="n">
+        <v>364.513</v>
+      </c>
+      <c r="J45" s="9">
+        <f>K45-G45-H45-I45</f>
+        <v/>
+      </c>
+      <c r="K45" t="n">
+        <v>1201.012</v>
+      </c>
+      <c r="L45" t="n">
+        <v>601.976</v>
+      </c>
+      <c r="M45" t="n">
+        <v>448.375</v>
+      </c>
+      <c r="N45" t="n">
+        <v>508.461</v>
+      </c>
+      <c r="O45" s="9">
+        <f>P45-L45-M45-N45</f>
+        <v/>
+      </c>
+      <c r="P45" t="n">
+        <v>2186.19</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>701.4400000000001</v>
+      </c>
+      <c r="R45" t="n">
+        <v>471.877</v>
+      </c>
+      <c r="S45" t="n">
+        <v>510.709</v>
+      </c>
+      <c r="T45" s="9">
+        <f>U45-Q45-R45-S45</f>
+        <v/>
+      </c>
+      <c r="U45" t="n">
+        <v>2430.166</v>
       </c>
       <c r="V45" t="n">
         <v>659.954</v>
@@ -16000,37 +16032,69 @@
           <t>รายได้อื่น</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="9">
-        <f>B46+C46+D46+E46</f>
-        <v/>
-      </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="9">
-        <f>G46+H46+I46+J46</f>
-        <v/>
-      </c>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="n"/>
-      <c r="O46" s="5" t="n"/>
-      <c r="P46" s="9">
-        <f>L46+M46+N46+O46</f>
-        <v/>
-      </c>
-      <c r="Q46" s="5" t="n"/>
-      <c r="R46" s="5" t="n"/>
-      <c r="S46" s="5" t="n"/>
-      <c r="T46" s="5" t="n"/>
-      <c r="U46" s="9">
-        <f>Q46+R46+S46+T46</f>
-        <v/>
+      <c r="B46" t="n">
+        <v>2.074</v>
+      </c>
+      <c r="C46" t="n">
+        <v>28.913</v>
+      </c>
+      <c r="D46" t="n">
+        <v>20.554</v>
+      </c>
+      <c r="E46" s="9">
+        <f>F46-B46-C46-D46</f>
+        <v/>
+      </c>
+      <c r="F46" t="n">
+        <v>21.366</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.269</v>
+      </c>
+      <c r="H46" t="n">
+        <v>39.261</v>
+      </c>
+      <c r="I46" t="n">
+        <v>44.847</v>
+      </c>
+      <c r="J46" s="9">
+        <f>K46-G46-H46-I46</f>
+        <v/>
+      </c>
+      <c r="K46" t="n">
+        <v>25.114</v>
+      </c>
+      <c r="L46" t="n">
+        <v>4.414</v>
+      </c>
+      <c r="M46" t="n">
+        <v>26.406</v>
+      </c>
+      <c r="N46" t="n">
+        <v>31.478</v>
+      </c>
+      <c r="O46" s="9">
+        <f>P46-L46-M46-N46</f>
+        <v/>
+      </c>
+      <c r="P46" t="n">
+        <v>29.154</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="R46" t="n">
+        <v>55.858</v>
+      </c>
+      <c r="S46" t="n">
+        <v>43.349</v>
+      </c>
+      <c r="T46" s="9">
+        <f>U46-Q46-R46-S46</f>
+        <v/>
+      </c>
+      <c r="U46" t="n">
+        <v>95.286</v>
       </c>
       <c r="V46" t="n">
         <v>4.999</v>
@@ -16055,37 +16119,69 @@
           <t>ต้นทุนขาย (จริง)</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="9">
-        <f>B47+C47+D47+E47</f>
-        <v/>
-      </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="9">
-        <f>G47+H47+I47+J47</f>
-        <v/>
-      </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="n"/>
-      <c r="O47" s="5" t="n"/>
-      <c r="P47" s="9">
-        <f>L47+M47+N47+O47</f>
-        <v/>
-      </c>
-      <c r="Q47" s="5" t="n"/>
-      <c r="R47" s="5" t="n"/>
-      <c r="S47" s="5" t="n"/>
-      <c r="T47" s="5" t="n"/>
-      <c r="U47" s="9">
-        <f>Q47+R47+S47+T47</f>
-        <v/>
+      <c r="B47" t="n">
+        <v>59.991</v>
+      </c>
+      <c r="C47" t="n">
+        <v>53.13</v>
+      </c>
+      <c r="D47" t="n">
+        <v>57.563</v>
+      </c>
+      <c r="E47" s="9">
+        <f>F47-B47-C47-D47</f>
+        <v/>
+      </c>
+      <c r="F47" t="n">
+        <v>251.839</v>
+      </c>
+      <c r="G47" t="n">
+        <v>67.55200000000001</v>
+      </c>
+      <c r="H47" t="n">
+        <v>82.545</v>
+      </c>
+      <c r="I47" t="n">
+        <v>128.473</v>
+      </c>
+      <c r="J47" s="9">
+        <f>K47-G47-H47-I47</f>
+        <v/>
+      </c>
+      <c r="K47" t="n">
+        <v>448.111</v>
+      </c>
+      <c r="L47" t="n">
+        <v>164.22</v>
+      </c>
+      <c r="M47" t="n">
+        <v>140.662</v>
+      </c>
+      <c r="N47" t="n">
+        <v>176.621</v>
+      </c>
+      <c r="O47" s="9">
+        <f>P47-L47-M47-N47</f>
+        <v/>
+      </c>
+      <c r="P47" t="n">
+        <v>676.828</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>191.092</v>
+      </c>
+      <c r="R47" t="n">
+        <v>151.669</v>
+      </c>
+      <c r="S47" t="n">
+        <v>175.902</v>
+      </c>
+      <c r="T47" s="9">
+        <f>U47-Q47-R47-S47</f>
+        <v/>
+      </c>
+      <c r="U47" t="n">
+        <v>734.1660000000001</v>
       </c>
       <c r="V47" t="n">
         <v>188.579</v>
@@ -16110,37 +16206,69 @@
           <t>กำไรสุทธิ (รวม)</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="9">
-        <f>B48+C48+D48+E48</f>
-        <v/>
-      </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="9">
-        <f>G48+H48+I48+J48</f>
-        <v/>
-      </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="n"/>
-      <c r="O48" s="5" t="n"/>
-      <c r="P48" s="9">
-        <f>L48+M48+N48+O48</f>
-        <v/>
-      </c>
-      <c r="Q48" s="5" t="n"/>
-      <c r="R48" s="5" t="n"/>
-      <c r="S48" s="5" t="n"/>
-      <c r="T48" s="5" t="n"/>
-      <c r="U48" s="9">
-        <f>Q48+R48+S48+T48</f>
-        <v/>
+      <c r="B48" t="n">
+        <v>-84.02500000000001</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-107.398</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-113.631</v>
+      </c>
+      <c r="E48" s="9">
+        <f>F48-B48-C48-D48</f>
+        <v/>
+      </c>
+      <c r="F48" t="n">
+        <v>-486.364</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-84.61799999999999</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-43.38</v>
+      </c>
+      <c r="I48" t="n">
+        <v>62.364</v>
+      </c>
+      <c r="J48" s="9">
+        <f>K48-G48-H48-I48</f>
+        <v/>
+      </c>
+      <c r="K48" t="n">
+        <v>-73.89400000000001</v>
+      </c>
+      <c r="L48" t="n">
+        <v>117.248</v>
+      </c>
+      <c r="M48" t="n">
+        <v>102.171</v>
+      </c>
+      <c r="N48" t="n">
+        <v>66.246</v>
+      </c>
+      <c r="O48" s="9">
+        <f>P48-L48-M48-N48</f>
+        <v/>
+      </c>
+      <c r="P48" t="n">
+        <v>139.518</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>223.647</v>
+      </c>
+      <c r="R48" t="n">
+        <v>90.274</v>
+      </c>
+      <c r="S48" t="n">
+        <v>34.719</v>
+      </c>
+      <c r="T48" s="9">
+        <f>U48-Q48-R48-S48</f>
+        <v/>
+      </c>
+      <c r="U48" t="n">
+        <v>370.976</v>
       </c>
       <c r="V48" t="n">
         <v>159.821</v>
@@ -16165,37 +16293,69 @@
           <t>กำไรสุทธิ (ส่วนแม่)</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="9">
-        <f>B49+C49+D49+E49</f>
-        <v/>
-      </c>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="9">
-        <f>G49+H49+I49+J49</f>
-        <v/>
-      </c>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="n"/>
-      <c r="O49" s="5" t="n"/>
-      <c r="P49" s="9">
-        <f>L49+M49+N49+O49</f>
-        <v/>
-      </c>
-      <c r="Q49" s="5" t="n"/>
-      <c r="R49" s="5" t="n"/>
-      <c r="S49" s="5" t="n"/>
-      <c r="T49" s="5" t="n"/>
-      <c r="U49" s="9">
-        <f>Q49+R49+S49+T49</f>
-        <v/>
+      <c r="B49" t="n">
+        <v>-84.01900000000001</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-113.427</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-114.035</v>
+      </c>
+      <c r="E49" s="9">
+        <f>F49-B49-C49-D49</f>
+        <v/>
+      </c>
+      <c r="F49" t="n">
+        <v>-492.81</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-84.631</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-44.856</v>
+      </c>
+      <c r="I49" t="n">
+        <v>60.434</v>
+      </c>
+      <c r="J49" s="9">
+        <f>K49-G49-H49-I49</f>
+        <v/>
+      </c>
+      <c r="K49" t="n">
+        <v>-80.191</v>
+      </c>
+      <c r="L49" t="n">
+        <v>116.072</v>
+      </c>
+      <c r="M49" t="n">
+        <v>101.987</v>
+      </c>
+      <c r="N49" t="n">
+        <v>66.148</v>
+      </c>
+      <c r="O49" s="9">
+        <f>P49-L49-M49-N49</f>
+        <v/>
+      </c>
+      <c r="P49" t="n">
+        <v>137.986</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>223.643</v>
+      </c>
+      <c r="R49" t="n">
+        <v>90.267</v>
+      </c>
+      <c r="S49" t="n">
+        <v>34.715</v>
+      </c>
+      <c r="T49" s="9">
+        <f>U49-Q49-R49-S49</f>
+        <v/>
+      </c>
+      <c r="U49" t="n">
+        <v>370.956</v>
       </c>
       <c r="V49" t="n">
         <v>159.817</v>
@@ -20122,22 +20282,54 @@
           <t>ลูกหนี้การค้า</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="n"/>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="n"/>
-      <c r="O52" s="5" t="n"/>
-      <c r="P52" s="5" t="n"/>
-      <c r="Q52" s="5" t="n"/>
+      <c r="B52" t="n">
+        <v>17.979</v>
+      </c>
+      <c r="C52" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="D52" t="n">
+        <v>5.633</v>
+      </c>
+      <c r="E52" t="n">
+        <v>12.294</v>
+      </c>
+      <c r="F52" t="n">
+        <v>28.897</v>
+      </c>
+      <c r="G52" t="n">
+        <v>29.831</v>
+      </c>
+      <c r="H52" t="n">
+        <v>43.417</v>
+      </c>
+      <c r="I52" t="n">
+        <v>76.648</v>
+      </c>
+      <c r="J52" t="n">
+        <v>88.569</v>
+      </c>
+      <c r="K52" t="n">
+        <v>56.896</v>
+      </c>
+      <c r="L52" t="n">
+        <v>42.509</v>
+      </c>
+      <c r="M52" t="n">
+        <v>74.08199999999999</v>
+      </c>
+      <c r="N52" t="n">
+        <v>75.488</v>
+      </c>
+      <c r="O52" t="n">
+        <v>73.267</v>
+      </c>
+      <c r="P52" t="n">
+        <v>43.853</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>65.036</v>
+      </c>
       <c r="R52" t="n">
         <v>80.06399999999999</v>
       </c>
@@ -20160,22 +20352,54 @@
           <t>สินค้าคงเหลือ</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="n"/>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="n"/>
-      <c r="O53" s="5" t="n"/>
-      <c r="P53" s="5" t="n"/>
-      <c r="Q53" s="5" t="n"/>
+      <c r="B53" t="n">
+        <v>24.835</v>
+      </c>
+      <c r="C53" t="n">
+        <v>23.251</v>
+      </c>
+      <c r="D53" t="n">
+        <v>22.663</v>
+      </c>
+      <c r="E53" t="n">
+        <v>20.033</v>
+      </c>
+      <c r="F53" t="n">
+        <v>20.297</v>
+      </c>
+      <c r="G53" t="n">
+        <v>19.427</v>
+      </c>
+      <c r="H53" t="n">
+        <v>19.074</v>
+      </c>
+      <c r="I53" t="n">
+        <v>18</v>
+      </c>
+      <c r="J53" t="n">
+        <v>24.184</v>
+      </c>
+      <c r="K53" t="n">
+        <v>20.793</v>
+      </c>
+      <c r="L53" t="n">
+        <v>23.989</v>
+      </c>
+      <c r="M53" t="n">
+        <v>24.112</v>
+      </c>
+      <c r="N53" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="O53" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="P53" t="n">
+        <v>24.049</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>23.925</v>
+      </c>
       <c r="R53" t="n">
         <v>28.732</v>
       </c>
@@ -20198,22 +20422,54 @@
           <t>เจ้าหนี้การค้า</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="n"/>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
-      <c r="N54" s="5" t="n"/>
-      <c r="O54" s="5" t="n"/>
-      <c r="P54" s="5" t="n"/>
-      <c r="Q54" s="5" t="n"/>
+      <c r="B54" t="n">
+        <v>97.71299999999999</v>
+      </c>
+      <c r="C54" t="n">
+        <v>89.02800000000001</v>
+      </c>
+      <c r="D54" t="n">
+        <v>74.083</v>
+      </c>
+      <c r="E54" t="n">
+        <v>74.58799999999999</v>
+      </c>
+      <c r="F54" t="n">
+        <v>99.652</v>
+      </c>
+      <c r="G54" t="n">
+        <v>74.864</v>
+      </c>
+      <c r="H54" t="n">
+        <v>90.167</v>
+      </c>
+      <c r="I54" t="n">
+        <v>113.972</v>
+      </c>
+      <c r="J54" t="n">
+        <v>192.481</v>
+      </c>
+      <c r="K54" t="n">
+        <v>139.563</v>
+      </c>
+      <c r="L54" t="n">
+        <v>143.965</v>
+      </c>
+      <c r="M54" t="n">
+        <v>156.461</v>
+      </c>
+      <c r="N54" t="n">
+        <v>222.811</v>
+      </c>
+      <c r="O54" t="n">
+        <v>176.546</v>
+      </c>
+      <c r="P54" t="n">
+        <v>155.739</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>164.766</v>
+      </c>
       <c r="R54" t="n">
         <v>234.957</v>
       </c>
@@ -20236,22 +20492,54 @@
           <t>สินทรัพย์รวม</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="n"/>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
-      <c r="N55" s="5" t="n"/>
-      <c r="O55" s="5" t="n"/>
-      <c r="P55" s="5" t="n"/>
-      <c r="Q55" s="5" t="n"/>
+      <c r="B55" t="n">
+        <v>7678.673</v>
+      </c>
+      <c r="C55" t="n">
+        <v>7704.899</v>
+      </c>
+      <c r="D55" t="n">
+        <v>7795.243</v>
+      </c>
+      <c r="E55" t="n">
+        <v>7761.689</v>
+      </c>
+      <c r="F55" t="n">
+        <v>7577.451</v>
+      </c>
+      <c r="G55" t="n">
+        <v>7445.292</v>
+      </c>
+      <c r="H55" t="n">
+        <v>7561.836</v>
+      </c>
+      <c r="I55" t="n">
+        <v>7787.865</v>
+      </c>
+      <c r="J55" t="n">
+        <v>7809.042</v>
+      </c>
+      <c r="K55" t="n">
+        <v>7829.609</v>
+      </c>
+      <c r="L55" t="n">
+        <v>7961.29</v>
+      </c>
+      <c r="M55" t="n">
+        <v>8028.141</v>
+      </c>
+      <c r="N55" t="n">
+        <v>7848.676</v>
+      </c>
+      <c r="O55" t="n">
+        <v>8086.747</v>
+      </c>
+      <c r="P55" t="n">
+        <v>8060.359</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>8007.153</v>
+      </c>
       <c r="R55" t="n">
         <v>8067.434</v>
       </c>
@@ -20274,22 +20562,54 @@
           <t>ส่วนของเจ้าของรวม</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="5" t="n"/>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="n"/>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
-      <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
-      <c r="N56" s="5" t="n"/>
-      <c r="O56" s="5" t="n"/>
-      <c r="P56" s="5" t="n"/>
-      <c r="Q56" s="5" t="n"/>
+      <c r="B56" t="n">
+        <v>7381.006</v>
+      </c>
+      <c r="C56" t="n">
+        <v>7425.499</v>
+      </c>
+      <c r="D56" t="n">
+        <v>7512.439</v>
+      </c>
+      <c r="E56" t="n">
+        <v>7481.804</v>
+      </c>
+      <c r="F56" t="n">
+        <v>7251.166</v>
+      </c>
+      <c r="G56" t="n">
+        <v>7131.687</v>
+      </c>
+      <c r="H56" t="n">
+        <v>7206.907</v>
+      </c>
+      <c r="I56" t="n">
+        <v>7379.094</v>
+      </c>
+      <c r="J56" t="n">
+        <v>7292.631</v>
+      </c>
+      <c r="K56" t="n">
+        <v>7434.763</v>
+      </c>
+      <c r="L56" t="n">
+        <v>7548.144</v>
+      </c>
+      <c r="M56" t="n">
+        <v>7575.094</v>
+      </c>
+      <c r="N56" t="n">
+        <v>7298.278</v>
+      </c>
+      <c r="O56" t="n">
+        <v>7610.423</v>
+      </c>
+      <c r="P56" t="n">
+        <v>7600.249</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>7459.225</v>
+      </c>
       <c r="R56" t="n">
         <v>7439.227</v>
       </c>
@@ -20312,22 +20632,54 @@
           <t>หนี้สินรวม</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
-      <c r="N57" s="5" t="n"/>
-      <c r="O57" s="5" t="n"/>
-      <c r="P57" s="5" t="n"/>
-      <c r="Q57" s="5" t="n"/>
+      <c r="B57" t="n">
+        <v>297.667</v>
+      </c>
+      <c r="C57" t="n">
+        <v>279.4</v>
+      </c>
+      <c r="D57" t="n">
+        <v>282.804</v>
+      </c>
+      <c r="E57" t="n">
+        <v>279.885</v>
+      </c>
+      <c r="F57" t="n">
+        <v>326.285</v>
+      </c>
+      <c r="G57" t="n">
+        <v>313.605</v>
+      </c>
+      <c r="H57" t="n">
+        <v>354.929</v>
+      </c>
+      <c r="I57" t="n">
+        <v>408.771</v>
+      </c>
+      <c r="J57" t="n">
+        <v>516.4109999999999</v>
+      </c>
+      <c r="K57" t="n">
+        <v>394.846</v>
+      </c>
+      <c r="L57" t="n">
+        <v>413.146</v>
+      </c>
+      <c r="M57" t="n">
+        <v>453.047</v>
+      </c>
+      <c r="N57" t="n">
+        <v>550.397</v>
+      </c>
+      <c r="O57" t="n">
+        <v>476.324</v>
+      </c>
+      <c r="P57" t="n">
+        <v>460.11</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>547.928</v>
+      </c>
       <c r="R57" t="n">
         <v>628.207</v>
       </c>
@@ -21014,7 +21366,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=20, MANRIN=17, MINT=20, OHTL=20, SHANG=4, SHR=4, VRANDA=4</t>
+          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=20, MANRIN=17, MINT=20, OHTL=20, SHANG=20, SHR=4, VRANDA=4</t>
         </is>
       </c>
     </row>

--- a/tour-finance/output/TOUR_all_linked.xlsx
+++ b/tour-finance/output/TOUR_all_linked.xlsx
@@ -16412,37 +16412,69 @@
           <t>รายได้รวม</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="9">
-        <f>B51+C51+D51+E51</f>
-        <v/>
-      </c>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="9">
-        <f>G51+H51+I51+J51</f>
-        <v/>
-      </c>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
-      <c r="N51" s="5" t="n"/>
-      <c r="O51" s="5" t="n"/>
-      <c r="P51" s="9">
-        <f>L51+M51+N51+O51</f>
-        <v/>
-      </c>
-      <c r="Q51" s="5" t="n"/>
-      <c r="R51" s="5" t="n"/>
-      <c r="S51" s="5" t="n"/>
-      <c r="T51" s="5" t="n"/>
-      <c r="U51" s="9">
-        <f>Q51+R51+S51+T51</f>
-        <v/>
+      <c r="B51" t="n">
+        <v>692.241</v>
+      </c>
+      <c r="C51" t="n">
+        <v>837.966</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1433.64</v>
+      </c>
+      <c r="E51" s="9">
+        <f>F51-B51-C51-D51</f>
+        <v/>
+      </c>
+      <c r="F51" t="n">
+        <v>4689.55</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1700.05</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2094.021</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2466.344</v>
+      </c>
+      <c r="J51" s="9">
+        <f>K51-G51-H51-I51</f>
+        <v/>
+      </c>
+      <c r="K51" t="n">
+        <v>8824.288</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2576.759</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2318.612</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2495.846</v>
+      </c>
+      <c r="O51" s="9">
+        <f>P51-L51-M51-N51</f>
+        <v/>
+      </c>
+      <c r="P51" t="n">
+        <v>10096.755</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2781.537</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2527.774</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2538.71</v>
+      </c>
+      <c r="T51" s="9">
+        <f>U51-Q51-R51-S51</f>
+        <v/>
+      </c>
+      <c r="U51" t="n">
+        <v>10558.246</v>
       </c>
       <c r="V51" t="n">
         <v>2649.224</v>
@@ -16467,37 +16499,69 @@
           <t>รายได้อื่น</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="9">
-        <f>B52+C52+D52+E52</f>
-        <v/>
-      </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="9">
-        <f>G52+H52+I52+J52</f>
-        <v/>
-      </c>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="n"/>
-      <c r="O52" s="5" t="n"/>
-      <c r="P52" s="9">
-        <f>L52+M52+N52+O52</f>
-        <v/>
-      </c>
-      <c r="Q52" s="5" t="n"/>
-      <c r="R52" s="5" t="n"/>
-      <c r="S52" s="5" t="n"/>
-      <c r="T52" s="5" t="n"/>
-      <c r="U52" s="9">
-        <f>Q52+R52+S52+T52</f>
-        <v/>
+      <c r="B52" t="n">
+        <v>148.477</v>
+      </c>
+      <c r="C52" t="n">
+        <v>34.821</v>
+      </c>
+      <c r="D52" t="n">
+        <v>12.028</v>
+      </c>
+      <c r="E52" s="9">
+        <f>F52-B52-C52-D52</f>
+        <v/>
+      </c>
+      <c r="F52" t="n">
+        <v>177.096</v>
+      </c>
+      <c r="G52" t="n">
+        <v>10.428</v>
+      </c>
+      <c r="H52" t="n">
+        <v>22.688</v>
+      </c>
+      <c r="I52" t="n">
+        <v>104.247</v>
+      </c>
+      <c r="J52" s="9">
+        <f>K52-G52-H52-I52</f>
+        <v/>
+      </c>
+      <c r="K52" t="n">
+        <v>131.735</v>
+      </c>
+      <c r="L52" t="n">
+        <v>32.486</v>
+      </c>
+      <c r="M52" t="n">
+        <v>41.534</v>
+      </c>
+      <c r="N52" t="n">
+        <v>95.017</v>
+      </c>
+      <c r="O52" s="9">
+        <f>P52-L52-M52-N52</f>
+        <v/>
+      </c>
+      <c r="P52" t="n">
+        <v>395.675</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>38.763</v>
+      </c>
+      <c r="R52" t="n">
+        <v>58.683</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5.019</v>
+      </c>
+      <c r="T52" s="9">
+        <f>U52-Q52-R52-S52</f>
+        <v/>
+      </c>
+      <c r="U52" t="n">
+        <v>206</v>
       </c>
       <c r="V52" t="n">
         <v>27.131</v>
@@ -16522,37 +16586,69 @@
           <t>ต้นทุนขาย (จริง)</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="9">
-        <f>B53+C53+D53+E53</f>
-        <v/>
-      </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="9">
-        <f>G53+H53+I53+J53</f>
-        <v/>
-      </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="n"/>
-      <c r="O53" s="5" t="n"/>
-      <c r="P53" s="9">
-        <f>L53+M53+N53+O53</f>
-        <v/>
-      </c>
-      <c r="Q53" s="5" t="n"/>
-      <c r="R53" s="5" t="n"/>
-      <c r="S53" s="5" t="n"/>
-      <c r="T53" s="5" t="n"/>
-      <c r="U53" s="9">
-        <f>Q53+R53+S53+T53</f>
-        <v/>
+      <c r="B53" t="n">
+        <v>566.057</v>
+      </c>
+      <c r="C53" t="n">
+        <v>785.5359999999999</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1018.67</v>
+      </c>
+      <c r="E53" s="9">
+        <f>F53-B53-C53-D53</f>
+        <v/>
+      </c>
+      <c r="F53" t="n">
+        <v>3595.957</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1258.798</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1427.143</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1528.194</v>
+      </c>
+      <c r="J53" s="9">
+        <f>K53-G53-H53-I53</f>
+        <v/>
+      </c>
+      <c r="K53" t="n">
+        <v>5807.443</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1604.888</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1598.95</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1548.071</v>
+      </c>
+      <c r="O53" s="9">
+        <f>P53-L53-M53-N53</f>
+        <v/>
+      </c>
+      <c r="P53" t="n">
+        <v>6326.417</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1633.455</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1657.384</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1565.109</v>
+      </c>
+      <c r="T53" s="9">
+        <f>U53-Q53-R53-S53</f>
+        <v/>
+      </c>
+      <c r="U53" t="n">
+        <v>6450.213</v>
       </c>
       <c r="V53" t="n">
         <v>1582.956</v>
@@ -16577,37 +16673,69 @@
           <t>กำไรสุทธิ (รวม)</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="9">
-        <f>B54+C54+D54+E54</f>
-        <v/>
-      </c>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="9">
-        <f>G54+H54+I54+J54</f>
-        <v/>
-      </c>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
-      <c r="N54" s="5" t="n"/>
-      <c r="O54" s="5" t="n"/>
-      <c r="P54" s="9">
-        <f>L54+M54+N54+O54</f>
-        <v/>
-      </c>
-      <c r="Q54" s="5" t="n"/>
-      <c r="R54" s="5" t="n"/>
-      <c r="S54" s="5" t="n"/>
-      <c r="T54" s="5" t="n"/>
-      <c r="U54" s="9">
-        <f>Q54+R54+S54+T54</f>
-        <v/>
+      <c r="B54" t="n">
+        <v>-310.898</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-571.4349999999999</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-281.861</v>
+      </c>
+      <c r="E54" s="9">
+        <f>F54-B54-C54-D54</f>
+        <v/>
+      </c>
+      <c r="F54" t="n">
+        <v>-1234.222</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-204.086</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-96.879</v>
+      </c>
+      <c r="I54" t="n">
+        <v>207.484</v>
+      </c>
+      <c r="J54" s="9">
+        <f>K54-G54-H54-I54</f>
+        <v/>
+      </c>
+      <c r="K54" t="n">
+        <v>14.382</v>
+      </c>
+      <c r="L54" t="n">
+        <v>124.881</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.004</v>
+      </c>
+      <c r="N54" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="O54" s="9">
+        <f>P54-L54-M54-N54</f>
+        <v/>
+      </c>
+      <c r="P54" t="n">
+        <v>86.407</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>111.624</v>
+      </c>
+      <c r="R54" t="n">
+        <v>-71.592</v>
+      </c>
+      <c r="S54" t="n">
+        <v>-53.396</v>
+      </c>
+      <c r="T54" s="9">
+        <f>U54-Q54-R54-S54</f>
+        <v/>
+      </c>
+      <c r="U54" t="n">
+        <v>133.934</v>
       </c>
       <c r="V54" t="n">
         <v>175.544</v>
@@ -16635,7 +16763,10 @@
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="5" t="n"/>
       <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
+      <c r="E55" s="9">
+        <f>F55-B55-C55-D55</f>
+        <v/>
+      </c>
       <c r="F55" s="9">
         <f>B55+C55+D55+E55</f>
         <v/>
@@ -16643,7 +16774,10 @@
       <c r="G55" s="5" t="n"/>
       <c r="H55" s="5" t="n"/>
       <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
+      <c r="J55" s="9">
+        <f>K55-G55-H55-I55</f>
+        <v/>
+      </c>
       <c r="K55" s="9">
         <f>G55+H55+I55+J55</f>
         <v/>
@@ -16651,7 +16785,10 @@
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="5" t="n"/>
       <c r="N55" s="5" t="n"/>
-      <c r="O55" s="5" t="n"/>
+      <c r="O55" s="9">
+        <f>P55-L55-M55-N55</f>
+        <v/>
+      </c>
       <c r="P55" s="9">
         <f>L55+M55+N55+O55</f>
         <v/>
@@ -16659,7 +16796,10 @@
       <c r="Q55" s="5" t="n"/>
       <c r="R55" s="5" t="n"/>
       <c r="S55" s="5" t="n"/>
-      <c r="T55" s="5" t="n"/>
+      <c r="T55" s="9">
+        <f>U55-Q55-R55-S55</f>
+        <v/>
+      </c>
       <c r="U55" s="9">
         <f>Q55+R55+S55+T55</f>
         <v/>
@@ -20730,22 +20870,54 @@
           <t>ลูกหนี้การค้า</t>
         </is>
       </c>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="5" t="n"/>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="n"/>
-      <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
-      <c r="N59" s="5" t="n"/>
-      <c r="O59" s="5" t="n"/>
-      <c r="P59" s="5" t="n"/>
-      <c r="Q59" s="5" t="n"/>
+      <c r="B59" t="n">
+        <v>52.299</v>
+      </c>
+      <c r="C59" t="n">
+        <v>113.022</v>
+      </c>
+      <c r="D59" t="n">
+        <v>116.663</v>
+      </c>
+      <c r="E59" t="n">
+        <v>212.509</v>
+      </c>
+      <c r="F59" t="n">
+        <v>387.226</v>
+      </c>
+      <c r="G59" t="n">
+        <v>392.217</v>
+      </c>
+      <c r="H59" t="n">
+        <v>439.668</v>
+      </c>
+      <c r="I59" t="n">
+        <v>464.506</v>
+      </c>
+      <c r="J59" t="n">
+        <v>501.356</v>
+      </c>
+      <c r="K59" t="n">
+        <v>437.075</v>
+      </c>
+      <c r="L59" t="n">
+        <v>443.983</v>
+      </c>
+      <c r="M59" t="n">
+        <v>386.003</v>
+      </c>
+      <c r="N59" t="n">
+        <v>534.556</v>
+      </c>
+      <c r="O59" t="n">
+        <v>480.556</v>
+      </c>
+      <c r="P59" t="n">
+        <v>343.433</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>316.165</v>
+      </c>
       <c r="R59" t="n">
         <v>475.753</v>
       </c>
@@ -20768,22 +20940,54 @@
           <t>สินค้าคงเหลือ</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="5" t="n"/>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="n"/>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="n"/>
-      <c r="O60" s="5" t="n"/>
-      <c r="P60" s="5" t="n"/>
-      <c r="Q60" s="5" t="n"/>
+      <c r="B60" t="n">
+        <v>175.762</v>
+      </c>
+      <c r="C60" t="n">
+        <v>184.864</v>
+      </c>
+      <c r="D60" t="n">
+        <v>165.008</v>
+      </c>
+      <c r="E60" t="n">
+        <v>168.977</v>
+      </c>
+      <c r="F60" t="n">
+        <v>197.777</v>
+      </c>
+      <c r="G60" t="n">
+        <v>194.508</v>
+      </c>
+      <c r="H60" t="n">
+        <v>205.79</v>
+      </c>
+      <c r="I60" t="n">
+        <v>214.535</v>
+      </c>
+      <c r="J60" t="n">
+        <v>228.506</v>
+      </c>
+      <c r="K60" t="n">
+        <v>222.848</v>
+      </c>
+      <c r="L60" t="n">
+        <v>233.082</v>
+      </c>
+      <c r="M60" t="n">
+        <v>230.417</v>
+      </c>
+      <c r="N60" t="n">
+        <v>230.951</v>
+      </c>
+      <c r="O60" t="n">
+        <v>219.271</v>
+      </c>
+      <c r="P60" t="n">
+        <v>220.927</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>199.997</v>
+      </c>
       <c r="R60" t="n">
         <v>232.259</v>
       </c>
@@ -20806,24 +21010,56 @@
           <t>เจ้าหนี้การค้า</t>
         </is>
       </c>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="5" t="n"/>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="n"/>
-      <c r="G61" s="5" t="n"/>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="n"/>
-      <c r="L61" s="5" t="n"/>
-      <c r="M61" s="5" t="n"/>
-      <c r="N61" s="5" t="n"/>
-      <c r="O61" s="5" t="n"/>
-      <c r="P61" s="5" t="n"/>
-      <c r="Q61" s="5" t="n"/>
+      <c r="B61" t="n">
+        <v>587.285</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1434.284</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1311.748</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1503.368</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1634.569</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1603.991</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1687.776</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1535.406</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1710.634</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1726.671</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1764.509</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1719.383</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1666.948</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1545.236</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1017.739</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>934.721</v>
+      </c>
       <c r="R61" t="n">
-        <v>975.128</v>
+        <v>975.127</v>
       </c>
       <c r="S61" t="n">
         <v>865.016</v>
@@ -20844,22 +21080,54 @@
           <t>สินทรัพย์รวม</t>
         </is>
       </c>
-      <c r="B62" s="5" t="n"/>
-      <c r="C62" s="5" t="n"/>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="n"/>
-      <c r="G62" s="5" t="n"/>
-      <c r="H62" s="5" t="n"/>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
-      <c r="L62" s="5" t="n"/>
-      <c r="M62" s="5" t="n"/>
-      <c r="N62" s="5" t="n"/>
-      <c r="O62" s="5" t="n"/>
-      <c r="P62" s="5" t="n"/>
-      <c r="Q62" s="5" t="n"/>
+      <c r="B62" t="n">
+        <v>27117.268</v>
+      </c>
+      <c r="C62" t="n">
+        <v>36754.953</v>
+      </c>
+      <c r="D62" t="n">
+        <v>37165.42</v>
+      </c>
+      <c r="E62" t="n">
+        <v>38408.151</v>
+      </c>
+      <c r="F62" t="n">
+        <v>37214.118</v>
+      </c>
+      <c r="G62" t="n">
+        <v>36458.411</v>
+      </c>
+      <c r="H62" t="n">
+        <v>37047.483</v>
+      </c>
+      <c r="I62" t="n">
+        <v>38433.024</v>
+      </c>
+      <c r="J62" t="n">
+        <v>36449.599</v>
+      </c>
+      <c r="K62" t="n">
+        <v>36139.858</v>
+      </c>
+      <c r="L62" t="n">
+        <v>38010.378</v>
+      </c>
+      <c r="M62" t="n">
+        <v>38311.374</v>
+      </c>
+      <c r="N62" t="n">
+        <v>37722.704</v>
+      </c>
+      <c r="O62" t="n">
+        <v>39325.93</v>
+      </c>
+      <c r="P62" t="n">
+        <v>38844.783</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>35396.49</v>
+      </c>
       <c r="R62" t="n">
         <v>36325.359</v>
       </c>
@@ -20882,22 +21150,54 @@
           <t>ส่วนของเจ้าของรวม</t>
         </is>
       </c>
-      <c r="B63" s="5" t="n"/>
-      <c r="C63" s="5" t="n"/>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="5" t="n"/>
-      <c r="H63" s="5" t="n"/>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="5" t="n"/>
-      <c r="L63" s="5" t="n"/>
-      <c r="M63" s="5" t="n"/>
-      <c r="N63" s="5" t="n"/>
-      <c r="O63" s="5" t="n"/>
-      <c r="P63" s="5" t="n"/>
-      <c r="Q63" s="5" t="n"/>
+      <c r="B63" t="n">
+        <v>15675.937</v>
+      </c>
+      <c r="C63" t="n">
+        <v>15954.945</v>
+      </c>
+      <c r="D63" t="n">
+        <v>15819.261</v>
+      </c>
+      <c r="E63" t="n">
+        <v>16238.608</v>
+      </c>
+      <c r="F63" t="n">
+        <v>15881.858</v>
+      </c>
+      <c r="G63" t="n">
+        <v>15549.686</v>
+      </c>
+      <c r="H63" t="n">
+        <v>15997.386</v>
+      </c>
+      <c r="I63" t="n">
+        <v>17083.078</v>
+      </c>
+      <c r="J63" t="n">
+        <v>16019.169</v>
+      </c>
+      <c r="K63" t="n">
+        <v>15973.516</v>
+      </c>
+      <c r="L63" t="n">
+        <v>16580.939</v>
+      </c>
+      <c r="M63" t="n">
+        <v>16834.999</v>
+      </c>
+      <c r="N63" t="n">
+        <v>16091.047</v>
+      </c>
+      <c r="O63" t="n">
+        <v>17091.248</v>
+      </c>
+      <c r="P63" t="n">
+        <v>17119.998</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>15365.781</v>
+      </c>
       <c r="R63" t="n">
         <v>15925.838</v>
       </c>
@@ -20920,22 +21220,54 @@
           <t>หนี้สินรวม</t>
         </is>
       </c>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="5" t="n"/>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="n"/>
-      <c r="L64" s="5" t="n"/>
-      <c r="M64" s="5" t="n"/>
-      <c r="N64" s="5" t="n"/>
-      <c r="O64" s="5" t="n"/>
-      <c r="P64" s="5" t="n"/>
-      <c r="Q64" s="5" t="n"/>
+      <c r="B64" t="n">
+        <v>11441.331</v>
+      </c>
+      <c r="C64" t="n">
+        <v>20800.008</v>
+      </c>
+      <c r="D64" t="n">
+        <v>21346.159</v>
+      </c>
+      <c r="E64" t="n">
+        <v>22169.543</v>
+      </c>
+      <c r="F64" t="n">
+        <v>21332.26</v>
+      </c>
+      <c r="G64" t="n">
+        <v>20908.725</v>
+      </c>
+      <c r="H64" t="n">
+        <v>21050.097</v>
+      </c>
+      <c r="I64" t="n">
+        <v>21349.946</v>
+      </c>
+      <c r="J64" t="n">
+        <v>20430.43</v>
+      </c>
+      <c r="K64" t="n">
+        <v>20166.342</v>
+      </c>
+      <c r="L64" t="n">
+        <v>21429.439</v>
+      </c>
+      <c r="M64" t="n">
+        <v>21476.375</v>
+      </c>
+      <c r="N64" t="n">
+        <v>21631.656</v>
+      </c>
+      <c r="O64" t="n">
+        <v>22234.682</v>
+      </c>
+      <c r="P64" t="n">
+        <v>21724.785</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>20030.709</v>
+      </c>
       <c r="R64" t="n">
         <v>20399.521</v>
       </c>
@@ -21366,7 +21698,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=20, MANRIN=17, MINT=20, OHTL=20, SHANG=20, SHR=4, VRANDA=4</t>
+          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=20, MANRIN=17, MINT=20, OHTL=20, SHANG=20, SHR=20, VRANDA=4</t>
         </is>
       </c>
     </row>

--- a/tour-finance/output/TOUR_all_linked.xlsx
+++ b/tour-finance/output/TOUR_all_linked.xlsx
@@ -16854,37 +16854,69 @@
           <t>รายได้รวม</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="9">
-        <f>B57+C57+D57+E57</f>
-        <v/>
-      </c>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="9">
-        <f>G57+H57+I57+J57</f>
-        <v/>
-      </c>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
-      <c r="N57" s="5" t="n"/>
-      <c r="O57" s="5" t="n"/>
-      <c r="P57" s="9">
-        <f>L57+M57+N57+O57</f>
-        <v/>
-      </c>
-      <c r="Q57" s="5" t="n"/>
-      <c r="R57" s="5" t="n"/>
-      <c r="S57" s="5" t="n"/>
-      <c r="T57" s="5" t="n"/>
-      <c r="U57" s="9">
-        <f>Q57+R57+S57+T57</f>
-        <v/>
+      <c r="B57" t="n">
+        <v>356.129</v>
+      </c>
+      <c r="C57" t="n">
+        <v>314.481</v>
+      </c>
+      <c r="D57" t="n">
+        <v>239.763</v>
+      </c>
+      <c r="E57" s="9">
+        <f>F57-B57-C57-D57</f>
+        <v/>
+      </c>
+      <c r="F57" t="n">
+        <v>1307.472</v>
+      </c>
+      <c r="G57" t="n">
+        <v>306.885</v>
+      </c>
+      <c r="H57" t="n">
+        <v>323.864</v>
+      </c>
+      <c r="I57" t="n">
+        <v>329.927</v>
+      </c>
+      <c r="J57" s="9">
+        <f>K57-G57-H57-I57</f>
+        <v/>
+      </c>
+      <c r="K57" t="n">
+        <v>1365.82</v>
+      </c>
+      <c r="L57" t="n">
+        <v>382.669</v>
+      </c>
+      <c r="M57" t="n">
+        <v>315.369</v>
+      </c>
+      <c r="N57" t="n">
+        <v>328.523</v>
+      </c>
+      <c r="O57" s="9">
+        <f>P57-L57-M57-N57</f>
+        <v/>
+      </c>
+      <c r="P57" t="n">
+        <v>1402.468</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>420.897</v>
+      </c>
+      <c r="R57" t="n">
+        <v>348.916</v>
+      </c>
+      <c r="S57" t="n">
+        <v>389.591</v>
+      </c>
+      <c r="T57" s="9">
+        <f>U57-Q57-R57-S57</f>
+        <v/>
+      </c>
+      <c r="U57" t="n">
+        <v>1537.433</v>
       </c>
       <c r="V57" t="n">
         <v>427.929</v>
@@ -16909,37 +16941,69 @@
           <t>รายได้อื่น</t>
         </is>
       </c>
-      <c r="B58" s="5" t="n"/>
-      <c r="C58" s="5" t="n"/>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="9">
-        <f>B58+C58+D58+E58</f>
-        <v/>
-      </c>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="9">
-        <f>G58+H58+I58+J58</f>
-        <v/>
-      </c>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="n"/>
-      <c r="O58" s="5" t="n"/>
-      <c r="P58" s="9">
-        <f>L58+M58+N58+O58</f>
-        <v/>
-      </c>
-      <c r="Q58" s="5" t="n"/>
-      <c r="R58" s="5" t="n"/>
-      <c r="S58" s="5" t="n"/>
-      <c r="T58" s="5" t="n"/>
-      <c r="U58" s="9">
-        <f>Q58+R58+S58+T58</f>
-        <v/>
+      <c r="B58" t="n">
+        <v>17.274</v>
+      </c>
+      <c r="C58" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="D58" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="E58" s="9">
+        <f>F58-B58-C58-D58</f>
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v>37.031</v>
+      </c>
+      <c r="G58" t="n">
+        <v>15.989</v>
+      </c>
+      <c r="H58" t="n">
+        <v>11.119</v>
+      </c>
+      <c r="I58" t="n">
+        <v>7.932</v>
+      </c>
+      <c r="J58" s="9">
+        <f>K58-G58-H58-I58</f>
+        <v/>
+      </c>
+      <c r="K58" t="n">
+        <v>44.869</v>
+      </c>
+      <c r="L58" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="M58" t="n">
+        <v>8.962999999999999</v>
+      </c>
+      <c r="N58" t="n">
+        <v>6.424</v>
+      </c>
+      <c r="O58" s="9">
+        <f>P58-L58-M58-N58</f>
+        <v/>
+      </c>
+      <c r="P58" t="n">
+        <v>31.828</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>12.142</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6.223</v>
+      </c>
+      <c r="S58" t="n">
+        <v>6.399</v>
+      </c>
+      <c r="T58" s="9">
+        <f>U58-Q58-R58-S58</f>
+        <v/>
+      </c>
+      <c r="U58" t="n">
+        <v>35.426</v>
       </c>
       <c r="V58" t="n">
         <v>15.045</v>
@@ -16964,37 +17028,69 @@
           <t>ต้นทุนขาย (จริง)</t>
         </is>
       </c>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="5" t="n"/>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="9">
-        <f>B59+C59+D59+E59</f>
-        <v/>
-      </c>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="9">
-        <f>G59+H59+I59+J59</f>
-        <v/>
-      </c>
-      <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
-      <c r="N59" s="5" t="n"/>
-      <c r="O59" s="5" t="n"/>
-      <c r="P59" s="9">
-        <f>L59+M59+N59+O59</f>
-        <v/>
-      </c>
-      <c r="Q59" s="5" t="n"/>
-      <c r="R59" s="5" t="n"/>
-      <c r="S59" s="5" t="n"/>
-      <c r="T59" s="5" t="n"/>
-      <c r="U59" s="9">
-        <f>Q59+R59+S59+T59</f>
-        <v/>
+      <c r="B59" t="n">
+        <v>111.345</v>
+      </c>
+      <c r="C59" t="n">
+        <v>89.117</v>
+      </c>
+      <c r="D59" t="n">
+        <v>90.499</v>
+      </c>
+      <c r="E59" s="9">
+        <f>F59-B59-C59-D59</f>
+        <v/>
+      </c>
+      <c r="F59" t="n">
+        <v>433.732</v>
+      </c>
+      <c r="G59" t="n">
+        <v>130.674</v>
+      </c>
+      <c r="H59" t="n">
+        <v>152.008</v>
+      </c>
+      <c r="I59" t="n">
+        <v>166.305</v>
+      </c>
+      <c r="J59" s="9">
+        <f>K59-G59-H59-I59</f>
+        <v/>
+      </c>
+      <c r="K59" t="n">
+        <v>639.546</v>
+      </c>
+      <c r="L59" t="n">
+        <v>180.764</v>
+      </c>
+      <c r="M59" t="n">
+        <v>175.78</v>
+      </c>
+      <c r="N59" t="n">
+        <v>177.091</v>
+      </c>
+      <c r="O59" s="9">
+        <f>P59-L59-M59-N59</f>
+        <v/>
+      </c>
+      <c r="P59" t="n">
+        <v>723.39</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>189.69</v>
+      </c>
+      <c r="R59" t="n">
+        <v>174.55</v>
+      </c>
+      <c r="S59" t="n">
+        <v>178.731</v>
+      </c>
+      <c r="T59" s="9">
+        <f>U59-Q59-R59-S59</f>
+        <v/>
+      </c>
+      <c r="U59" t="n">
+        <v>739.745</v>
       </c>
       <c r="V59" t="n">
         <v>218.02</v>
@@ -17019,37 +17115,69 @@
           <t>กำไรสุทธิ (รวม)</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="5" t="n"/>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="9">
-        <f>B60+C60+D60+E60</f>
-        <v/>
-      </c>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="9">
-        <f>G60+H60+I60+J60</f>
-        <v/>
-      </c>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="n"/>
-      <c r="O60" s="5" t="n"/>
-      <c r="P60" s="9">
-        <f>L60+M60+N60+O60</f>
-        <v/>
-      </c>
-      <c r="Q60" s="5" t="n"/>
-      <c r="R60" s="5" t="n"/>
-      <c r="S60" s="5" t="n"/>
-      <c r="T60" s="5" t="n"/>
-      <c r="U60" s="9">
-        <f>Q60+R60+S60+T60</f>
-        <v/>
+      <c r="B60" t="n">
+        <v>-34.673</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-35.359</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-49.808</v>
+      </c>
+      <c r="E60" s="9">
+        <f>F60-B60-C60-D60</f>
+        <v/>
+      </c>
+      <c r="F60" t="n">
+        <v>-107.249</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-21.359</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="I60" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="J60" s="9">
+        <f>K60-G60-H60-I60</f>
+        <v/>
+      </c>
+      <c r="K60" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="L60" t="n">
+        <v>7.072</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-14.771</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-20.352</v>
+      </c>
+      <c r="O60" s="9">
+        <f>P60-L60-M60-N60</f>
+        <v/>
+      </c>
+      <c r="P60" t="n">
+        <v>-140.769</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>36.301</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5.086</v>
+      </c>
+      <c r="T60" s="9">
+        <f>U60-Q60-R60-S60</f>
+        <v/>
+      </c>
+      <c r="U60" t="n">
+        <v>51.188</v>
       </c>
       <c r="V60" t="n">
         <v>42.867</v>
@@ -17074,37 +17202,70 @@
           <t>กำไรสุทธิ (ส่วนแม่)</t>
         </is>
       </c>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="5" t="n"/>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
+      <c r="B61" t="n">
+        <v>-34.673</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-35.359</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-49.808</v>
+      </c>
+      <c r="E61" s="9">
+        <f>F61-B61-C61-D61</f>
+        <v/>
+      </c>
       <c r="F61" s="9">
         <f>B61+C61+D61+E61</f>
         <v/>
       </c>
-      <c r="G61" s="5" t="n"/>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="9">
-        <f>G61+H61+I61+J61</f>
-        <v/>
-      </c>
-      <c r="L61" s="5" t="n"/>
-      <c r="M61" s="5" t="n"/>
-      <c r="N61" s="5" t="n"/>
-      <c r="O61" s="5" t="n"/>
-      <c r="P61" s="9">
-        <f>L61+M61+N61+O61</f>
-        <v/>
-      </c>
-      <c r="Q61" s="5" t="n"/>
-      <c r="R61" s="5" t="n"/>
-      <c r="S61" s="5" t="n"/>
-      <c r="T61" s="5" t="n"/>
-      <c r="U61" s="9">
-        <f>Q61+R61+S61+T61</f>
-        <v/>
+      <c r="G61" t="n">
+        <v>-21.359</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="J61" s="9">
+        <f>K61-G61-H61-I61</f>
+        <v/>
+      </c>
+      <c r="K61" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="L61" t="n">
+        <v>7.072</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-14.771</v>
+      </c>
+      <c r="N61" t="n">
+        <v>-20.352</v>
+      </c>
+      <c r="O61" s="9">
+        <f>P61-L61-M61-N61</f>
+        <v/>
+      </c>
+      <c r="P61" t="n">
+        <v>-140.769</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>36.301</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5.086</v>
+      </c>
+      <c r="T61" s="9">
+        <f>U61-Q61-R61-S61</f>
+        <v/>
+      </c>
+      <c r="U61" t="n">
+        <v>51.188</v>
       </c>
       <c r="V61" t="n">
         <v>42.867</v>
@@ -21318,22 +21479,54 @@
           <t>ลูกหนี้การค้า</t>
         </is>
       </c>
-      <c r="B66" s="5" t="n"/>
-      <c r="C66" s="5" t="n"/>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="5" t="n"/>
-      <c r="H66" s="5" t="n"/>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="n"/>
-      <c r="L66" s="5" t="n"/>
-      <c r="M66" s="5" t="n"/>
-      <c r="N66" s="5" t="n"/>
-      <c r="O66" s="5" t="n"/>
-      <c r="P66" s="5" t="n"/>
-      <c r="Q66" s="5" t="n"/>
+      <c r="B66" t="n">
+        <v>32.556</v>
+      </c>
+      <c r="C66" t="n">
+        <v>25.334</v>
+      </c>
+      <c r="D66" t="n">
+        <v>26.575</v>
+      </c>
+      <c r="E66" t="n">
+        <v>34.836</v>
+      </c>
+      <c r="F66" t="n">
+        <v>42.684</v>
+      </c>
+      <c r="G66" t="n">
+        <v>36.444</v>
+      </c>
+      <c r="H66" t="n">
+        <v>40.884</v>
+      </c>
+      <c r="I66" t="n">
+        <v>39.706</v>
+      </c>
+      <c r="J66" t="n">
+        <v>52.742</v>
+      </c>
+      <c r="K66" t="n">
+        <v>43.357</v>
+      </c>
+      <c r="L66" t="n">
+        <v>37.041</v>
+      </c>
+      <c r="M66" t="n">
+        <v>44.533</v>
+      </c>
+      <c r="N66" t="n">
+        <v>55.106</v>
+      </c>
+      <c r="O66" t="n">
+        <v>49.507</v>
+      </c>
+      <c r="P66" t="n">
+        <v>52.801</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>38.157</v>
+      </c>
       <c r="R66" t="n">
         <v>55.427</v>
       </c>
@@ -21356,22 +21549,54 @@
           <t>สินค้าคงเหลือ</t>
         </is>
       </c>
-      <c r="B67" s="5" t="n"/>
-      <c r="C67" s="5" t="n"/>
-      <c r="D67" s="5" t="n"/>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="n"/>
-      <c r="G67" s="5" t="n"/>
-      <c r="H67" s="5" t="n"/>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="5" t="n"/>
-      <c r="L67" s="5" t="n"/>
-      <c r="M67" s="5" t="n"/>
-      <c r="N67" s="5" t="n"/>
-      <c r="O67" s="5" t="n"/>
-      <c r="P67" s="5" t="n"/>
-      <c r="Q67" s="5" t="n"/>
+      <c r="B67" t="n">
+        <v>22.856</v>
+      </c>
+      <c r="C67" t="n">
+        <v>20.845</v>
+      </c>
+      <c r="D67" t="n">
+        <v>21.035</v>
+      </c>
+      <c r="E67" t="n">
+        <v>20.024</v>
+      </c>
+      <c r="F67" t="n">
+        <v>18.876</v>
+      </c>
+      <c r="G67" t="n">
+        <v>17.516</v>
+      </c>
+      <c r="H67" t="n">
+        <v>17.115</v>
+      </c>
+      <c r="I67" t="n">
+        <v>17.758</v>
+      </c>
+      <c r="J67" t="n">
+        <v>19.872</v>
+      </c>
+      <c r="K67" t="n">
+        <v>18.562</v>
+      </c>
+      <c r="L67" t="n">
+        <v>18.568</v>
+      </c>
+      <c r="M67" t="n">
+        <v>17.729</v>
+      </c>
+      <c r="N67" t="n">
+        <v>17.401</v>
+      </c>
+      <c r="O67" t="n">
+        <v>14.345</v>
+      </c>
+      <c r="P67" t="n">
+        <v>13.825</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>13.835</v>
+      </c>
       <c r="R67" t="n">
         <v>16.851</v>
       </c>
@@ -21394,22 +21619,54 @@
           <t>เจ้าหนี้การค้า</t>
         </is>
       </c>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="5" t="n"/>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="n"/>
-      <c r="H68" s="5" t="n"/>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="5" t="n"/>
-      <c r="K68" s="5" t="n"/>
-      <c r="L68" s="5" t="n"/>
-      <c r="M68" s="5" t="n"/>
-      <c r="N68" s="5" t="n"/>
-      <c r="O68" s="5" t="n"/>
-      <c r="P68" s="5" t="n"/>
-      <c r="Q68" s="5" t="n"/>
+      <c r="B68" t="n">
+        <v>260.916</v>
+      </c>
+      <c r="C68" t="n">
+        <v>180.669</v>
+      </c>
+      <c r="D68" t="n">
+        <v>176.007</v>
+      </c>
+      <c r="E68" t="n">
+        <v>174.968</v>
+      </c>
+      <c r="F68" t="n">
+        <v>184.913</v>
+      </c>
+      <c r="G68" t="n">
+        <v>163.586</v>
+      </c>
+      <c r="H68" t="n">
+        <v>166.155</v>
+      </c>
+      <c r="I68" t="n">
+        <v>161.027</v>
+      </c>
+      <c r="J68" t="n">
+        <v>196.33</v>
+      </c>
+      <c r="K68" t="n">
+        <v>185.14</v>
+      </c>
+      <c r="L68" t="n">
+        <v>185.093</v>
+      </c>
+      <c r="M68" t="n">
+        <v>221.45</v>
+      </c>
+      <c r="N68" t="n">
+        <v>280.552</v>
+      </c>
+      <c r="O68" t="n">
+        <v>300.211</v>
+      </c>
+      <c r="P68" t="n">
+        <v>323.586</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>331.171</v>
+      </c>
       <c r="R68" t="n">
         <v>440.911</v>
       </c>
@@ -21432,22 +21689,54 @@
           <t>สินทรัพย์รวม</t>
         </is>
       </c>
-      <c r="B69" s="5" t="n"/>
-      <c r="C69" s="5" t="n"/>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="n"/>
-      <c r="L69" s="5" t="n"/>
-      <c r="M69" s="5" t="n"/>
-      <c r="N69" s="5" t="n"/>
-      <c r="O69" s="5" t="n"/>
-      <c r="P69" s="5" t="n"/>
-      <c r="Q69" s="5" t="n"/>
+      <c r="B69" t="n">
+        <v>5353.744</v>
+      </c>
+      <c r="C69" t="n">
+        <v>5081.931</v>
+      </c>
+      <c r="D69" t="n">
+        <v>4908.636</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4850.744</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4795.433</v>
+      </c>
+      <c r="G69" t="n">
+        <v>4707.634</v>
+      </c>
+      <c r="H69" t="n">
+        <v>4631.572</v>
+      </c>
+      <c r="I69" t="n">
+        <v>4558.176</v>
+      </c>
+      <c r="J69" t="n">
+        <v>4740.703</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4656.829</v>
+      </c>
+      <c r="L69" t="n">
+        <v>4621.775</v>
+      </c>
+      <c r="M69" t="n">
+        <v>4701.844</v>
+      </c>
+      <c r="N69" t="n">
+        <v>4803.484</v>
+      </c>
+      <c r="O69" t="n">
+        <v>4873.268</v>
+      </c>
+      <c r="P69" t="n">
+        <v>5061.003</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>5255.116</v>
+      </c>
       <c r="R69" t="n">
         <v>5614.758</v>
       </c>
@@ -21470,22 +21759,54 @@
           <t>ส่วนของเจ้าของรวม</t>
         </is>
       </c>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="5" t="n"/>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="5" t="n"/>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="n"/>
-      <c r="L70" s="5" t="n"/>
-      <c r="M70" s="5" t="n"/>
-      <c r="N70" s="5" t="n"/>
-      <c r="O70" s="5" t="n"/>
-      <c r="P70" s="5" t="n"/>
-      <c r="Q70" s="5" t="n"/>
+      <c r="B70" t="n">
+        <v>2069.246</v>
+      </c>
+      <c r="C70" t="n">
+        <v>2034.573</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1967.246</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1917.438</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1930.028</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1908.669</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1910.388</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1912.418</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1931.141</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1938.213</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1923.442</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1903.09</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1787.905</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1824.206</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1824.873</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1829.959</v>
+      </c>
       <c r="R70" t="n">
         <v>1839.092</v>
       </c>
@@ -21508,22 +21829,54 @@
           <t>หนี้สินรวม</t>
         </is>
       </c>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="5" t="n"/>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="5" t="n"/>
-      <c r="L71" s="5" t="n"/>
-      <c r="M71" s="5" t="n"/>
-      <c r="N71" s="5" t="n"/>
-      <c r="O71" s="5" t="n"/>
-      <c r="P71" s="5" t="n"/>
-      <c r="Q71" s="5" t="n"/>
+      <c r="B71" t="n">
+        <v>3284.498</v>
+      </c>
+      <c r="C71" t="n">
+        <v>3047.358</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2941.39</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2933.306</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2865.405</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2798.965</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2721.184</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2645.758</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2809.562</v>
+      </c>
+      <c r="K71" t="n">
+        <v>2718.616</v>
+      </c>
+      <c r="L71" t="n">
+        <v>2698.333</v>
+      </c>
+      <c r="M71" t="n">
+        <v>2798.754</v>
+      </c>
+      <c r="N71" t="n">
+        <v>3015.579</v>
+      </c>
+      <c r="O71" t="n">
+        <v>3049.062</v>
+      </c>
+      <c r="P71" t="n">
+        <v>3236.13</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>3425.157</v>
+      </c>
       <c r="R71" t="n">
         <v>3775.666</v>
       </c>
@@ -21698,7 +22051,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=20, MANRIN=17, MINT=20, OHTL=20, SHANG=20, SHR=20, VRANDA=4</t>
+          <t>จำนวนงวดที่มีข้อมูลจริงแล้ว (จากทั้งหมด 20 ไตรมาส): ASIA=20, CENTEL=20, DUSIT=20, ERW=20, MANRIN=17, MINT=20, OHTL=20, SHANG=20, SHR=20, VRANDA=20</t>
         </is>
       </c>
     </row>

--- a/tour-finance/output/TOUR_all_linked.xlsx
+++ b/tour-finance/output/TOUR_all_linked.xlsx
@@ -13077,10 +13077,7 @@
       <c r="D7" t="n">
         <v>-36.74</v>
       </c>
-      <c r="E7" s="9">
-        <f>F7-B7-C7-D7</f>
-        <v/>
-      </c>
+      <c r="E7" s="5" t="n"/>
       <c r="F7" s="9">
         <f>B7+C7+D7+E7</f>
         <v/>
@@ -13092,10 +13089,7 @@
       <c r="I7" t="n">
         <v>-24.879</v>
       </c>
-      <c r="J7" s="9">
-        <f>K7-G7-H7-I7</f>
-        <v/>
-      </c>
+      <c r="J7" s="5" t="n"/>
       <c r="K7" s="9">
         <f>G7+H7+I7+J7</f>
         <v/>
@@ -13107,10 +13101,7 @@
       <c r="N7" t="n">
         <v>6.344</v>
       </c>
-      <c r="O7" s="9">
-        <f>P7-L7-M7-N7</f>
-        <v/>
-      </c>
+      <c r="O7" s="5" t="n"/>
       <c r="P7" s="9">
         <f>L7+M7+N7+O7</f>
         <v/>
@@ -13122,10 +13113,7 @@
       <c r="S7" t="n">
         <v>-3.001</v>
       </c>
-      <c r="T7" s="9">
-        <f>U7-Q7-R7-S7</f>
-        <v/>
-      </c>
+      <c r="T7" s="5" t="n"/>
       <c r="U7" s="9">
         <f>Q7+R7+S7+T7</f>
         <v/>
@@ -13137,10 +13125,7 @@
       <c r="X7" t="n">
         <v>-5.466</v>
       </c>
-      <c r="Y7" s="9">
-        <f>Z7-V7-W7-X7</f>
-        <v/>
-      </c>
+      <c r="Y7" s="5" t="n"/>
       <c r="Z7" s="9">
         <f>V7+W7+X7+Y7</f>
         <v/>
@@ -14473,10 +14458,7 @@
       <c r="D25" t="n">
         <v>-622.789</v>
       </c>
-      <c r="E25" s="9">
-        <f>F25-B25-C25-D25</f>
-        <v/>
-      </c>
+      <c r="E25" s="5" t="n"/>
       <c r="F25" s="9">
         <f>B25+C25+D25+E25</f>
         <v/>
@@ -14488,10 +14470,7 @@
       <c r="I25" t="n">
         <v>-11.52</v>
       </c>
-      <c r="J25" s="9">
-        <f>K25-G25-H25-I25</f>
-        <v/>
-      </c>
+      <c r="J25" s="5" t="n"/>
       <c r="K25" s="9">
         <f>G25+H25+I25+J25</f>
         <v/>
@@ -14503,10 +14482,7 @@
       <c r="N25" t="n">
         <v>148.293</v>
       </c>
-      <c r="O25" s="9">
-        <f>P25-L25-M25-N25</f>
-        <v/>
-      </c>
+      <c r="O25" s="5" t="n"/>
       <c r="P25" s="9">
         <f>L25+M25+N25+O25</f>
         <v/>
@@ -14518,10 +14494,7 @@
       <c r="S25" t="n">
         <v>124.53</v>
       </c>
-      <c r="T25" s="9">
-        <f>U25-Q25-R25-S25</f>
-        <v/>
-      </c>
+      <c r="T25" s="5" t="n"/>
       <c r="U25" s="9">
         <f>Q25+R25+S25+T25</f>
         <v/>
@@ -14531,10 +14504,7 @@
       <c r="X25" t="n">
         <v>56.6</v>
       </c>
-      <c r="Y25" s="9">
-        <f>Z25-V25-W25-X25</f>
-        <v/>
-      </c>
+      <c r="Y25" s="5" t="n"/>
       <c r="Z25" s="9">
         <f>V25+W25+X25+Y25</f>
         <v/>
@@ -14953,10 +14923,7 @@
       <c r="Q31" s="5" t="n"/>
       <c r="R31" s="5" t="n"/>
       <c r="S31" s="5" t="n"/>
-      <c r="T31" s="9">
-        <f>U31-Q31-R31-S31</f>
-        <v/>
-      </c>
+      <c r="T31" s="5" t="n"/>
       <c r="U31" s="9">
         <f>Q31+R31+S31+T31</f>
         <v/>
@@ -14964,10 +14931,7 @@
       <c r="V31" s="5" t="n"/>
       <c r="W31" s="5" t="n"/>
       <c r="X31" s="5" t="n"/>
-      <c r="Y31" s="9">
-        <f>Z31-V31-W31-X31</f>
-        <v/>
-      </c>
+      <c r="Y31" s="5" t="n"/>
       <c r="Z31" s="9">
         <f>V31+W31+X31+Y31</f>
         <v/>
@@ -16763,10 +16727,7 @@
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="5" t="n"/>
       <c r="D55" s="5" t="n"/>
-      <c r="E55" s="9">
-        <f>F55-B55-C55-D55</f>
-        <v/>
-      </c>
+      <c r="E55" s="5" t="n"/>
       <c r="F55" s="9">
         <f>B55+C55+D55+E55</f>
         <v/>
@@ -16774,10 +16735,7 @@
       <c r="G55" s="5" t="n"/>
       <c r="H55" s="5" t="n"/>
       <c r="I55" s="5" t="n"/>
-      <c r="J55" s="9">
-        <f>K55-G55-H55-I55</f>
-        <v/>
-      </c>
+      <c r="J55" s="5" t="n"/>
       <c r="K55" s="9">
         <f>G55+H55+I55+J55</f>
         <v/>
@@ -16785,10 +16743,7 @@
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="5" t="n"/>
       <c r="N55" s="5" t="n"/>
-      <c r="O55" s="9">
-        <f>P55-L55-M55-N55</f>
-        <v/>
-      </c>
+      <c r="O55" s="5" t="n"/>
       <c r="P55" s="9">
         <f>L55+M55+N55+O55</f>
         <v/>
@@ -16796,10 +16751,7 @@
       <c r="Q55" s="5" t="n"/>
       <c r="R55" s="5" t="n"/>
       <c r="S55" s="5" t="n"/>
-      <c r="T55" s="9">
-        <f>U55-Q55-R55-S55</f>
-        <v/>
-      </c>
+      <c r="T55" s="5" t="n"/>
       <c r="U55" s="9">
         <f>Q55+R55+S55+T55</f>
         <v/>
@@ -16807,10 +16759,7 @@
       <c r="V55" s="5" t="n"/>
       <c r="W55" s="5" t="n"/>
       <c r="X55" s="5" t="n"/>
-      <c r="Y55" s="9">
-        <f>Z55-V55-W55-X55</f>
-        <v/>
-      </c>
+      <c r="Y55" s="5" t="n"/>
       <c r="Z55" s="9">
         <f>V55+W55+X55+Y55</f>
         <v/>
@@ -17211,10 +17160,7 @@
       <c r="D61" t="n">
         <v>-49.808</v>
       </c>
-      <c r="E61" s="9">
-        <f>F61-B61-C61-D61</f>
-        <v/>
-      </c>
+      <c r="E61" s="5" t="n"/>
       <c r="F61" s="9">
         <f>B61+C61+D61+E61</f>
         <v/>

--- a/tour-finance/output/TOUR_all_linked.xlsx
+++ b/tour-finance/output/TOUR_all_linked.xlsx
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>33.155</v>
+        <v>140.797</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>4423.239</v>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>32.852</v>
+        <v>150.322</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>3929.778</v>
@@ -17534,67 +17534,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.655</v>
+        <v>116.615</v>
       </c>
       <c r="C5" t="n">
-        <v>17.226</v>
+        <v>103.557</v>
       </c>
       <c r="D5" t="n">
-        <v>13.107</v>
+        <v>86.577</v>
       </c>
       <c r="E5" t="n">
-        <v>18.514</v>
+        <v>92.384</v>
       </c>
       <c r="F5" t="n">
-        <v>14.131</v>
+        <v>82.438</v>
       </c>
       <c r="G5" t="n">
-        <v>16.515</v>
+        <v>82.773</v>
       </c>
       <c r="H5" t="n">
-        <v>21.681</v>
+        <v>100.259</v>
       </c>
       <c r="I5" t="n">
-        <v>24.026</v>
+        <v>109.055</v>
       </c>
       <c r="J5" t="n">
-        <v>24.926</v>
+        <v>116.107</v>
       </c>
       <c r="K5" t="n">
-        <v>27.178</v>
+        <v>125.439</v>
       </c>
       <c r="L5" t="n">
-        <v>24.927</v>
+        <v>118.84</v>
       </c>
       <c r="M5" t="n">
-        <v>27.801</v>
+        <v>118.148</v>
       </c>
       <c r="N5" t="n">
-        <v>27.136</v>
+        <v>118.752</v>
       </c>
       <c r="O5" t="n">
-        <v>29.724</v>
+        <v>123.558</v>
       </c>
       <c r="P5" t="n">
-        <v>28.136</v>
+        <v>123.974</v>
       </c>
       <c r="Q5" t="n">
-        <v>34.269</v>
+        <v>122.209</v>
       </c>
       <c r="R5" t="n">
-        <v>33.155</v>
+        <v>140.797</v>
       </c>
       <c r="S5" t="n">
-        <v>31.85</v>
+        <v>122.033</v>
       </c>
       <c r="T5" t="n">
-        <v>28.029</v>
+        <v>118.6</v>
       </c>
       <c r="U5" t="n">
-        <v>27.619</v>
+        <v>119.99</v>
       </c>
       <c r="V5" t="n">
-        <v>32.852</v>
+        <v>150.322</v>
       </c>
     </row>
     <row r="6">
@@ -19634,43 +19634,43 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>12285.894</v>
+        <v>14523.92</v>
       </c>
       <c r="C38" t="n">
-        <v>12560.738</v>
+        <v>14721.379</v>
       </c>
       <c r="D38" t="n">
-        <v>12245.698</v>
+        <v>14396.577</v>
       </c>
       <c r="E38" t="n">
-        <v>14057.042</v>
+        <v>16127.792</v>
       </c>
       <c r="F38" t="n">
-        <v>14637.995</v>
+        <v>16864.816</v>
       </c>
       <c r="G38" t="n">
-        <v>18889.532</v>
+        <v>20758.575</v>
       </c>
       <c r="H38" t="n">
-        <v>17198.61</v>
+        <v>19195.547</v>
       </c>
       <c r="I38" t="n">
-        <v>18590.806</v>
+        <v>20887.878</v>
       </c>
       <c r="J38" t="n">
-        <v>17052.269</v>
+        <v>19372.997</v>
       </c>
       <c r="K38" t="n">
-        <v>17614.873</v>
+        <v>20232.1</v>
       </c>
       <c r="L38" t="n">
-        <v>19429.147</v>
+        <v>21612.902</v>
       </c>
       <c r="M38" t="n">
-        <v>19843.861</v>
+        <v>22006.368</v>
       </c>
       <c r="N38" t="n">
-        <v>18487.349</v>
+        <v>20564.327</v>
       </c>
       <c r="O38" t="n">
         <v>19703.261</v>

--- a/tour-finance/output/TOUR_all_linked.xlsx
+++ b/tour-finance/output/TOUR_all_linked.xlsx
@@ -1251,15 +1251,21 @@
           <t>กำไรสุทธิ (ส่วนของผู้ถือหุ้นบริษัทใหญ่)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="5" t="n">
+        <v>-1.129</v>
+      </c>
       <c r="C7" s="5" t="n">
         <v>1992.902</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>-453.313</v>
       </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="E7" s="5" t="n">
+        <v>838.085</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>39.818</v>
+      </c>
       <c r="G7" s="5" t="n">
         <v>9009.342000000001</v>
       </c>
@@ -1269,7 +1275,9 @@
       <c r="I7" s="5" t="n">
         <v>240.912</v>
       </c>
-      <c r="J7" s="5" t="n"/>
+      <c r="J7" s="5" t="n">
+        <v>-1586.048</v>
+      </c>
       <c r="K7" s="5" t="n">
         <v>100.784</v>
       </c>
@@ -13070,65 +13078,85 @@
           <t>กำไรสุทธิ (ส่วนแม่)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" t="n">
+        <v>-48.531</v>
+      </c>
       <c r="C7" t="n">
         <v>-58.854</v>
       </c>
       <c r="D7" t="n">
         <v>-36.74</v>
       </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="9">
-        <f>B7+C7+D7+E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="5" t="n"/>
+      <c r="E7" s="9">
+        <f>F7-B7-C7-D7</f>
+        <v/>
+      </c>
+      <c r="F7" t="n">
+        <v>-209.093</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-49.915</v>
+      </c>
       <c r="H7" t="n">
         <v>-35.074</v>
       </c>
       <c r="I7" t="n">
         <v>-24.879</v>
       </c>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="9">
-        <f>G7+H7+I7+J7</f>
-        <v/>
-      </c>
-      <c r="L7" s="5" t="n"/>
+      <c r="J7" s="9">
+        <f>K7-G7-H7-I7</f>
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v>-111.452</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-11.584</v>
+      </c>
       <c r="M7" t="n">
         <v>-5.349</v>
       </c>
       <c r="N7" t="n">
         <v>6.344</v>
       </c>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="9">
-        <f>L7+M7+N7+O7</f>
-        <v/>
-      </c>
-      <c r="Q7" s="5" t="n"/>
+      <c r="O7" s="9">
+        <f>P7-L7-M7-N7</f>
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v>-54.265</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.637</v>
+      </c>
       <c r="R7" t="n">
         <v>-3.459</v>
       </c>
       <c r="S7" t="n">
         <v>-3.001</v>
       </c>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="9">
-        <f>Q7+R7+S7+T7</f>
-        <v/>
-      </c>
-      <c r="V7" s="5" t="n"/>
+      <c r="T7" s="9">
+        <f>U7-Q7-R7-S7</f>
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v>-2.181</v>
+      </c>
+      <c r="V7" t="n">
+        <v>14.963</v>
+      </c>
       <c r="W7" t="n">
         <v>-14.469</v>
       </c>
       <c r="X7" t="n">
         <v>-5.466</v>
       </c>
-      <c r="Y7" s="5" t="n"/>
-      <c r="Z7" s="9">
-        <f>V7+W7+X7+Y7</f>
-        <v/>
+      <c r="Y7" s="9">
+        <f>Z7-V7-W7-X7</f>
+        <v/>
+      </c>
+      <c r="Z7" t="n">
+        <v>-1.129</v>
       </c>
     </row>
     <row r="8">
@@ -14191,7 +14219,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11.432</v>
+        <v>16.644</v>
       </c>
       <c r="C22" t="n">
         <v>23.294</v>
@@ -14207,7 +14235,7 @@
         <v>77.11799999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>7.275</v>
+        <v>12.487</v>
       </c>
       <c r="H22" t="n">
         <v>69.651</v>
@@ -14223,7 +14251,7 @@
         <v>86.023</v>
       </c>
       <c r="L22" t="n">
-        <v>20.232</v>
+        <v>25.444</v>
       </c>
       <c r="M22" t="n">
         <v>52.552</v>
@@ -14451,63 +14479,85 @@
           <t>กำไรสุทธิ (ส่วนแม่)</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
+      <c r="B25" t="n">
+        <v>-491.944</v>
+      </c>
       <c r="C25" t="n">
         <v>-689.778</v>
       </c>
       <c r="D25" t="n">
         <v>-622.789</v>
       </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="9">
-        <f>B25+C25+D25+E25</f>
-        <v/>
-      </c>
-      <c r="G25" s="5" t="n"/>
+      <c r="E25" s="9">
+        <f>F25-B25-C25-D25</f>
+        <v/>
+      </c>
+      <c r="F25" t="n">
+        <v>-2050.217</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-313.095</v>
+      </c>
       <c r="H25" t="n">
         <v>-139.108</v>
       </c>
       <c r="I25" t="n">
         <v>-11.52</v>
       </c>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="9">
-        <f>G25+H25+I25+J25</f>
-        <v/>
-      </c>
-      <c r="L25" s="5" t="n"/>
+      <c r="J25" s="9">
+        <f>K25-G25-H25-I25</f>
+        <v/>
+      </c>
+      <c r="K25" t="n">
+        <v>-224.19</v>
+      </c>
+      <c r="L25" t="n">
+        <v>238.561</v>
+      </c>
       <c r="M25" t="n">
         <v>141.969</v>
       </c>
       <c r="N25" t="n">
         <v>148.293</v>
       </c>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="9">
-        <f>L25+M25+N25+O25</f>
-        <v/>
-      </c>
-      <c r="Q25" s="5" t="n"/>
+      <c r="O25" s="9">
+        <f>P25-L25-M25-N25</f>
+        <v/>
+      </c>
+      <c r="P25" t="n">
+        <v>742.6559999999999</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>416.953</v>
+      </c>
       <c r="R25" t="n">
         <v>361.434</v>
       </c>
       <c r="S25" t="n">
         <v>124.53</v>
       </c>
-      <c r="T25" s="5" t="n"/>
-      <c r="U25" s="9">
-        <f>Q25+R25+S25+T25</f>
-        <v/>
-      </c>
-      <c r="V25" s="5" t="n"/>
-      <c r="W25" s="5" t="n"/>
+      <c r="T25" s="9">
+        <f>U25-Q25-R25-S25</f>
+        <v/>
+      </c>
+      <c r="U25" t="n">
+        <v>1280.743</v>
+      </c>
+      <c r="V25" t="n">
+        <v>345.382</v>
+      </c>
+      <c r="W25" t="n">
+        <v>63.009</v>
+      </c>
       <c r="X25" t="n">
         <v>56.6</v>
       </c>
-      <c r="Y25" s="5" t="n"/>
-      <c r="Z25" s="9">
-        <f>V25+W25+X25+Y25</f>
-        <v/>
+      <c r="Y25" s="9">
+        <f>Z25-V25-W25-X25</f>
+        <v/>
+      </c>
+      <c r="Z25" t="n">
+        <v>838.085</v>
       </c>
     </row>
     <row r="26">
@@ -14896,45 +14946,85 @@
           <t>กำไรสุทธิ (ส่วนแม่)</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
+      <c r="B31" t="n">
+        <v>-16.489</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-22.583</v>
+      </c>
+      <c r="D31" t="n">
+        <v>12.558</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-22.328</v>
+      </c>
       <c r="F31" s="9">
         <f>B31+C31+D31+E31</f>
         <v/>
       </c>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
+      <c r="G31" t="n">
+        <v>-30.293</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-12.05</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-4.503</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6.961</v>
+      </c>
       <c r="K31" s="9">
         <f>G31+H31+I31+J31</f>
         <v/>
       </c>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
+      <c r="L31" t="n">
+        <v>6.844</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="N31" t="n">
+        <v>15.371</v>
+      </c>
+      <c r="O31" t="n">
+        <v>11.273</v>
+      </c>
       <c r="P31" s="9">
         <f>L31+M31+N31+O31</f>
         <v/>
       </c>
-      <c r="Q31" s="5" t="n"/>
-      <c r="R31" s="5" t="n"/>
-      <c r="S31" s="5" t="n"/>
-      <c r="T31" s="5" t="n"/>
-      <c r="U31" s="9">
-        <f>Q31+R31+S31+T31</f>
-        <v/>
-      </c>
-      <c r="V31" s="5" t="n"/>
-      <c r="W31" s="5" t="n"/>
-      <c r="X31" s="5" t="n"/>
-      <c r="Y31" s="5" t="n"/>
-      <c r="Z31" s="9">
-        <f>V31+W31+X31+Y31</f>
-        <v/>
+      <c r="Q31" t="n">
+        <v>13.794</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6.882</v>
+      </c>
+      <c r="S31" t="n">
+        <v>18.194</v>
+      </c>
+      <c r="T31" s="9">
+        <f>U31-Q31-R31-S31</f>
+        <v/>
+      </c>
+      <c r="U31" t="n">
+        <v>50.821</v>
+      </c>
+      <c r="V31" t="n">
+        <v>14.114</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.665</v>
+      </c>
+      <c r="X31" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="Y31" s="9">
+        <f>Z31-V31-W31-X31</f>
+        <v/>
+      </c>
+      <c r="Z31" t="n">
+        <v>39.818</v>
       </c>
     </row>
     <row r="32">
@@ -16724,45 +16814,85 @@
           <t>กำไรสุทธิ (ส่วนแม่)</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="9">
-        <f>B55+C55+D55+E55</f>
-        <v/>
-      </c>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="9">
-        <f>G55+H55+I55+J55</f>
-        <v/>
-      </c>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
-      <c r="N55" s="5" t="n"/>
-      <c r="O55" s="5" t="n"/>
-      <c r="P55" s="9">
-        <f>L55+M55+N55+O55</f>
-        <v/>
-      </c>
-      <c r="Q55" s="5" t="n"/>
-      <c r="R55" s="5" t="n"/>
-      <c r="S55" s="5" t="n"/>
-      <c r="T55" s="5" t="n"/>
-      <c r="U55" s="9">
-        <f>Q55+R55+S55+T55</f>
-        <v/>
-      </c>
-      <c r="V55" s="5" t="n"/>
-      <c r="W55" s="5" t="n"/>
-      <c r="X55" s="5" t="n"/>
-      <c r="Y55" s="5" t="n"/>
-      <c r="Z55" s="9">
-        <f>V55+W55+X55+Y55</f>
-        <v/>
+      <c r="B55" t="n">
+        <v>-310.898</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-571.4349999999999</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-281.861</v>
+      </c>
+      <c r="E55" s="9">
+        <f>F55-B55-C55-D55</f>
+        <v/>
+      </c>
+      <c r="F55" t="n">
+        <v>-1234.222</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-204.086</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-96.879</v>
+      </c>
+      <c r="I55" t="n">
+        <v>207.484</v>
+      </c>
+      <c r="J55" s="9">
+        <f>K55-G55-H55-I55</f>
+        <v/>
+      </c>
+      <c r="K55" t="n">
+        <v>14.382</v>
+      </c>
+      <c r="L55" t="n">
+        <v>124.881</v>
+      </c>
+      <c r="M55" t="n">
+        <v>-117.222</v>
+      </c>
+      <c r="N55" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="O55" s="9">
+        <f>P55-L55-M55-N55</f>
+        <v/>
+      </c>
+      <c r="P55" t="n">
+        <v>86.407</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>111.624</v>
+      </c>
+      <c r="R55" t="n">
+        <v>-71.592</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-53.396</v>
+      </c>
+      <c r="T55" s="9">
+        <f>U55-Q55-R55-S55</f>
+        <v/>
+      </c>
+      <c r="U55" t="n">
+        <v>133.934</v>
+      </c>
+      <c r="V55" t="n">
+        <v>175.544</v>
+      </c>
+      <c r="W55" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="X55" t="n">
+        <v>128.587</v>
+      </c>
+      <c r="Y55" s="9">
+        <f>Z55-V55-W55-X55</f>
+        <v/>
+      </c>
+      <c r="Z55" t="n">
+        <v>-1586.048</v>
       </c>
     </row>
     <row r="56">
@@ -17160,10 +17290,12 @@
       <c r="D61" t="n">
         <v>-49.808</v>
       </c>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="9">
-        <f>B61+C61+D61+E61</f>
-        <v/>
+      <c r="E61" s="9">
+        <f>F61-B61-C61-D61</f>
+        <v/>
+      </c>
+      <c r="F61" t="n">
+        <v>-107.249</v>
       </c>
       <c r="G61" t="n">
         <v>-21.359</v>
